--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -9,7 +9,7 @@
     <sheet sheetId="3" name="Year 1 Pro Forma" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F84</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-Year Model'!$1:$2</definedName>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="213">
   <si>
     <t>Heritage Academy Charter — Financial Model Assumptions</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>Prior-Year ADA</t>
+  </si>
+  <si>
+    <t>Attendance Ratio (ADA ÷ ADM)</t>
   </si>
   <si>
     <t>Per-Pupil Rate</t>
@@ -801,7 +804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -823,6 +826,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,7 +1187,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2179,72 +2183,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B70" s="15">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="B72" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="C72" s="16" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+      <c r="D72" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B72" s="9">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" s="9">
         <v>8200</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C73" s="9">
         <v>9100</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D73" s="9">
         <v>10500</v>
       </c>
     </row>
-    <row r="74" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B74" s="15" t="s">
+    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C75" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D75" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E75" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F75" s="16" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B75" s="6">
-        <v>80</v>
-      </c>
-      <c r="C75" s="6">
-        <v>130</v>
-      </c>
-      <c r="D75" s="6">
-        <v>180</v>
-      </c>
-      <c r="E75" s="6">
-        <v>230</v>
-      </c>
-      <c r="F75" s="6">
-        <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,19 +2244,19 @@
         <v>123</v>
       </c>
       <c r="B76" s="6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C76" s="6">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="D76" s="6">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E76" s="6">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="F76" s="6">
-        <v>140</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2272,38 +2264,58 @@
         <v>124</v>
       </c>
       <c r="B77" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C77" s="6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D77" s="6">
+        <v>100</v>
+      </c>
+      <c r="E77" s="6">
+        <v>120</v>
+      </c>
+      <c r="F77" s="6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="6">
+        <v>0</v>
+      </c>
+      <c r="C78" s="6">
+        <v>0</v>
+      </c>
+      <c r="D78" s="6">
         <v>20</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E78" s="6">
         <v>50</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F78" s="6">
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A80:G80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -2328,7 +2340,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2337,53 +2349,53 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="19">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2513,32 +2525,32 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="19">
+        <v>129</v>
+      </c>
+      <c r="B12" s="20">
         <f>SUM(B6:B11)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>SUM(C6:C11)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>SUM(D6:D11)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>SUM(E6:E11)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>SUM(F6:F11)</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2548,7 +2560,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" s="12">
         <v>116944</v>
@@ -2568,7 +2580,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" s="12">
         <v>91328</v>
@@ -2588,7 +2600,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" s="12">
         <v>278438</v>
@@ -2608,7 +2620,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="12">
         <v>59029</v>
@@ -2628,7 +2640,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" s="12">
         <v>87955</v>
@@ -2648,7 +2660,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="12">
         <v>69053</v>
@@ -2668,7 +2680,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" s="12">
         <v>77790</v>
@@ -2688,25 +2700,25 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="19">
+        <v>138</v>
+      </c>
+      <c r="B22" s="20">
         <f>SUM(B15:B21)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>SUM(C15:C21)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>SUM(D15:D21)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>SUM(E15:E21)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>SUM(F15:F21)</f>
         <v>936642</v>
       </c>
@@ -2733,7 +2745,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="12">
         <v>65000</v>
@@ -2752,22 +2764,22 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="21">
+      <c r="A27" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="22">
         <v>65000</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="22">
         <v>134000</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="22">
         <v>207000</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="22">
         <v>284000</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="22">
         <v>366000</v>
       </c>
     </row>
@@ -2783,7 +2795,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B29" s="12">
         <v>45000</v>
@@ -2802,22 +2814,22 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B30" s="21">
+      <c r="A30" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="22">
         <v>45000</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="22">
         <v>92800</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="22">
         <v>143400</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="22">
         <v>196800</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="22">
         <v>253500</v>
       </c>
     </row>
@@ -2833,7 +2845,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" s="12">
         <v>220000</v>
@@ -2853,7 +2865,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="12">
         <v>30000</v>
@@ -2873,7 +2885,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B34" s="12">
         <v>18333</v>
@@ -2892,22 +2904,22 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B35" s="21">
+      <c r="A35" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" s="22">
         <v>268333</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="22">
         <v>331660</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="22">
         <v>341614</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <v>351856</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="22">
         <v>362419</v>
       </c>
     </row>
@@ -2923,7 +2935,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="12">
         <v>25000</v>
@@ -2943,7 +2955,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="12">
         <v>10000</v>
@@ -2963,7 +2975,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="12">
         <v>15000</v>
@@ -2983,7 +2995,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="12">
         <v>75000</v>
@@ -3002,53 +3014,53 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B41" s="21">
+      <c r="A41" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="22">
         <v>125000</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <v>216400</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <v>302454</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="22">
         <v>393564</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41" s="22">
         <v>490030</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="19">
+        <v>152</v>
+      </c>
+      <c r="B42" s="20">
         <f>B27+B30+B35+B41</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="20">
         <f>C27+C30+C35+C41</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <f>D27+D30+D35+D41</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <f>E27+E30+E35+E41</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <f>F27+F30+F35+F41</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -3098,32 +3110,32 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B47" s="19">
+        <v>154</v>
+      </c>
+      <c r="B47" s="20">
         <f>SUM(B45:B46)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="20">
         <f>SUM(C45:C46)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="20">
         <f>SUM(D45:D46)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <f>SUM(E45:E46)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <f>SUM(F45:F46)</f>
         <v>56629</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3132,33 +3144,33 @@
       <c r="F49" s="3"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="21">
+      <c r="A50" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B50" s="22">
         <f>B12</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="21">
+      <c r="C50" s="22">
         <f>C12</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="21">
+      <c r="D50" s="22">
         <f>D12</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="22">
         <f>E12</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="21">
+      <c r="F50" s="22">
         <f>F12</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B51" s="12">
         <f>B22</f>
@@ -3183,7 +3195,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B52" s="12">
         <f>B42</f>
@@ -3208,7 +3220,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B53" s="12">
         <f>B47</f>
@@ -3232,26 +3244,26 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="21">
+      <c r="A54" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="22">
         <f>B51+B52+B53</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="21">
+      <c r="C54" s="22">
         <f>C51+C52+C53</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="22">
         <f>D51+D52+D53</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="22">
         <f>E51+E52+E53</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="21">
+      <c r="F54" s="22">
         <f>F51+F52+F53</f>
         <v>2465220</v>
       </c>
@@ -3262,58 +3274,58 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B56" s="23">
+      <c r="A56" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B56" s="24">
         <f>B50-B54</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="25">
         <f>C50-C54</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D56" s="25">
         <f>D50-D54</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="24">
+      <c r="E56" s="25">
         <f>E50-E54</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="24">
+      <c r="F56" s="25">
         <f>F50-F54</f>
         <v>3059480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B57" s="25">
+        <v>162</v>
+      </c>
+      <c r="B57" s="26">
         <f>IF(B50=0,"",B56/B50)</f>
         <v>-0.18</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="26">
         <f>IF(C50=0,"",C56/C50)</f>
         <v>0.2</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="26">
         <f>IF(D50=0,"",D56/D50)</f>
         <v>0.39</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="26">
         <f>IF(E50=0,"",E56/E50)</f>
         <v>0.49</v>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="26">
         <f>IF(F50=0,"",F56/F50)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B58" s="12">
         <f>B56</f>
@@ -3338,7 +3350,7 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3347,33 +3359,33 @@
       <c r="F60" s="3"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" s="21">
+      <c r="A61" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="22">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="22">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="21">
+      <c r="D61" s="22">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="21">
+      <c r="E61" s="22">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="21">
+      <c r="F61" s="22">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B62" s="12">
         <f>B53</f>
@@ -3397,26 +3409,26 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B63" s="26">
+      <c r="A63" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" s="27">
         <f>IF(B62=0,"N/A",B61/B62)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="26">
+      <c r="C63" s="27">
         <f>IF(C62=0,"N/A",C61/C62)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="26">
+      <c r="D63" s="27">
         <f>IF(D62=0,"N/A",D61/D62)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="27">
         <f>IF(E62=0,"N/A",E61/E62)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="26">
+      <c r="F63" s="27">
         <f>IF(F62=0,"N/A",F61/F62)</f>
         <v>55.03</v>
       </c>
@@ -3447,108 +3459,108 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B65" s="21">
+      <c r="A65" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B65" s="22">
         <f>B64+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="21">
+      <c r="C65" s="22">
         <f>C64+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="21">
+      <c r="D65" s="22">
         <f>D64+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="21">
+      <c r="E65" s="22">
         <f>E64+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="22">
         <f>F64+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B66" s="27">
+        <v>169</v>
+      </c>
+      <c r="B66" s="28">
         <f>IF(B54=0,"",B65/B54*365)</f>
         <v>-56</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="28">
         <f>IF(C54=0,"",C65/C54*365)</f>
         <v>46</v>
       </c>
-      <c r="D66" s="27">
+      <c r="D66" s="28">
         <f>IF(D54=0,"",D65/D54*365)</f>
         <v>271</v>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="28">
         <f>IF(E54=0,"",E65/E54*365)</f>
         <v>593</v>
       </c>
-      <c r="F66" s="27">
+      <c r="F66" s="28">
         <f>IF(F54=0,"",F65/F54*365)</f>
         <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B67" s="28">
+        <v>170</v>
+      </c>
+      <c r="B67" s="29">
         <f>IF(B54=0,"",B65/(B54/12))</f>
         <v>-1.8</v>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="29">
         <f>IF(C54=0,"",C65/(C54/12))</f>
         <v>1.5</v>
       </c>
-      <c r="D67" s="28">
+      <c r="D67" s="29">
         <f>IF(D54=0,"",D65/(D54/12))</f>
         <v>8.9</v>
       </c>
-      <c r="E67" s="28">
+      <c r="E67" s="29">
         <f>IF(E54=0,"",E65/(E54/12))</f>
         <v>19.5</v>
       </c>
-      <c r="F67" s="28">
+      <c r="F67" s="29">
         <f>IF(F54=0,"",F65/(F54/12))</f>
         <v>32.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B68" s="25">
+        <v>171</v>
+      </c>
+      <c r="B68" s="26">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="26">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="25">
+      <c r="D68" s="26">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="26">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="26">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3558,7 +3570,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B71" s="4" t="str">
         <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
@@ -3583,7 +3595,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B72" s="4" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
@@ -3608,7 +3620,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B73" s="4" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
@@ -3633,7 +3645,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B74" s="4" t="str">
         <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
@@ -3658,7 +3670,7 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3668,7 +3680,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B77" s="12">
         <f>IF(B3=0,"",B12/B3)</f>
@@ -3693,7 +3705,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B78" s="12">
         <f>IF(B3=0,"",B54/B3)</f>
@@ -3718,7 +3730,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B79" s="12">
         <f>B51+B53</f>
@@ -3743,7 +3755,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B80" s="12">
         <f>IF(B3=0,"",B52/B3)</f>
@@ -3768,7 +3780,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B81" s="12">
         <f>IF(B3=0,"",B77-B80)</f>
@@ -3792,39 +3804,39 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="B82" s="30">
+      <c r="A82" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="31">
         <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C82" s="31">
         <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="30">
+      <c r="D82" s="31">
         <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="30">
+      <c r="E82" s="31">
         <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="30">
+      <c r="F82" s="31">
         <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
+      <c r="A84" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3855,7 +3867,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3872,52 +3884,52 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="L2" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="M2" s="16" t="s">
         <v>195</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4205,57 +4217,57 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="19">
+        <v>129</v>
+      </c>
+      <c r="B10" s="20">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="20">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="20">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="20">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="19" t="str">
+      <c r="L10" s="20" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="19" t="str">
+      <c r="M10" s="20" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="20">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
@@ -4267,7 +4279,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4600,57 +4612,57 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="19">
+        <v>138</v>
+      </c>
+      <c r="B20" s="20">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="20">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="20">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="20">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="19" t="str">
+      <c r="L20" s="20" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="19" t="str">
+      <c r="M20" s="20" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="20">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
@@ -4698,7 +4710,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B24" s="12">
         <v>6500</v>
@@ -4742,46 +4754,46 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="22">
         <v>6500</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="22">
         <v>6500</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <v>6500</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="22">
         <v>6500</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="22">
         <v>6500</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="22">
         <v>6500</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="22">
         <v>6500</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="22">
         <v>6500</v>
       </c>
-      <c r="J25" s="21">
+      <c r="J25" s="22">
         <v>6500</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="22">
         <v>6500</v>
       </c>
-      <c r="L25" s="21">
-        <v>0</v>
-      </c>
-      <c r="M25" s="21">
-        <v>0</v>
-      </c>
-      <c r="N25" s="21">
+      <c r="L25" s="22">
+        <v>0</v>
+      </c>
+      <c r="M25" s="22">
+        <v>0</v>
+      </c>
+      <c r="N25" s="22">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
@@ -4806,7 +4818,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="12">
         <v>4500</v>
@@ -4850,46 +4862,46 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="21">
+      <c r="A28" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="22">
         <v>4500</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="22">
         <v>4500</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="22">
         <v>4500</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="22">
         <v>4500</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="22">
         <v>4500</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="22">
         <v>4500</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="22">
         <v>4500</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="22">
         <v>4500</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J28" s="22">
         <v>4500</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="22">
         <v>4500</v>
       </c>
-      <c r="L28" s="21">
-        <v>0</v>
-      </c>
-      <c r="M28" s="21">
-        <v>0</v>
-      </c>
-      <c r="N28" s="21">
+      <c r="L28" s="22">
+        <v>0</v>
+      </c>
+      <c r="M28" s="22">
+        <v>0</v>
+      </c>
+      <c r="N28" s="22">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
@@ -4914,7 +4926,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B30" s="12">
         <v>22000</v>
@@ -4959,7 +4971,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B31" s="12">
         <v>3000</v>
@@ -5004,7 +5016,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="12">
         <v>1833</v>
@@ -5048,46 +5060,46 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="B33" s="21">
+      <c r="A33" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="22">
         <v>26833</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="22">
         <v>26833</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="22">
         <v>26833</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <v>26833</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="22">
         <v>26833</v>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="22">
         <v>26833</v>
       </c>
-      <c r="H33" s="21">
+      <c r="H33" s="22">
         <v>26833</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="22">
         <v>26833</v>
       </c>
-      <c r="J33" s="21">
+      <c r="J33" s="22">
         <v>26833</v>
       </c>
-      <c r="K33" s="21">
+      <c r="K33" s="22">
         <v>26833</v>
       </c>
-      <c r="L33" s="21">
-        <v>0</v>
-      </c>
-      <c r="M33" s="21">
-        <v>0</v>
-      </c>
-      <c r="N33" s="21">
+      <c r="L33" s="22">
+        <v>0</v>
+      </c>
+      <c r="M33" s="22">
+        <v>0</v>
+      </c>
+      <c r="N33" s="22">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
@@ -5112,7 +5124,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" s="12">
         <v>2500</v>
@@ -5157,7 +5169,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B36" s="12">
         <v>1000</v>
@@ -5202,7 +5214,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B37" s="12">
         <v>1500</v>
@@ -5247,7 +5259,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B38" s="12">
         <v>7500</v>
@@ -5291,103 +5303,103 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B39" s="21">
+      <c r="A39" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="22">
         <v>12500</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="22">
         <v>12500</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="22">
         <v>12500</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="22">
         <v>12500</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="22">
         <v>12500</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="22">
         <v>12500</v>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="22">
         <v>12500</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="22">
         <v>12500</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="22">
         <v>12500</v>
       </c>
-      <c r="K39" s="21">
+      <c r="K39" s="22">
         <v>12500</v>
       </c>
-      <c r="L39" s="21">
-        <v>0</v>
-      </c>
-      <c r="M39" s="21">
-        <v>0</v>
-      </c>
-      <c r="N39" s="21">
+      <c r="L39" s="22">
+        <v>0</v>
+      </c>
+      <c r="M39" s="22">
+        <v>0</v>
+      </c>
+      <c r="N39" s="22">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="19">
+        <v>152</v>
+      </c>
+      <c r="B40" s="20">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="20">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="20">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="20">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="20">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="20">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="19">
+      <c r="J40" s="20">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="19" t="str">
+      <c r="L40" s="20" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="19" t="str">
+      <c r="M40" s="20" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="19">
+      <c r="N40" s="20">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
@@ -5398,8 +5410,8 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>205</v>
+      <c r="A42" s="18" t="s">
+        <v>206</v>
       </c>
       <c r="B42" s="12">
         <v>8886</v>
@@ -5449,7 +5461,7 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -5466,179 +5478,179 @@
       <c r="N44" s="3"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B45" s="21">
+      <c r="A45" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" s="22">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="21">
+      <c r="C45" s="22">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="22">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="22">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="22">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="21">
+      <c r="H45" s="22">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="22">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="21">
+      <c r="J45" s="22">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="21">
+      <c r="K45" s="22">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="21">
+      <c r="L45" s="22">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="21">
+      <c r="M45" s="22">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="21">
+      <c r="N45" s="22">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B46" s="21">
+      <c r="A46" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" s="22">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="22">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="22">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="22">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F46" s="22">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="22">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="22">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="22">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="21">
+      <c r="J46" s="22">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="21">
+      <c r="K46" s="22">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="21">
+      <c r="L46" s="22">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="21">
+      <c r="M46" s="22">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="21">
+      <c r="N46" s="22">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B47" s="21">
+      <c r="A47" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="22">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="22">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="22">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="22">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="22">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="22">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="21">
+      <c r="H47" s="22">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="21">
+      <c r="I47" s="22">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="21">
+      <c r="J47" s="22">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="21">
+      <c r="K47" s="22">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="22">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="21">
+      <c r="M47" s="22">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="21">
+      <c r="N47" s="22">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -5653,16 +5665,16 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B51" s="21">
+        <v>211</v>
+      </c>
+      <c r="B51" s="22">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B52" s="12">
         <f>MIN(B47:M47)</f>
@@ -5670,22 +5682,22 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
+      <c r="A54" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -155,7 +155,7 @@
     <t>CSP Startup Grant</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -690,7 +690,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -706,7 +706,7 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -718,7 +718,7 @@
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="213">
   <si>
-    <t>Heritage Academy Charter — Financial Model Assumptions</t>
+    <t>Heritage Academy Charter - Financial Model Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
@@ -404,7 +404,7 @@
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — 5-Year Financial Model</t>
+    <t>Heritage Academy Charter - 5-Year Financial Model</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -575,7 +575,7 @@
     <t>Break-Even Enrollment</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — 2026-27 Pro Forma</t>
+    <t>Heritage Academy Charter - 2026-27 Pro Forma</t>
   </si>
   <si>
     <t>August</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -4,29 +4,104 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Assumptions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="5-Year Model" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Year 1 Pro Forma" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$J80</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'5-Year Model'!$A1:$F84</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'5-Year Model'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Year 1 Pro Forma'!$A1:$N54</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J80</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F84</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="277">
+  <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>5-Year Model: Detailed revenue, expense, and cash projections</t>
+  </si>
+  <si>
+    <t>Pro Forma: Consolidated income statement</t>
+  </si>
+  <si>
+    <t>Actuals vs Projections: Variance tracking</t>
+  </si>
+  <si>
+    <t>Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
   <si>
     <t>Heritage Academy Charter - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,9 +218,6 @@
     <t>Per Student</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Federal Title I</t>
   </si>
   <si>
@@ -660,6 +732,132 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 17% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 66.83x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>33.9 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
   </si>
 </sst>
 </file>
@@ -673,11 +871,27 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -694,12 +908,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -738,8 +947,20 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -753,12 +974,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -804,47 +1035,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,6 +1456,163 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy Charter&amp;R&amp;8&amp;IInstructions</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1197,1118 +1623,1118 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="11">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11">
+        <v>200</v>
+      </c>
+      <c r="D17" s="11">
+        <v>300</v>
+      </c>
+      <c r="E17" s="11">
+        <v>400</v>
+      </c>
+      <c r="F17" s="11">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="12">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>12</v>
+      </c>
+      <c r="G20" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="H20" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="12">
+        <v>750</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>12</v>
+      </c>
+      <c r="G21" s="13">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="12">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>12</v>
+      </c>
+      <c r="G22" s="13">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="12">
+        <v>150000</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>12</v>
+      </c>
+      <c r="G23" s="13">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="12">
+        <v>25000</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>12</v>
+      </c>
+      <c r="G24" s="13">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="12">
+        <v>400</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>12</v>
+      </c>
+      <c r="G25" s="13">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12">
+        <v>105000</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="12">
+        <v>82000</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G30" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="14">
+        <v>5</v>
+      </c>
+      <c r="E31" s="12">
+        <v>50000</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="14">
+        <v>1</v>
+      </c>
+      <c r="E32" s="12">
+        <v>53000</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G32" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="14">
+        <v>3</v>
+      </c>
+      <c r="E33" s="12">
+        <v>28000</v>
+      </c>
+      <c r="F33" s="13">
+        <v>0.18</v>
+      </c>
+      <c r="G33" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="14">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12">
+        <v>62000</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="14">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="E35" s="12">
+        <v>36000</v>
+      </c>
+      <c r="F35" s="13">
+        <v>0.22</v>
+      </c>
+      <c r="G35" s="13">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="12">
+        <v>22000</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="12">
+        <v>22000</v>
+      </c>
+      <c r="E43" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="12">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="13">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="12">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" s="12">
+        <v>650</v>
+      </c>
+      <c r="E46" s="13">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="12">
+        <v>450</v>
+      </c>
+      <c r="E47" s="13">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" s="12">
+        <v>30000</v>
+      </c>
+      <c r="E48" s="13">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="12">
+        <v>12000</v>
+      </c>
+      <c r="E49" s="13">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="12">
+        <v>18000</v>
+      </c>
+      <c r="E50" s="13">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="12">
+        <v>750</v>
+      </c>
+      <c r="E51" s="13">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="15">
+        <v>0</v>
+      </c>
+      <c r="D54" s="12">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="9">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="G54" s="15">
+        <v>46629</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="12">
+        <v>60000</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" s="14">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="13">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="12">
+        <v>8200</v>
+      </c>
+      <c r="C73" s="12">
+        <v>9100</v>
+      </c>
+      <c r="D73" s="12">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="9">
+        <v>80</v>
+      </c>
+      <c r="C76" s="9">
+        <v>130</v>
+      </c>
+      <c r="D76" s="9">
+        <v>180</v>
+      </c>
+      <c r="E76" s="9">
+        <v>230</v>
+      </c>
+      <c r="F76" s="9">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" s="9">
+        <v>40</v>
+      </c>
+      <c r="C77" s="9">
+        <v>70</v>
+      </c>
+      <c r="D77" s="9">
+        <v>100</v>
+      </c>
+      <c r="E77" s="9">
+        <v>120</v>
+      </c>
+      <c r="F77" s="9">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" s="9">
+        <v>0</v>
+      </c>
+      <c r="C78" s="9">
+        <v>0</v>
+      </c>
+      <c r="D78" s="9">
         <v>20</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="8">
-        <v>120</v>
-      </c>
-      <c r="C17" s="8">
-        <v>200</v>
-      </c>
-      <c r="D17" s="8">
-        <v>300</v>
-      </c>
-      <c r="E17" s="8">
-        <v>400</v>
-      </c>
-      <c r="F17" s="8">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="9">
-        <v>8500</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>12</v>
-      </c>
-      <c r="G20" s="10">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="9">
-        <v>750</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="9">
-        <v>1100</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>12</v>
-      </c>
-      <c r="G22" s="10">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="9">
-        <v>150000</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>12</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="9">
-        <v>25000</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>12</v>
-      </c>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="9">
-        <v>400</v>
-      </c>
-      <c r="E25" s="10">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>12</v>
-      </c>
-      <c r="G25" s="10">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="E78" s="9">
         <v>50</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="11">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9">
-        <v>105000</v>
-      </c>
-      <c r="F29" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="11">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9">
-        <v>82000</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="11">
-        <v>5</v>
-      </c>
-      <c r="E31" s="9">
-        <v>50000</v>
-      </c>
-      <c r="F31" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="11">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9">
-        <v>53000</v>
-      </c>
-      <c r="F32" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="11">
-        <v>3</v>
-      </c>
-      <c r="E33" s="9">
-        <v>28000</v>
-      </c>
-      <c r="F33" s="10">
-        <v>0.18</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="11">
-        <v>1</v>
-      </c>
-      <c r="E34" s="9">
-        <v>62000</v>
-      </c>
-      <c r="F34" s="10">
-        <v>0.26</v>
-      </c>
-      <c r="G34" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="11">
-        <v>2</v>
-      </c>
-      <c r="E35" s="9">
-        <v>36000</v>
-      </c>
-      <c r="F35" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="9">
-        <v>22000</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" s="9">
-        <v>22000</v>
-      </c>
-      <c r="E43" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="9">
-        <v>22000</v>
-      </c>
-      <c r="E45" s="10">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="9">
-        <v>650</v>
-      </c>
-      <c r="E46" s="10">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="9">
-        <v>450</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="9">
-        <v>12000</v>
-      </c>
-      <c r="E49" s="10">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="9">
-        <v>18000</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="9">
-        <v>750</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="12">
-        <v>0</v>
-      </c>
-      <c r="D54" s="9">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="13">
-        <v>0.06</v>
-      </c>
-      <c r="F54" s="6">
-        <v>10</v>
-      </c>
-      <c r="G54" s="12">
-        <v>46629</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="F78" s="9">
         <v>100</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C55" s="9">
-        <v>60000</v>
-      </c>
-      <c r="D55" s="4">
-        <v>0</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B58" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" s="11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="10">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B62" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B63" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B68" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B70" s="15">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B73" s="9">
-        <v>8200</v>
-      </c>
-      <c r="C73" s="9">
-        <v>9100</v>
-      </c>
-      <c r="D73" s="9">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B76" s="6">
-        <v>80</v>
-      </c>
-      <c r="C76" s="6">
-        <v>130</v>
-      </c>
-      <c r="D76" s="6">
-        <v>180</v>
-      </c>
-      <c r="E76" s="6">
-        <v>230</v>
-      </c>
-      <c r="F76" s="6">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B77" s="6">
-        <v>40</v>
-      </c>
-      <c r="C77" s="6">
-        <v>70</v>
-      </c>
-      <c r="D77" s="6">
-        <v>100</v>
-      </c>
-      <c r="E77" s="6">
-        <v>120</v>
-      </c>
-      <c r="F77" s="6">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B78" s="6">
-        <v>0</v>
-      </c>
-      <c r="C78" s="6">
-        <v>0</v>
-      </c>
-      <c r="D78" s="6">
-        <v>20</v>
-      </c>
-      <c r="E78" s="6">
-        <v>50</v>
-      </c>
-      <c r="F78" s="6">
-        <v>100</v>
-      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
+      <c r="A80" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2326,7 +2752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2339,1504 +2765,1504 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>27</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="19">
+      <c r="A3" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="22">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="22">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="22">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="22">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="22">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="15">
         <v>807500</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>1617850</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>2466200</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>3327850</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>4233200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="15">
         <v>75000</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>153000</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>234000</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>318400</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>406000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="15">
         <v>110000</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>224400</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <v>343200</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <v>466800</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>595500</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="15">
         <v>125000</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>100000</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>50000</v>
       </c>
-      <c r="E9" s="12">
-        <v>0</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="E9" s="15">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="15">
         <v>20833</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="15">
         <v>35000</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="15">
         <v>45000</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="15">
         <v>55000</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="15">
         <v>65000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="15">
         <v>40000</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="15">
         <v>82400</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="15">
         <v>127200</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="15">
         <v>174800</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <v>225000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="23">
         <f>SUM(B6:B11)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="23">
         <f>SUM(C6:C11)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="23">
         <f>SUM(D6:D11)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="23">
         <f>SUM(E6:E11)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="23">
         <f>SUM(F6:F11)</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="15">
         <v>116944</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>140333</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <v>140333</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>140333</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <v>140333</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="15">
         <v>91328</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>109593</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <v>109593</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>109593</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="15">
         <v>109593</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="A17" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="15">
         <v>278438</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="15">
         <v>334125</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="15">
         <v>334125</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="15">
         <v>334125</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="15">
         <v>334125</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="15">
         <v>59029</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="15">
         <v>70835</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="15">
         <v>70835</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="15">
         <v>70835</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="15">
         <v>70835</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="15">
         <v>87955</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>105546</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>105546</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>105546</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>105546</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="15">
         <v>69053</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="15">
         <v>82863</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="15">
         <v>82863</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="15">
         <v>82863</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="15">
         <v>82863</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="12">
+      <c r="A21" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="15">
         <v>77790</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>93348</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <v>93348</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>93348</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <v>93348</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="20">
+      <c r="A22" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="23">
         <f>SUM(B15:B21)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="23">
         <f>SUM(C15:C21)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="23">
         <f>SUM(D15:D21)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="23">
         <f>SUM(E15:E21)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="23">
         <f>SUM(F15:F21)</f>
         <v>936642</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="A24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="A25" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="12">
+      <c r="A26" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="15">
         <v>65000</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="15">
         <v>134000</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="15">
         <v>207000</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="15">
         <v>284000</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="15">
         <v>366000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B27" s="22">
+      <c r="A27" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" s="25">
         <v>65000</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="25">
         <v>134000</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="25">
         <v>207000</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="25">
         <v>284000</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="25">
         <v>366000</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="A28" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29" s="12">
+      <c r="A29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="15">
         <v>45000</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="15">
         <v>92800</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="15">
         <v>143400</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="15">
         <v>196800</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="15">
         <v>253500</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B30" s="22">
+      <c r="A30" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="25">
         <v>45000</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="25">
         <v>92800</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="25">
         <v>143400</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="25">
         <v>196800</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="25">
         <v>253500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="A31" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B32" s="12">
+      <c r="A32" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" s="15">
         <v>220000</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="15">
         <v>271920</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="15">
         <v>280078</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="15">
         <v>288480</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="15">
         <v>297134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B33" s="12">
+      <c r="A33" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="15">
         <v>30000</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="15">
         <v>37080</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="15">
         <v>38196</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="15">
         <v>39336</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="15">
         <v>40524</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B34" s="12">
+      <c r="A34" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" s="15">
         <v>18333</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="15">
         <v>22660</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="15">
         <v>23340</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="15">
         <v>24040</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="15">
         <v>24761</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="22">
+      <c r="A35" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="25">
         <v>268333</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="25">
         <v>331660</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="25">
         <v>341614</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="25">
         <v>351856</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="25">
         <v>362419</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="A36" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="12">
+      <c r="A37" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B37" s="15">
         <v>25000</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="15">
         <v>30900</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="15">
         <v>31827</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="15">
         <v>32782</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="15">
         <v>33765</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="12">
+      <c r="A38" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="15">
         <v>10000</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="15">
         <v>12360</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="15">
         <v>12731</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="15">
         <v>13113</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="15">
         <v>13506</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B39" s="12">
+      <c r="A39" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="15">
         <v>15000</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="15">
         <v>18540</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="15">
         <v>19096</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="15">
         <v>19669</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="15">
         <v>20259</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="12">
+      <c r="A40" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" s="15">
         <v>75000</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="15">
         <v>154600</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="15">
         <v>238800</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="15">
         <v>328000</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="15">
         <v>422500</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="22">
+      <c r="A41" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="25">
         <v>125000</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="25">
         <v>216400</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="25">
         <v>302454</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="25">
         <v>393564</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="25">
         <v>490030</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B42" s="23">
         <f>B27+B30+B35+B41</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="23">
         <f>C27+C30+C35+C41</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="23">
         <f>D27+D30+D35+D41</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="23">
         <f>E27+E30+E35+E41</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="23">
         <f>F27+F30+F35+F41</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="A44" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="12">
+      <c r="A45" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="15">
         <v>46629</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="15">
         <v>46629</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="15">
         <v>46629</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="15">
         <v>46629</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="15">
         <v>46629</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="12">
+      <c r="A46" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="15">
         <v>60000</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="15">
         <v>20000</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="15">
         <v>25000</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="15">
         <v>10000</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B47" s="20">
+      <c r="A47" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" s="23">
         <f>SUM(B45:B46)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="20">
+      <c r="C47" s="23">
         <f>SUM(C45:C46)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="23">
         <f>SUM(D45:D46)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="23">
         <f>SUM(E45:E46)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="23">
         <f>SUM(F45:F46)</f>
         <v>56629</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="A49" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="22">
+      <c r="A50" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" s="25">
         <f>B12</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="25">
         <f>C12</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="25">
         <f>D12</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="25">
         <f>E12</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="25">
         <f>F12</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B51" s="12">
+      <c r="A51" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="15">
         <f>B22</f>
         <v>780535</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="15">
         <f>C22</f>
         <v>936642</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="15">
         <f>D22</f>
         <v>936642</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="15">
         <f>E22</f>
         <v>936642</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="15">
         <f>F22</f>
         <v>936642</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" s="12">
+      <c r="A52" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="15">
         <f>B42</f>
         <v>503333</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="15">
         <f>C42</f>
         <v>774860</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="15">
         <f>D42</f>
         <v>994468</v>
       </c>
-      <c r="E52" s="12">
+      <c r="E52" s="15">
         <f>E42</f>
         <v>1226220</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="15">
         <f>F42</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" s="12">
+      <c r="A53" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B53" s="15">
         <f>B47</f>
         <v>106629</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="15">
         <f>C47</f>
         <v>66629</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="15">
         <f>D47</f>
         <v>71629</v>
       </c>
-      <c r="E53" s="12">
+      <c r="E53" s="15">
         <f>E47</f>
         <v>56629</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="15">
         <f>F47</f>
         <v>56629</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B54" s="22">
+      <c r="A54" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="25">
         <f>B51+B52+B53</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="25">
         <f>C51+C52+C53</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="25">
         <f>D51+D52+D53</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="25">
         <f>E51+E52+E53</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="25">
         <f>F51+F52+F53</f>
         <v>2465220</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="B56" s="24">
+      <c r="A56" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56" s="27">
         <f>B50-B54</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="28">
         <f>C50-C54</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="25">
+      <c r="D56" s="28">
         <f>D50-D54</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="28">
         <f>E50-E54</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="28">
         <f>F50-F54</f>
         <v>3059480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B57" s="26">
+      <c r="A57" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="29">
         <f>IF(B50=0,"",B56/B50)</f>
         <v>-0.18</v>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="29">
         <f>IF(C50=0,"",C56/C50)</f>
         <v>0.2</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="29">
         <f>IF(D50=0,"",D56/D50)</f>
         <v>0.39</v>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="29">
         <f>IF(E50=0,"",E56/E50)</f>
         <v>0.49</v>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="29">
         <f>IF(F50=0,"",F56/F50)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" s="12">
+      <c r="A58" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="15">
         <f>B56</f>
         <v>-212164</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="15">
         <f>B58+C56</f>
         <v>222355</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="15">
         <f>C58+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E58" s="12">
+      <c r="E58" s="15">
         <f>D58+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="15">
         <f>E58+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="A60" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B61" s="22">
+      <c r="A61" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="25">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="25">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="25">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="25">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="25">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B62" s="12">
+      <c r="A62" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B62" s="15">
         <f>B53</f>
         <v>106629</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="15">
         <f>C53</f>
         <v>66629</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="15">
         <f>D53</f>
         <v>71629</v>
       </c>
-      <c r="E62" s="12">
+      <c r="E62" s="15">
         <f>E53</f>
         <v>56629</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="15">
         <f>F53</f>
         <v>56629</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B63" s="27">
+      <c r="A63" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="30">
         <f>IF(B62=0,"N/A",B61/B62)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="30">
         <f>IF(C62=0,"N/A",C61/C62)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="27">
+      <c r="D63" s="30">
         <f>IF(D62=0,"N/A",D61/D62)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="27">
+      <c r="E63" s="30">
         <f>IF(E62=0,"N/A",E61/E62)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="27">
+      <c r="F63" s="30">
         <f>IF(F62=0,"N/A",F61/F62)</f>
         <v>55.03</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="12" t="str">
+      <c r="A64" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="15" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="15">
         <f>B65</f>
         <v>-212164</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="15">
         <f>C65</f>
         <v>222355</v>
       </c>
-      <c r="E64" s="12">
+      <c r="E64" s="15">
         <f>D65</f>
         <v>1485216</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="15">
         <f>E65</f>
         <v>3608575</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="B65" s="22">
+      <c r="A65" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" s="25">
         <f>B64+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="25">
         <f>C64+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="22">
+      <c r="D65" s="25">
         <f>D64+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="22">
+      <c r="E65" s="25">
         <f>E64+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="22">
+      <c r="F65" s="25">
         <f>F64+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B66" s="28">
+      <c r="A66" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B66" s="31">
         <f>IF(B54=0,"",B65/B54*365)</f>
         <v>-56</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="31">
         <f>IF(C54=0,"",C65/C54*365)</f>
         <v>46</v>
       </c>
-      <c r="D66" s="28">
+      <c r="D66" s="31">
         <f>IF(D54=0,"",D65/D54*365)</f>
         <v>271</v>
       </c>
-      <c r="E66" s="28">
+      <c r="E66" s="31">
         <f>IF(E54=0,"",E65/E54*365)</f>
         <v>593</v>
       </c>
-      <c r="F66" s="28">
+      <c r="F66" s="31">
         <f>IF(F54=0,"",F65/F54*365)</f>
         <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B67" s="29">
+      <c r="A67" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B67" s="32">
         <f>IF(B54=0,"",B65/(B54/12))</f>
         <v>-1.8</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="32">
         <f>IF(C54=0,"",C65/(C54/12))</f>
         <v>1.5</v>
       </c>
-      <c r="D67" s="29">
+      <c r="D67" s="32">
         <f>IF(D54=0,"",D65/(D54/12))</f>
         <v>8.9</v>
       </c>
-      <c r="E67" s="29">
+      <c r="E67" s="32">
         <f>IF(E54=0,"",E65/(E54/12))</f>
         <v>19.5</v>
       </c>
-      <c r="F67" s="29">
+      <c r="F67" s="32">
         <f>IF(F54=0,"",F65/(F54/12))</f>
         <v>32.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B68" s="26">
+      <c r="A68" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="29">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="26">
+      <c r="C68" s="29">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="26">
+      <c r="D68" s="29">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="29">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="29">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
+      <c r="A70" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" s="4" t="str">
+      <c r="A71" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B71" s="7" t="str">
         <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C71" s="4" t="str">
+      <c r="C71" s="7" t="str">
         <f>IF(C62=0,"N/A",IF(C63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D71" s="4" t="str">
+      <c r="D71" s="7" t="str">
         <f>IF(D62=0,"N/A",IF(D63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E71" s="4" t="str">
+      <c r="E71" s="7" t="str">
         <f>IF(E62=0,"N/A",IF(E63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F71" s="4" t="str">
+      <c r="F71" s="7" t="str">
         <f>IF(F62=0,"N/A",IF(F63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B72" s="4" t="str">
+      <c r="A72" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" s="7" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C72" s="4" t="str">
+      <c r="C72" s="7" t="str">
         <f>IF(C56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D72" s="4" t="str">
+      <c r="D72" s="7" t="str">
         <f>IF(D56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E72" s="4" t="str">
+      <c r="E72" s="7" t="str">
         <f>IF(E56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F72" s="4" t="str">
+      <c r="F72" s="7" t="str">
         <f>IF(F56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="4" t="str">
+      <c r="A73" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C73" s="4" t="str">
+      <c r="C73" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D73" s="4" t="str">
+      <c r="D73" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E73" s="4" t="str">
+      <c r="E73" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="F73" s="4" t="str">
+      <c r="F73" s="7" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B74" s="4" t="str">
+      <c r="A74" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" s="7" t="str">
         <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C74" s="4" t="str">
+      <c r="C74" s="7" t="str">
         <f>IF(C54=0,"N/A",IF(C65/(C54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D74" s="4" t="str">
+      <c r="D74" s="7" t="str">
         <f>IF(D54=0,"N/A",IF(D65/(D54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E74" s="4" t="str">
+      <c r="E74" s="7" t="str">
         <f>IF(E54=0,"N/A",IF(E65/(E54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F74" s="4" t="str">
+      <c r="F74" s="7" t="str">
         <f>IF(F54=0,"N/A",IF(F65/(F54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
+      <c r="A76" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B77" s="12">
+      <c r="A77" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" s="15">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>9819</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="15">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>11063</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="15">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>10885</v>
       </c>
-      <c r="E77" s="12">
+      <c r="E77" s="15">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>10857</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="15">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>11049</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B78" s="12">
+      <c r="A78" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" s="15">
         <f>IF(B3=0,"",B54/B3)</f>
         <v>11587</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="15">
         <f>IF(C3=0,"",C54/C3)</f>
         <v>8891</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="15">
         <f>IF(D3=0,"",D54/D3)</f>
         <v>6676</v>
       </c>
-      <c r="E78" s="12">
+      <c r="E78" s="15">
         <f>IF(E3=0,"",E54/E3)</f>
         <v>5549</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="15">
         <f>IF(F3=0,"",F54/F3)</f>
         <v>4930</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B79" s="12">
+      <c r="A79" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B79" s="15">
         <f>B51+B53</f>
         <v>887164</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="15">
         <f>C51+C53</f>
         <v>1003271</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="15">
         <f>D51+D53</f>
         <v>1008271</v>
       </c>
-      <c r="E79" s="12">
+      <c r="E79" s="15">
         <f>E51+E53</f>
         <v>993271</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="15">
         <f>F51+F53</f>
         <v>993271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B80" s="12">
+      <c r="A80" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B80" s="15">
         <f>IF(B3=0,"",B52/B3)</f>
         <v>4194</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="15">
         <f>IF(C3=0,"",C52/C3)</f>
         <v>3874</v>
       </c>
-      <c r="D80" s="12">
+      <c r="D80" s="15">
         <f>IF(D3=0,"",D52/D3)</f>
         <v>3315</v>
       </c>
-      <c r="E80" s="12">
+      <c r="E80" s="15">
         <f>IF(E3=0,"",E52/E3)</f>
         <v>3066</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="15">
         <f>IF(F3=0,"",F52/F3)</f>
         <v>2944</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B81" s="12">
+      <c r="A81" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B81" s="15">
         <f>IF(B3=0,"",B77-B80)</f>
         <v>5625</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="15">
         <f>IF(C3=0,"",C77-C80)</f>
         <v>7189</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="15">
         <f>IF(D3=0,"",D77-D80)</f>
         <v>7570</v>
       </c>
-      <c r="E81" s="12">
+      <c r="E81" s="15">
         <f>IF(E3=0,"",E77-E80)</f>
         <v>7792</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="15">
         <f>IF(F3=0,"",F77-F80)</f>
         <v>8106</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B82" s="31">
+      <c r="A82" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" s="34">
         <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="34">
         <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="31">
+      <c r="D82" s="34">
         <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="31">
+      <c r="E82" s="34">
         <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="31">
+      <c r="F82" s="34">
         <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
+      <c r="A84" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3852,7 +4278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3866,1838 +4292,1838 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>196</v>
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="A3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="15">
         <v>96900</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="15">
         <v>96900</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="15">
         <v>96900</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="15">
         <v>96900</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>96900</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>96900</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="15">
         <v>96900</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="15">
         <v>96900</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="15">
         <v>96900</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="15">
         <v>96900</v>
       </c>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
-        <v>0</v>
-      </c>
-      <c r="N4" s="12">
+      <c r="L4" s="15">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0</v>
+      </c>
+      <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
         <v>807500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="12">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="15">
         <v>9000</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>9000</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="15">
         <v>9000</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="15">
         <v>9000</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="15">
         <v>9000</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>9000</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="15">
         <v>9000</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="15">
         <v>9000</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="15">
         <v>9000</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="15">
         <v>9000</v>
       </c>
-      <c r="L5" s="12">
-        <v>0</v>
-      </c>
-      <c r="M5" s="12">
-        <v>0</v>
-      </c>
-      <c r="N5" s="12">
+      <c r="L5" s="15">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="A6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="15">
         <v>13200</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>13200</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="15">
         <v>13200</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <v>13200</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>13200</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>13200</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="15">
         <v>13200</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="15">
         <v>13200</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="15">
         <v>13200</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="15">
         <v>13200</v>
       </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
         <f>SUM(B6:M6)</f>
         <v>110000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="A7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="15">
         <v>15000</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>15000</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="15">
         <v>15000</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <v>15000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>15000</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>15000</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="15">
         <v>15000</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="15">
         <v>15000</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="15">
         <v>15000</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="15">
         <v>15000</v>
       </c>
-      <c r="L7" s="12">
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+      <c r="L7" s="15">
+        <v>0</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
         <f>SUM(B7:M7)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="15">
         <v>2500</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>2500</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="15">
         <v>2500</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <v>2500</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>2500</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <v>2500</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="15">
         <v>2500</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="15">
         <v>2500</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="15">
         <v>2500</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="15">
         <v>2500</v>
       </c>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12">
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
         <f>SUM(B8:M8)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="15">
         <v>4800</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>4800</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="15">
         <v>4800</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="15">
         <v>4800</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="15">
         <v>4800</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="15">
         <v>4800</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="15">
         <v>4800</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="15">
         <v>4800</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="15">
         <v>4800</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="15">
         <v>4800</v>
       </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
-      <c r="M9" s="12">
-        <v>0</v>
-      </c>
-      <c r="N9" s="12">
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
         <f>SUM(B9:M9)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="23">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="23">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="23">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="23">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="23">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="23">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="23">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="23">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="23">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="23">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="20" t="str">
+      <c r="L10" s="23" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="20" t="str">
+      <c r="M10" s="23" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="23">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="A12" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="15">
         <v>11694</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="15">
         <v>11694</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="15">
         <v>11694</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <v>11694</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="15">
         <v>11694</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="15">
         <v>11694</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="15">
         <v>11694</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="15">
         <v>11694</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="15">
         <v>11694</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="15">
         <v>11694</v>
       </c>
-      <c r="L13" s="12">
-        <v>0</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0</v>
-      </c>
-      <c r="N13" s="12">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
         <f>SUM(B13:M13)</f>
         <v>116944</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="A14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="15">
         <v>9133</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="15">
         <v>9133</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="15">
         <v>9133</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="15">
         <v>9133</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="15">
         <v>9133</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="15">
         <v>9133</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="15">
         <v>9133</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="15">
         <v>9133</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="15">
         <v>9133</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="15">
         <v>9133</v>
       </c>
-      <c r="L14" s="12">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
         <f>SUM(B14:M14)</f>
         <v>91328</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="15">
         <v>27844</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>27844</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="15">
         <v>27844</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>27844</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="15">
         <v>27844</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="15">
         <v>27844</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="15">
         <v>27844</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="15">
         <v>27844</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="15">
         <v>27844</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="15">
         <v>27844</v>
       </c>
-      <c r="L15" s="12">
-        <v>0</v>
-      </c>
-      <c r="M15" s="12">
-        <v>0</v>
-      </c>
-      <c r="N15" s="12">
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="15">
         <f>SUM(B15:M15)</f>
         <v>278438</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="A16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="15">
         <v>5903</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>5903</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="15">
         <v>5903</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>5903</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="15">
         <v>5903</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="15">
         <v>5903</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="15">
         <v>5903</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="15">
         <v>5903</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="15">
         <v>5903</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="15">
         <v>5903</v>
       </c>
-      <c r="L16" s="12">
-        <v>0</v>
-      </c>
-      <c r="M16" s="12">
-        <v>0</v>
-      </c>
-      <c r="N16" s="12">
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>0</v>
+      </c>
+      <c r="N16" s="15">
         <f>SUM(B16:M16)</f>
         <v>59029</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="A17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="15">
         <v>8796</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="15">
         <v>8796</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="15">
         <v>8796</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="15">
         <v>8796</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="15">
         <v>8796</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="15">
         <v>8796</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="15">
         <v>8796</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="15">
         <v>8796</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="15">
         <v>8796</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="15">
         <v>8796</v>
       </c>
-      <c r="L17" s="12">
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
-        <v>0</v>
-      </c>
-      <c r="N17" s="12">
+      <c r="L17" s="15">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15">
+        <v>0</v>
+      </c>
+      <c r="N17" s="15">
         <f>SUM(B17:M17)</f>
         <v>87955</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="15">
         <v>6905</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="15">
         <v>6905</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="15">
         <v>6905</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="15">
         <v>6905</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="15">
         <v>6905</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="15">
         <v>6905</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="15">
         <v>6905</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="15">
         <v>6905</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="15">
         <v>6905</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="15">
         <v>6905</v>
       </c>
-      <c r="L18" s="12">
-        <v>0</v>
-      </c>
-      <c r="M18" s="12">
-        <v>0</v>
-      </c>
-      <c r="N18" s="12">
+      <c r="L18" s="15">
+        <v>0</v>
+      </c>
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15">
         <f>SUM(B18:M18)</f>
         <v>69053</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="15">
         <v>7779</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>7779</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>7779</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>7779</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>7779</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="15">
         <v>7779</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="15">
         <v>7779</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="15">
         <v>7779</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="15">
         <v>7779</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="15">
         <v>7779</v>
       </c>
-      <c r="L19" s="12">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12">
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15">
         <f>SUM(B19:M19)</f>
         <v>77790</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="23">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="23">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="23">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="23">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="23">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="23">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="23">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="23">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="23">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="23">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="20" t="str">
+      <c r="L20" s="23" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="20" t="str">
+      <c r="M20" s="23" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="23">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="A22" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
+      <c r="A23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B24" s="12">
+      <c r="A24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="15">
         <v>6500</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="15">
         <v>6500</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="15">
         <v>6500</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <v>6500</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="15">
         <v>6500</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="15">
         <v>6500</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="15">
         <v>6500</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="15">
         <v>6500</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="15">
         <v>6500</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="15">
         <v>6500</v>
       </c>
-      <c r="L24" s="12">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12">
+      <c r="L24" s="15">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0</v>
+      </c>
+      <c r="N24" s="15">
         <f>SUM(B24:M24)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" s="22">
+      <c r="A25" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="25">
         <v>6500</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="25">
         <v>6500</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="25">
         <v>6500</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="25">
         <v>6500</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="25">
         <v>6500</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="25">
         <v>6500</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="25">
         <v>6500</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="25">
         <v>6500</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="25">
         <v>6500</v>
       </c>
-      <c r="K25" s="22">
+      <c r="K25" s="25">
         <v>6500</v>
       </c>
-      <c r="L25" s="22">
-        <v>0</v>
-      </c>
-      <c r="M25" s="22">
-        <v>0</v>
-      </c>
-      <c r="N25" s="22">
+      <c r="L25" s="25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="25">
+        <v>0</v>
+      </c>
+      <c r="N25" s="25">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="A26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" s="12">
+      <c r="A27" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="15">
         <v>4500</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="15">
         <v>4500</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="15">
         <v>4500</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="15">
         <v>4500</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="15">
         <v>4500</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="15">
         <v>4500</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="15">
         <v>4500</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="15">
         <v>4500</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="15">
         <v>4500</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="15">
         <v>4500</v>
       </c>
-      <c r="L27" s="12">
-        <v>0</v>
-      </c>
-      <c r="M27" s="12">
-        <v>0</v>
-      </c>
-      <c r="N27" s="12">
+      <c r="L27" s="15">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
         <f>SUM(B27:M27)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B28" s="22">
+      <c r="A28" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="25">
         <v>4500</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="25">
         <v>4500</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="25">
         <v>4500</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="25">
         <v>4500</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="25">
         <v>4500</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="25">
         <v>4500</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="25">
         <v>4500</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="25">
         <v>4500</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28" s="25">
         <v>4500</v>
       </c>
-      <c r="K28" s="22">
+      <c r="K28" s="25">
         <v>4500</v>
       </c>
-      <c r="L28" s="22">
-        <v>0</v>
-      </c>
-      <c r="M28" s="22">
-        <v>0</v>
-      </c>
-      <c r="N28" s="22">
+      <c r="L28" s="25">
+        <v>0</v>
+      </c>
+      <c r="M28" s="25">
+        <v>0</v>
+      </c>
+      <c r="N28" s="25">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="A29" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="12">
+      <c r="A30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="15">
         <v>22000</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="15">
         <v>22000</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="15">
         <v>22000</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="15">
         <v>22000</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="15">
         <v>22000</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="15">
         <v>22000</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="15">
         <v>22000</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="15">
         <v>22000</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="15">
         <v>22000</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="15">
         <v>22000</v>
       </c>
-      <c r="L30" s="12">
-        <v>0</v>
-      </c>
-      <c r="M30" s="12">
-        <v>0</v>
-      </c>
-      <c r="N30" s="12">
+      <c r="L30" s="15">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
         <f>SUM(B30:M30)</f>
         <v>220000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B31" s="12">
+      <c r="A31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="15">
         <v>3000</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="15">
         <v>3000</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="15">
         <v>3000</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="15">
         <v>3000</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="15">
         <v>3000</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="15">
         <v>3000</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="15">
         <v>3000</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="15">
         <v>3000</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="15">
         <v>3000</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="15">
         <v>3000</v>
       </c>
-      <c r="L31" s="12">
-        <v>0</v>
-      </c>
-      <c r="M31" s="12">
-        <v>0</v>
-      </c>
-      <c r="N31" s="12">
+      <c r="L31" s="15">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0</v>
+      </c>
+      <c r="N31" s="15">
         <f>SUM(B31:M31)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B32" s="12">
+      <c r="A32" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="15">
         <v>1833</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="15">
         <v>1833</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="15">
         <v>1833</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="15">
         <v>1833</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="15">
         <v>1833</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="15">
         <v>1833</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="15">
         <v>1833</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="15">
         <v>1833</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="15">
         <v>1833</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="15">
         <v>1833</v>
       </c>
-      <c r="L32" s="12">
-        <v>0</v>
-      </c>
-      <c r="M32" s="12">
-        <v>0</v>
-      </c>
-      <c r="N32" s="12">
+      <c r="L32" s="15">
+        <v>0</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0</v>
+      </c>
+      <c r="N32" s="15">
         <f>SUM(B32:M32)</f>
         <v>18333</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="22">
+      <c r="A33" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B33" s="25">
         <v>26833</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="25">
         <v>26833</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="25">
         <v>26833</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="25">
         <v>26833</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="25">
         <v>26833</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="25">
         <v>26833</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="25">
         <v>26833</v>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="25">
         <v>26833</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33" s="25">
         <v>26833</v>
       </c>
-      <c r="K33" s="22">
+      <c r="K33" s="25">
         <v>26833</v>
       </c>
-      <c r="L33" s="22">
-        <v>0</v>
-      </c>
-      <c r="M33" s="22">
-        <v>0</v>
-      </c>
-      <c r="N33" s="22">
+      <c r="L33" s="25">
+        <v>0</v>
+      </c>
+      <c r="M33" s="25">
+        <v>0</v>
+      </c>
+      <c r="N33" s="25">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
+      <c r="A34" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B35" s="12">
+      <c r="A35" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="15">
         <v>2500</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="15">
         <v>2500</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="15">
         <v>2500</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="15">
         <v>2500</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="15">
         <v>2500</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="15">
         <v>2500</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="15">
         <v>2500</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="15">
         <v>2500</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="15">
         <v>2500</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="15">
         <v>2500</v>
       </c>
-      <c r="L35" s="12">
-        <v>0</v>
-      </c>
-      <c r="M35" s="12">
-        <v>0</v>
-      </c>
-      <c r="N35" s="12">
+      <c r="L35" s="15">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15">
+        <v>0</v>
+      </c>
+      <c r="N35" s="15">
         <f>SUM(B35:M35)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B36" s="12">
+      <c r="A36" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="15">
         <v>1000</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="15">
         <v>1000</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="15">
         <v>1000</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="15">
         <v>1000</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="15">
         <v>1000</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="15">
         <v>1000</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="15">
         <v>1000</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="15">
         <v>1000</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="15">
         <v>1000</v>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="15">
         <v>1000</v>
       </c>
-      <c r="L36" s="12">
-        <v>0</v>
-      </c>
-      <c r="M36" s="12">
-        <v>0</v>
-      </c>
-      <c r="N36" s="12">
+      <c r="L36" s="15">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15">
+        <v>0</v>
+      </c>
+      <c r="N36" s="15">
         <f>SUM(B36:M36)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B37" s="12">
+      <c r="A37" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="15">
         <v>1500</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="15">
         <v>1500</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="15">
         <v>1500</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="15">
         <v>1500</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="15">
         <v>1500</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="15">
         <v>1500</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="15">
         <v>1500</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="15">
         <v>1500</v>
       </c>
-      <c r="J37" s="12">
+      <c r="J37" s="15">
         <v>1500</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="15">
         <v>1500</v>
       </c>
-      <c r="L37" s="12">
-        <v>0</v>
-      </c>
-      <c r="M37" s="12">
-        <v>0</v>
-      </c>
-      <c r="N37" s="12">
+      <c r="L37" s="15">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15">
+        <v>0</v>
+      </c>
+      <c r="N37" s="15">
         <f>SUM(B37:M37)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B38" s="12">
+      <c r="A38" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="15">
         <v>7500</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="15">
         <v>7500</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="15">
         <v>7500</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="15">
         <v>7500</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="15">
         <v>7500</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="15">
         <v>7500</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="15">
         <v>7500</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="15">
         <v>7500</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="15">
         <v>7500</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="15">
         <v>7500</v>
       </c>
-      <c r="L38" s="12">
-        <v>0</v>
-      </c>
-      <c r="M38" s="12">
-        <v>0</v>
-      </c>
-      <c r="N38" s="12">
+      <c r="L38" s="15">
+        <v>0</v>
+      </c>
+      <c r="M38" s="15">
+        <v>0</v>
+      </c>
+      <c r="N38" s="15">
         <f>SUM(B38:M38)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" s="22">
+      <c r="A39" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="25">
         <v>12500</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="25">
         <v>12500</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="25">
         <v>12500</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="25">
         <v>12500</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="25">
         <v>12500</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="25">
         <v>12500</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="25">
         <v>12500</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="25">
         <v>12500</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="25">
         <v>12500</v>
       </c>
-      <c r="K39" s="22">
+      <c r="K39" s="25">
         <v>12500</v>
       </c>
-      <c r="L39" s="22">
-        <v>0</v>
-      </c>
-      <c r="M39" s="22">
-        <v>0</v>
-      </c>
-      <c r="N39" s="22">
+      <c r="L39" s="25">
+        <v>0</v>
+      </c>
+      <c r="M39" s="25">
+        <v>0</v>
+      </c>
+      <c r="N39" s="25">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B40" s="20">
+      <c r="A40" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="23">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="23">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="23">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="23">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="23">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="23">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="23">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="20">
+      <c r="I40" s="23">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="20">
+      <c r="J40" s="23">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="20">
+      <c r="K40" s="23">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="20" t="str">
+      <c r="L40" s="23" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="20" t="str">
+      <c r="M40" s="23" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="20">
+      <c r="N40" s="23">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B42" s="12">
+      <c r="A42" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" s="15">
         <v>8886</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="15">
         <v>8886</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="15">
         <v>8886</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="15">
         <v>8886</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="15">
         <v>8886</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="15">
         <v>8886</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="15">
         <v>8886</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="15">
         <v>8886</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="15">
         <v>8886</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="15">
         <v>8886</v>
       </c>
-      <c r="L42" s="12">
+      <c r="L42" s="15">
         <v>8886</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M42" s="15">
         <v>8886</v>
       </c>
-      <c r="N42" s="12">
+      <c r="N42" s="15">
         <f>SUM(B42:M42)</f>
         <v>106629</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
+      <c r="A44" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B45" s="22">
+      <c r="A45" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B45" s="25">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="25">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="25">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="25">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="25">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="25">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="25">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="25">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45" s="25">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="25">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="22">
+      <c r="L45" s="25">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="22">
+      <c r="M45" s="25">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="22">
+      <c r="N45" s="25">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B46" s="22">
+      <c r="A46" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="25">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="22">
+      <c r="C46" s="25">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="25">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="25">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="25">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="22">
+      <c r="G46" s="25">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="25">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46" s="25">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46" s="25">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="22">
+      <c r="K46" s="25">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="22">
+      <c r="L46" s="25">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="22">
+      <c r="M46" s="25">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="22">
+      <c r="N46" s="25">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B47" s="22">
+      <c r="A47" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="25">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="25">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="25">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="25">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="25">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="25">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="25">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="25">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="25">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="25">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="22">
+      <c r="L47" s="25">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="22">
+      <c r="M47" s="25">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="22">
+      <c r="N47" s="25">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
+      <c r="A49" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B50" s="12">
+      <c r="A50" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B51" s="22">
+      <c r="A51" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="25">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B52" s="12">
+      <c r="A52" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B52" s="15">
         <f>MIN(B47:M47)</f>
         <v>9227</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
+      <c r="A54" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5711,4 +6137,398 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="36">
+        <v>120</v>
+      </c>
+      <c r="D6" s="36">
+        <v>200</v>
+      </c>
+      <c r="E6" s="36">
+        <v>300</v>
+      </c>
+      <c r="F6" s="36">
+        <v>400</v>
+      </c>
+      <c r="G6" s="36">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="37">
+        <v>1414000</v>
+      </c>
+      <c r="D7" s="37">
+        <v>2212650</v>
+      </c>
+      <c r="E7" s="37">
+        <v>3265600</v>
+      </c>
+      <c r="F7" s="37">
+        <v>4342850</v>
+      </c>
+      <c r="G7" s="37">
+        <v>5524700</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="37">
+        <v>780535</v>
+      </c>
+      <c r="D8" s="37">
+        <v>936642</v>
+      </c>
+      <c r="E8" s="37">
+        <v>936642</v>
+      </c>
+      <c r="F8" s="37">
+        <v>936642</v>
+      </c>
+      <c r="G8" s="37">
+        <v>936642</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="37">
+        <v>604000</v>
+      </c>
+      <c r="D9" s="37">
+        <v>774860</v>
+      </c>
+      <c r="E9" s="37">
+        <v>994467.6</v>
+      </c>
+      <c r="F9" s="37">
+        <v>1226219.9279999998</v>
+      </c>
+      <c r="G9" s="37">
+        <v>1471949.32584</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="37">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="D10" s="37">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="E10" s="37">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="F10" s="37">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="G10" s="37">
+        <v>46628.6108154935</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="38">
+        <v>-17163.6108154935</v>
+      </c>
+      <c r="D11" s="39">
+        <v>454519.3891845065</v>
+      </c>
+      <c r="E11" s="39">
+        <v>1287861.7891845065</v>
+      </c>
+      <c r="F11" s="39">
+        <v>2133359.461184507</v>
+      </c>
+      <c r="G11" s="39">
+        <v>3069480.0633445065</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="38">
+        <v>-17163.6108154935</v>
+      </c>
+      <c r="D12" s="39">
+        <v>437355.778369013</v>
+      </c>
+      <c r="E12" s="39">
+        <v>1725217.5675535195</v>
+      </c>
+      <c r="F12" s="39">
+        <v>3858577.0287380265</v>
+      </c>
+      <c r="G12" s="39">
+        <v>6928057.092082533</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="40">
+        <v>-0.0121383386248186</v>
+      </c>
+      <c r="D13" s="41">
+        <v>0.20541856560436875</v>
+      </c>
+      <c r="E13" s="41">
+        <v>0.39437217944160535</v>
+      </c>
+      <c r="F13" s="41">
+        <v>0.49123489440908774</v>
+      </c>
+      <c r="G13" s="41">
+        <v>0.555592170315946</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="E16" s="44"/>
+      <c r="F16" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G16" s="45"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>257</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="44"/>
+      <c r="F17" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="G17" s="45"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="44"/>
+      <c r="F18" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G18" s="45"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="44"/>
+      <c r="F19" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="G19" s="45"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="G20" s="45"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="G21" s="45"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="G22" s="45"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy Charter&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="285">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -771,6 +771,30 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -960,7 +984,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -990,6 +1014,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1035,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1098,6 +1127,17 @@
     <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6144,7 +6184,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6353,176 +6393,302 @@
         <v>0.555592170315946</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C14" s="37">
+        <v>11783.333333333334</v>
+      </c>
+      <c r="D14" s="37">
+        <v>11063.25</v>
+      </c>
+      <c r="E14" s="37">
+        <v>10885.333333333334</v>
+      </c>
+      <c r="F14" s="37">
+        <v>10857.125</v>
+      </c>
+      <c r="G14" s="37">
+        <v>11049.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="42">
+        <v>0.5520049504950495</v>
+      </c>
+      <c r="D15" s="41">
+        <v>0.4233123178089621</v>
+      </c>
+      <c r="E15" s="41">
+        <v>0.2868207986281235</v>
+      </c>
+      <c r="F15" s="41">
+        <v>0.21567449946463726</v>
+      </c>
+      <c r="G15" s="41">
+        <v>0.16953716943906458</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
+      <c r="C16" s="41">
+        <v>0.12814710042432814</v>
+      </c>
+      <c r="D16" s="41">
+        <v>0.10505864009219713</v>
+      </c>
+      <c r="E16" s="41">
+        <v>0.09135848848603624</v>
+      </c>
+      <c r="F16" s="41">
+        <v>0.08470612118769931</v>
+      </c>
+      <c r="G16" s="41">
+        <v>0.07992919031838833</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="42" t="s">
+      <c r="C17" s="42">
+        <v>0.020838048090523337</v>
+      </c>
+      <c r="D17" s="41">
+        <v>0.22649221521704743</v>
+      </c>
+      <c r="E17" s="41">
+        <v>0.40865090641842233</v>
+      </c>
+      <c r="F17" s="41">
+        <v>0.5019717632430317</v>
+      </c>
+      <c r="G17" s="41">
+        <v>0.5640321961663076</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C18" s="43">
+        <v>0.6319081672107103</v>
+      </c>
+      <c r="D18" s="44">
+        <v>10.747650235238861</v>
+      </c>
+      <c r="E18" s="44">
+        <v>28.61956160951256</v>
+      </c>
+      <c r="F18" s="44">
+        <v>46.752155680255555</v>
+      </c>
+      <c r="G18" s="44">
+        <v>66.82825457722186</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="C19" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="E16" s="44"/>
-      <c r="F16" s="45" t="s">
+      <c r="C20" s="46" t="s">
         <v>255</v>
       </c>
-      <c r="G16" s="45"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="42" t="s">
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C22" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D22" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E17" s="44"/>
-      <c r="F17" s="45" t="s">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G17" s="45"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="C18" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D18" s="44" t="s">
+      <c r="C23" s="48" t="s">
         <v>261</v>
       </c>
-      <c r="E18" s="44"/>
-      <c r="F18" s="45" t="s">
+      <c r="D23" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="G18" s="45"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+      <c r="E23" s="49"/>
+      <c r="F23" s="50" t="s">
         <v>263</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D19" s="44" t="s">
+      <c r="G23" s="50"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="45" t="s">
+      <c r="C24" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="G19" s="45"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="42" t="s">
+      <c r="D24" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D20" s="44" t="s">
+      <c r="E24" s="49"/>
+      <c r="F24" s="50" t="s">
         <v>267</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="45" t="s">
+      <c r="G24" s="50"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="42" t="s">
+      <c r="C25" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="C21" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D21" s="44" t="s">
+      <c r="E25" s="49"/>
+      <c r="F25" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="E21" s="44"/>
-      <c r="F21" s="45" t="s">
+      <c r="G25" s="50"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="G21" s="45"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="42" t="s">
+      <c r="C26" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="C22" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D22" s="44" t="s">
+      <c r="E26" s="49"/>
+      <c r="F26" s="50" t="s">
         <v>273</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="45" t="s">
+      <c r="G26" s="50"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="G22" s="45"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="42" t="s">
+      <c r="C27" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="49" t="s">
         <v>275</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="E27" s="49"/>
+      <c r="F27" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="47" t="s">
+      <c r="G27" s="50"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="49"/>
+      <c r="F28" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="G28" s="50"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" s="50"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
@@ -27,21 +27,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="291">
   <si>
     <t>How to Use This Workbook</t>
   </si>
   <si>
+    <t>Heritage Academy Charter</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+  </si>
+  <si>
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -89,6 +95,21 @@
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
     <t>Disclaimer</t>
   </si>
   <si>
@@ -108,9 +129,6 @@
   </si>
   <si>
     <t>School Name</t>
-  </si>
-  <si>
-    <t>Heritage Academy Charter</t>
   </si>
   <si>
     <t>State</t>
@@ -895,7 +913,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -910,8 +928,24 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -928,11 +962,6 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -993,12 +1022,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF2"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1009,11 +1043,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1064,101 +1093,253 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1494,9 +1675,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1508,134 +1690,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>5</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>8</v>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>13</v>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>14</v>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>5</v>
+      <c r="B22" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>17</v>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>18</v>
+      <c r="B24" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
+      <c r="B26" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>20</v>
+      <c r="B27" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>21</v>
+      <c r="B28" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1663,1118 +1885,1118 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
+      <c r="A2" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>29</v>
+      <c r="A6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>31</v>
+      <c r="A7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>33</v>
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>35</v>
+      <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>39</v>
+      <c r="A11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="13">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="15">
+        <v>120</v>
+      </c>
+      <c r="C17" s="15">
+        <v>200</v>
+      </c>
+      <c r="D17" s="15">
+        <v>300</v>
+      </c>
+      <c r="E17" s="15">
+        <v>400</v>
+      </c>
+      <c r="F17" s="15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="16">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <v>12</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="16">
+        <v>750</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <v>12</v>
+      </c>
+      <c r="G21" s="17">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <v>12</v>
+      </c>
+      <c r="G22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="16">
+        <v>150000</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>12</v>
+      </c>
+      <c r="G23" s="17">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="16">
+        <v>25000</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <v>12</v>
+      </c>
+      <c r="G24" s="17">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="16">
+        <v>400</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <v>12</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="18">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16">
+        <v>105000</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0.26</v>
+      </c>
+      <c r="G29" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="18">
+        <v>1</v>
+      </c>
+      <c r="E30" s="16">
+        <v>82000</v>
+      </c>
+      <c r="F30" s="17">
+        <v>0.26</v>
+      </c>
+      <c r="G30" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="18">
+        <v>5</v>
+      </c>
+      <c r="E31" s="16">
+        <v>50000</v>
+      </c>
+      <c r="F31" s="17">
+        <v>0.26</v>
+      </c>
+      <c r="G31" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="18">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16">
+        <v>53000</v>
+      </c>
+      <c r="F32" s="17">
+        <v>0.26</v>
+      </c>
+      <c r="G32" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="18">
+        <v>3</v>
+      </c>
+      <c r="E33" s="16">
+        <v>28000</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="G33" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="18">
+        <v>1</v>
+      </c>
+      <c r="E34" s="16">
+        <v>62000</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0.26</v>
+      </c>
+      <c r="G34" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="18">
+        <v>2</v>
+      </c>
+      <c r="E35" s="16">
+        <v>36000</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.22</v>
+      </c>
+      <c r="G35" s="17">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="16">
+        <v>22000</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="17">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="16">
+        <v>22000</v>
+      </c>
+      <c r="E43" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="16">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="17">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="16">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="17">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="16">
+        <v>650</v>
+      </c>
+      <c r="E46" s="17">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="16">
+        <v>450</v>
+      </c>
+      <c r="E47" s="17">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="16">
+        <v>30000</v>
+      </c>
+      <c r="E48" s="17">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="16">
+        <v>12000</v>
+      </c>
+      <c r="E49" s="17">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" s="16">
+        <v>18000</v>
+      </c>
+      <c r="E50" s="17">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="16">
+        <v>750</v>
+      </c>
+      <c r="E51" s="17">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="19">
+        <v>0</v>
+      </c>
+      <c r="D54" s="16">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="20">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="13">
+        <v>10</v>
+      </c>
+      <c r="G54" s="19">
+        <v>46629</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="16">
+        <v>60000</v>
+      </c>
+      <c r="D55" s="11">
+        <v>0</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="18">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="17">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" s="16">
+        <v>8200</v>
+      </c>
+      <c r="C73" s="16">
+        <v>9100</v>
+      </c>
+      <c r="D73" s="16">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B76" s="13">
+        <v>80</v>
+      </c>
+      <c r="C76" s="13">
+        <v>130</v>
+      </c>
+      <c r="D76" s="13">
+        <v>180</v>
+      </c>
+      <c r="E76" s="13">
+        <v>230</v>
+      </c>
+      <c r="F76" s="13">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="13">
         <v>40</v>
       </c>
-      <c r="B12" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="C77" s="13">
+        <v>70</v>
+      </c>
+      <c r="D77" s="13">
+        <v>100</v>
+      </c>
+      <c r="E77" s="13">
+        <v>120</v>
+      </c>
+      <c r="F77" s="13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="13">
+        <v>0</v>
+      </c>
+      <c r="C78" s="13">
+        <v>0</v>
+      </c>
+      <c r="D78" s="13">
+        <v>20</v>
+      </c>
+      <c r="E78" s="13">
         <v>50</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="11">
-        <v>120</v>
-      </c>
-      <c r="C17" s="11">
-        <v>200</v>
-      </c>
-      <c r="D17" s="11">
-        <v>300</v>
-      </c>
-      <c r="E17" s="11">
-        <v>400</v>
-      </c>
-      <c r="F17" s="11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="12">
-        <v>8500</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
-        <v>12</v>
-      </c>
-      <c r="G20" s="13">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="12">
-        <v>750</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>12</v>
-      </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="12">
-        <v>1100</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9">
-        <v>12</v>
-      </c>
-      <c r="G22" s="13">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="12">
-        <v>150000</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>12</v>
-      </c>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="12">
-        <v>25000</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>12</v>
-      </c>
-      <c r="G24" s="13">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="12">
-        <v>400</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>12</v>
-      </c>
-      <c r="G25" s="13">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12">
-        <v>105000</v>
-      </c>
-      <c r="F29" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12">
-        <v>82000</v>
-      </c>
-      <c r="F30" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="G30" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="14">
-        <v>5</v>
-      </c>
-      <c r="E31" s="12">
-        <v>50000</v>
-      </c>
-      <c r="F31" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="G31" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="14">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12">
-        <v>53000</v>
-      </c>
-      <c r="F32" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="G32" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="14">
-        <v>3</v>
-      </c>
-      <c r="E33" s="12">
-        <v>28000</v>
-      </c>
-      <c r="F33" s="13">
-        <v>0.18</v>
-      </c>
-      <c r="G33" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="14">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12">
-        <v>62000</v>
-      </c>
-      <c r="F34" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="G34" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="14">
-        <v>2</v>
-      </c>
-      <c r="E35" s="12">
-        <v>36000</v>
-      </c>
-      <c r="F35" s="13">
-        <v>0.22</v>
-      </c>
-      <c r="G35" s="13">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="12">
-        <v>22000</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="F78" s="13">
         <v>100</v>
       </c>
-      <c r="B40" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="12">
-        <v>22000</v>
-      </c>
-      <c r="E43" s="13">
-        <v>0.03</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="12">
-        <v>3000</v>
-      </c>
-      <c r="E44" s="13">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="12">
-        <v>22000</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" s="12">
-        <v>650</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" s="12">
-        <v>450</v>
-      </c>
-      <c r="E47" s="13">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D48" s="12">
-        <v>30000</v>
-      </c>
-      <c r="E48" s="13">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="12">
-        <v>12000</v>
-      </c>
-      <c r="E49" s="13">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="12">
-        <v>18000</v>
-      </c>
-      <c r="E50" s="13">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="12">
-        <v>750</v>
-      </c>
-      <c r="E51" s="13">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="15">
-        <v>0</v>
-      </c>
-      <c r="D54" s="12">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="F54" s="9">
-        <v>10</v>
-      </c>
-      <c r="G54" s="15">
-        <v>46629</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="12">
-        <v>60000</v>
-      </c>
-      <c r="D55" s="7">
-        <v>0</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B60" s="14">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B61" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="18">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B73" s="12">
-        <v>8200</v>
-      </c>
-      <c r="C73" s="12">
-        <v>9100</v>
-      </c>
-      <c r="D73" s="12">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="9">
-        <v>80</v>
-      </c>
-      <c r="C76" s="9">
-        <v>130</v>
-      </c>
-      <c r="D76" s="9">
-        <v>180</v>
-      </c>
-      <c r="E76" s="9">
-        <v>230</v>
-      </c>
-      <c r="F76" s="9">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B77" s="9">
-        <v>40</v>
-      </c>
-      <c r="C77" s="9">
-        <v>70</v>
-      </c>
-      <c r="D77" s="9">
-        <v>100</v>
-      </c>
-      <c r="E77" s="9">
-        <v>120</v>
-      </c>
-      <c r="F77" s="9">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B78" s="9">
-        <v>0</v>
-      </c>
-      <c r="C78" s="9">
-        <v>0</v>
-      </c>
-      <c r="D78" s="9">
-        <v>20</v>
-      </c>
-      <c r="E78" s="9">
-        <v>50</v>
-      </c>
-      <c r="F78" s="9">
-        <v>100</v>
-      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
+      <c r="A80" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2805,1504 +3027,1504 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>50</v>
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="22">
+      <c r="A3" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="26">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="26">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="26">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="26">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="26">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="19">
         <v>807500</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>1617850</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>2466200</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>3327850</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>4233200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="19">
         <v>75000</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>153000</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>234000</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>318400</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>406000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="19">
         <v>110000</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>224400</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="19">
         <v>343200</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="19">
         <v>466800</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="19">
         <v>595500</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="19">
         <v>125000</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>100000</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="19">
         <v>50000</v>
       </c>
-      <c r="E9" s="15">
-        <v>0</v>
-      </c>
-      <c r="F9" s="15">
+      <c r="E9" s="19">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="19">
         <v>20833</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="19">
         <v>35000</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="19">
         <v>45000</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="19">
         <v>55000</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="19">
         <v>65000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="15">
+      <c r="A11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="19">
         <v>40000</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="19">
         <v>82400</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="19">
         <v>127200</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="19">
         <v>174800</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="19">
         <v>225000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B12" s="23">
+      <c r="A12" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="27">
         <f>SUM(B6:B11)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="27">
         <f>SUM(C6:C11)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="27">
         <f>SUM(D6:D11)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="27">
         <f>SUM(E6:E11)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="27">
         <f>SUM(F6:F11)</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="19">
         <v>116944</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>140333</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="19">
         <v>140333</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>140333</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="19">
         <v>140333</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="19">
         <v>91328</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>109593</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="19">
         <v>109593</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <v>109593</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="19">
         <v>109593</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="19">
         <v>278438</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="19">
         <v>334125</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="19">
         <v>334125</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="19">
         <v>334125</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="19">
         <v>334125</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="19">
         <v>59029</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="19">
         <v>70835</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="19">
         <v>70835</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="19">
         <v>70835</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="19">
         <v>70835</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="19">
         <v>87955</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="19">
         <v>105546</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="19">
         <v>105546</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="19">
         <v>105546</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="19">
         <v>105546</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B20" s="15">
+      <c r="A20" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="19">
         <v>69053</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="19">
         <v>82863</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="19">
         <v>82863</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="19">
         <v>82863</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="19">
         <v>82863</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B21" s="15">
+      <c r="A21" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="19">
         <v>77790</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>93348</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="19">
         <v>93348</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="19">
         <v>93348</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="19">
         <v>93348</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="27">
         <f>SUM(B15:B21)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="27">
         <f>SUM(C15:C21)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="27">
         <f>SUM(D15:D21)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="27">
         <f>SUM(E15:E21)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="27">
         <f>SUM(F15:F21)</f>
         <v>936642</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="15">
+      <c r="A26" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="19">
         <v>65000</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="19">
         <v>134000</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="19">
         <v>207000</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="19">
         <v>284000</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="19">
         <v>366000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B27" s="25">
+      <c r="A27" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="29">
         <v>65000</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="29">
         <v>134000</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="29">
         <v>207000</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="29">
         <v>284000</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="29">
         <v>366000</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="19">
+        <v>45000</v>
+      </c>
+      <c r="C29" s="19">
+        <v>92800</v>
+      </c>
+      <c r="D29" s="19">
+        <v>143400</v>
+      </c>
+      <c r="E29" s="19">
+        <v>196800</v>
+      </c>
+      <c r="F29" s="19">
+        <v>253500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="29">
+        <v>45000</v>
+      </c>
+      <c r="C30" s="29">
+        <v>92800</v>
+      </c>
+      <c r="D30" s="29">
+        <v>143400</v>
+      </c>
+      <c r="E30" s="29">
+        <v>196800</v>
+      </c>
+      <c r="F30" s="29">
+        <v>253500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B29" s="15">
-        <v>45000</v>
-      </c>
-      <c r="C29" s="15">
-        <v>92800</v>
-      </c>
-      <c r="D29" s="15">
-        <v>143400</v>
-      </c>
-      <c r="E29" s="15">
-        <v>196800</v>
-      </c>
-      <c r="F29" s="15">
-        <v>253500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" s="25">
-        <v>45000</v>
-      </c>
-      <c r="C30" s="25">
-        <v>92800</v>
-      </c>
-      <c r="D30" s="25">
-        <v>143400</v>
-      </c>
-      <c r="E30" s="25">
-        <v>196800</v>
-      </c>
-      <c r="F30" s="25">
-        <v>253500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="A32" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="19">
         <v>220000</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="19">
         <v>271920</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="19">
         <v>280078</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="19">
         <v>288480</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="19">
         <v>297134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="15">
+      <c r="A33" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="19">
         <v>30000</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="19">
         <v>37080</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="19">
         <v>38196</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="19">
         <v>39336</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="19">
         <v>40524</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="19">
         <v>18333</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="19">
         <v>22660</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="19">
         <v>23340</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="19">
         <v>24040</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="19">
         <v>24761</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B35" s="25">
+      <c r="A35" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="29">
         <v>268333</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="29">
         <v>331660</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="29">
         <v>341614</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="29">
         <v>351856</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="29">
         <v>362419</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="A36" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="A37" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="19">
         <v>25000</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="19">
         <v>30900</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="19">
         <v>31827</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="19">
         <v>32782</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="19">
         <v>33765</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="15">
+      <c r="A38" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="19">
         <v>10000</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="19">
         <v>12360</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="19">
         <v>12731</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="19">
         <v>13113</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="19">
         <v>13506</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B39" s="15">
+      <c r="A39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" s="19">
         <v>15000</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="19">
         <v>18540</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="19">
         <v>19096</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="19">
         <v>19669</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="19">
         <v>20259</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B40" s="15">
+      <c r="A40" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" s="19">
         <v>75000</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="19">
         <v>154600</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="19">
         <v>238800</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="19">
         <v>328000</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="19">
         <v>422500</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B41" s="25">
+      <c r="A41" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="29">
         <v>125000</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="29">
         <v>216400</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="29">
         <v>302454</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="29">
         <v>393564</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="29">
         <v>490030</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B42" s="23">
+      <c r="A42" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="27">
         <f>B27+B30+B35+B41</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="27">
         <f>C27+C30+C35+C41</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="27">
         <f>D27+D30+D35+D41</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="27">
         <f>E27+E30+E35+E41</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="27">
         <f>F27+F30+F35+F41</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
+      <c r="A44" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B45" s="15">
+      <c r="A45" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="19">
         <v>46629</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="19">
         <v>46629</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="19">
         <v>46629</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="19">
         <v>46629</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="19">
         <v>46629</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="15">
+      <c r="A46" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="19">
         <v>60000</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="19">
         <v>20000</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="19">
         <v>25000</v>
       </c>
-      <c r="E46" s="15">
+      <c r="E46" s="19">
         <v>10000</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="19">
         <v>10000</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B47" s="23">
+      <c r="A47" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="27">
         <f>SUM(B45:B46)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="27">
         <f>SUM(C45:C46)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="27">
         <f>SUM(D45:D46)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="27">
         <f>SUM(E45:E46)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="27">
         <f>SUM(F45:F46)</f>
         <v>56629</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B50" s="25">
+      <c r="A50" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B50" s="29">
         <f>B12</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="29">
         <f>C12</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="25">
+      <c r="D50" s="29">
         <f>D12</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="29">
         <f>E12</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="25">
+      <c r="F50" s="29">
         <f>F12</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B51" s="15">
+      <c r="A51" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="19">
         <f>B22</f>
         <v>780535</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="19">
         <f>C22</f>
         <v>936642</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="19">
         <f>D22</f>
         <v>936642</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="19">
         <f>E22</f>
         <v>936642</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="19">
         <f>F22</f>
         <v>936642</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B52" s="15">
+      <c r="A52" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B52" s="19">
         <f>B42</f>
         <v>503333</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="19">
         <f>C42</f>
         <v>774860</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="19">
         <f>D42</f>
         <v>994468</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="19">
         <f>E42</f>
         <v>1226220</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="19">
         <f>F42</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B53" s="15">
+      <c r="A53" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="19">
         <f>B47</f>
         <v>106629</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="19">
         <f>C47</f>
         <v>66629</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="19">
         <f>D47</f>
         <v>71629</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="19">
         <f>E47</f>
         <v>56629</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="19">
         <f>F47</f>
         <v>56629</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B54" s="25">
+      <c r="A54" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" s="29">
         <f>B51+B52+B53</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="29">
         <f>C51+C52+C53</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="29">
         <f>D51+D52+D53</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="29">
         <f>E51+E52+E53</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="29">
         <f>F51+F52+F53</f>
         <v>2465220</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="B56" s="27">
+      <c r="A56" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" s="31">
         <f>B50-B54</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="32">
         <f>C50-C54</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="28">
+      <c r="D56" s="32">
         <f>D50-D54</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="28">
+      <c r="E56" s="32">
         <f>E50-E54</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="28">
+      <c r="F56" s="32">
         <f>F50-F54</f>
         <v>3059480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B57" s="29">
+      <c r="A57" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B57" s="33">
         <f>IF(B50=0,"",B56/B50)</f>
         <v>-0.18</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="33">
         <f>IF(C50=0,"",C56/C50)</f>
         <v>0.2</v>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="33">
         <f>IF(D50=0,"",D56/D50)</f>
         <v>0.39</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="33">
         <f>IF(E50=0,"",E56/E50)</f>
         <v>0.49</v>
       </c>
-      <c r="F57" s="29">
+      <c r="F57" s="33">
         <f>IF(F50=0,"",F56/F50)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B58" s="15">
+      <c r="A58" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" s="19">
         <f>B56</f>
         <v>-212164</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="19">
         <f>B58+C56</f>
         <v>222355</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="19">
         <f>C58+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E58" s="15">
+      <c r="E58" s="19">
         <f>D58+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="19">
         <f>E58+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+      <c r="A60" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="B61" s="25">
+      <c r="A61" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" s="29">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="29">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="25">
+      <c r="D61" s="29">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="29">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="29">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="B62" s="15">
+      <c r="A62" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B62" s="19">
         <f>B53</f>
         <v>106629</v>
       </c>
-      <c r="C62" s="15">
+      <c r="C62" s="19">
         <f>C53</f>
         <v>66629</v>
       </c>
-      <c r="D62" s="15">
+      <c r="D62" s="19">
         <f>D53</f>
         <v>71629</v>
       </c>
-      <c r="E62" s="15">
+      <c r="E62" s="19">
         <f>E53</f>
         <v>56629</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F62" s="19">
         <f>F53</f>
         <v>56629</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B63" s="30">
+      <c r="A63" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="B63" s="34">
         <f>IF(B62=0,"N/A",B61/B62)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C63" s="34">
         <f>IF(C62=0,"N/A",C61/C62)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="34">
         <f>IF(D62=0,"N/A",D61/D62)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="30">
+      <c r="E63" s="34">
         <f>IF(E62=0,"N/A",E61/E62)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="30">
+      <c r="F63" s="34">
         <f>IF(F62=0,"N/A",F61/F62)</f>
         <v>55.03</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="15" t="str">
+      <c r="A64" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="19" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C64" s="15">
+      <c r="C64" s="19">
         <f>B65</f>
         <v>-212164</v>
       </c>
-      <c r="D64" s="15">
+      <c r="D64" s="19">
         <f>C65</f>
         <v>222355</v>
       </c>
-      <c r="E64" s="15">
+      <c r="E64" s="19">
         <f>D65</f>
         <v>1485216</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="19">
         <f>E65</f>
         <v>3608575</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="B65" s="25">
+      <c r="A65" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="B65" s="29">
         <f>B64+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="29">
         <f>C64+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="25">
+      <c r="D65" s="29">
         <f>D64+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="29">
         <f>E64+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="25">
+      <c r="F65" s="29">
         <f>F64+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="35">
         <f>IF(B54=0,"",B65/B54*365)</f>
         <v>-56</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="35">
         <f>IF(C54=0,"",C65/C54*365)</f>
         <v>46</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="35">
         <f>IF(D54=0,"",D65/D54*365)</f>
         <v>271</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="35">
         <f>IF(E54=0,"",E65/E54*365)</f>
         <v>593</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="35">
         <f>IF(F54=0,"",F65/F54*365)</f>
         <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B67" s="32">
+      <c r="A67" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B67" s="36">
         <f>IF(B54=0,"",B65/(B54/12))</f>
         <v>-1.8</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="36">
         <f>IF(C54=0,"",C65/(C54/12))</f>
         <v>1.5</v>
       </c>
-      <c r="D67" s="32">
+      <c r="D67" s="36">
         <f>IF(D54=0,"",D65/(D54/12))</f>
         <v>8.9</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="36">
         <f>IF(E54=0,"",E65/(E54/12))</f>
         <v>19.5</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="36">
         <f>IF(F54=0,"",F65/(F54/12))</f>
         <v>32.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B68" s="29">
+      <c r="A68" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="33">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="33">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="29">
+      <c r="D68" s="33">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="29">
+      <c r="E68" s="33">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="33">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
+      <c r="A70" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B71" s="7" t="str">
+      <c r="A71" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B71" s="11" t="str">
         <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C71" s="7" t="str">
+      <c r="C71" s="11" t="str">
         <f>IF(C62=0,"N/A",IF(C63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D71" s="7" t="str">
+      <c r="D71" s="11" t="str">
         <f>IF(D62=0,"N/A",IF(D63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E71" s="7" t="str">
+      <c r="E71" s="11" t="str">
         <f>IF(E62=0,"N/A",IF(E63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F71" s="7" t="str">
+      <c r="F71" s="11" t="str">
         <f>IF(F62=0,"N/A",IF(F63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B72" s="7" t="str">
+      <c r="A72" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B72" s="11" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C72" s="7" t="str">
+      <c r="C72" s="11" t="str">
         <f>IF(C56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D72" s="7" t="str">
+      <c r="D72" s="11" t="str">
         <f>IF(D56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E72" s="7" t="str">
+      <c r="E72" s="11" t="str">
         <f>IF(E56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F72" s="7" t="str">
+      <c r="F72" s="11" t="str">
         <f>IF(F56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B73" s="7" t="str">
+      <c r="A73" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B73" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C73" s="7" t="str">
+      <c r="C73" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D73" s="7" t="str">
+      <c r="D73" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E73" s="7" t="str">
+      <c r="E73" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="F73" s="7" t="str">
+      <c r="F73" s="11" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B74" s="7" t="str">
+      <c r="A74" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B74" s="11" t="str">
         <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C74" s="7" t="str">
+      <c r="C74" s="11" t="str">
         <f>IF(C54=0,"N/A",IF(C65/(C54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D74" s="7" t="str">
+      <c r="D74" s="11" t="str">
         <f>IF(D54=0,"N/A",IF(D65/(D54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E74" s="7" t="str">
+      <c r="E74" s="11" t="str">
         <f>IF(E54=0,"N/A",IF(E65/(E54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F74" s="7" t="str">
+      <c r="F74" s="11" t="str">
         <f>IF(F54=0,"N/A",IF(F65/(F54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+      <c r="A76" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B77" s="15">
+      <c r="A77" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B77" s="19">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>9819</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="19">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>11063</v>
       </c>
-      <c r="D77" s="15">
+      <c r="D77" s="19">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>10885</v>
       </c>
-      <c r="E77" s="15">
+      <c r="E77" s="19">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>10857</v>
       </c>
-      <c r="F77" s="15">
+      <c r="F77" s="19">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>11049</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B78" s="15">
+      <c r="A78" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B78" s="19">
         <f>IF(B3=0,"",B54/B3)</f>
         <v>11587</v>
       </c>
-      <c r="C78" s="15">
+      <c r="C78" s="19">
         <f>IF(C3=0,"",C54/C3)</f>
         <v>8891</v>
       </c>
-      <c r="D78" s="15">
+      <c r="D78" s="19">
         <f>IF(D3=0,"",D54/D3)</f>
         <v>6676</v>
       </c>
-      <c r="E78" s="15">
+      <c r="E78" s="19">
         <f>IF(E3=0,"",E54/E3)</f>
         <v>5549</v>
       </c>
-      <c r="F78" s="15">
+      <c r="F78" s="19">
         <f>IF(F3=0,"",F54/F3)</f>
         <v>4930</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B79" s="15">
+      <c r="A79" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B79" s="19">
         <f>B51+B53</f>
         <v>887164</v>
       </c>
-      <c r="C79" s="15">
+      <c r="C79" s="19">
         <f>C51+C53</f>
         <v>1003271</v>
       </c>
-      <c r="D79" s="15">
+      <c r="D79" s="19">
         <f>D51+D53</f>
         <v>1008271</v>
       </c>
-      <c r="E79" s="15">
+      <c r="E79" s="19">
         <f>E51+E53</f>
         <v>993271</v>
       </c>
-      <c r="F79" s="15">
+      <c r="F79" s="19">
         <f>F51+F53</f>
         <v>993271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B80" s="15">
+      <c r="A80" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B80" s="19">
         <f>IF(B3=0,"",B52/B3)</f>
         <v>4194</v>
       </c>
-      <c r="C80" s="15">
+      <c r="C80" s="19">
         <f>IF(C3=0,"",C52/C3)</f>
         <v>3874</v>
       </c>
-      <c r="D80" s="15">
+      <c r="D80" s="19">
         <f>IF(D3=0,"",D52/D3)</f>
         <v>3315</v>
       </c>
-      <c r="E80" s="15">
+      <c r="E80" s="19">
         <f>IF(E3=0,"",E52/E3)</f>
         <v>3066</v>
       </c>
-      <c r="F80" s="15">
+      <c r="F80" s="19">
         <f>IF(F3=0,"",F52/F3)</f>
         <v>2944</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" s="15">
+      <c r="A81" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B81" s="19">
         <f>IF(B3=0,"",B77-B80)</f>
         <v>5625</v>
       </c>
-      <c r="C81" s="15">
+      <c r="C81" s="19">
         <f>IF(C3=0,"",C77-C80)</f>
         <v>7189</v>
       </c>
-      <c r="D81" s="15">
+      <c r="D81" s="19">
         <f>IF(D3=0,"",D77-D80)</f>
         <v>7570</v>
       </c>
-      <c r="E81" s="15">
+      <c r="E81" s="19">
         <f>IF(E3=0,"",E77-E80)</f>
         <v>7792</v>
       </c>
-      <c r="F81" s="15">
+      <c r="F81" s="19">
         <f>IF(F3=0,"",F77-F80)</f>
         <v>8106</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="B82" s="34">
+      <c r="A82" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" s="38">
         <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="34">
+      <c r="C82" s="38">
         <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="34">
+      <c r="D82" s="38">
         <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="34">
+      <c r="E82" s="38">
         <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="34">
+      <c r="F82" s="38">
         <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
+      <c r="A84" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4332,1838 +4554,1838 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="I2" s="19" t="s">
+      <c r="A2" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="D2" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="E2" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="F2" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="G2" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="H2" s="23" t="s">
         <v>218</v>
       </c>
+      <c r="I2" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="A3" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="19">
         <v>96900</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="19">
         <v>96900</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="19">
         <v>96900</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="19">
         <v>96900</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="19">
         <v>96900</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="19">
         <v>96900</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="19">
         <v>96900</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="19">
         <v>96900</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="19">
         <v>96900</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="19">
         <v>96900</v>
       </c>
-      <c r="L4" s="15">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15">
-        <v>0</v>
-      </c>
-      <c r="N4" s="15">
+      <c r="L4" s="19">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
         <f>SUM(B4:M4)</f>
         <v>807500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="19">
         <v>9000</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="19">
         <v>9000</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="19">
         <v>9000</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="19">
         <v>9000</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="19">
         <v>9000</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="19">
         <v>9000</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="19">
         <v>9000</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="19">
         <v>9000</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="19">
         <v>9000</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="19">
         <v>9000</v>
       </c>
-      <c r="L5" s="15">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>0</v>
-      </c>
-      <c r="N5" s="15">
+      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
         <f>SUM(B5:M5)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="19">
         <v>13200</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="19">
         <v>13200</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="19">
         <v>13200</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <v>13200</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="19">
         <v>13200</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="19">
         <v>13200</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="19">
         <v>13200</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="19">
         <v>13200</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="19">
         <v>13200</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="19">
         <v>13200</v>
       </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
-      <c r="M6" s="15">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15">
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
         <f>SUM(B6:M6)</f>
         <v>110000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="19">
         <v>15000</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="19">
         <v>15000</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="19">
         <v>15000</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="19">
         <v>15000</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="19">
         <v>15000</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="19">
         <v>15000</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="19">
         <v>15000</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="19">
         <v>15000</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="19">
         <v>15000</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="19">
         <v>15000</v>
       </c>
-      <c r="L7" s="15">
-        <v>0</v>
-      </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="L7" s="19">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19">
+        <v>0</v>
+      </c>
+      <c r="N7" s="19">
         <f>SUM(B7:M7)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="19">
         <v>2500</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="19">
         <v>2500</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="19">
         <v>2500</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="19">
         <v>2500</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="19">
         <v>2500</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="19">
         <v>2500</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="19">
         <v>2500</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="19">
         <v>2500</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="19">
         <v>2500</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="19">
         <v>2500</v>
       </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>0</v>
-      </c>
-      <c r="N8" s="15">
+      <c r="L8" s="19">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19">
         <f>SUM(B8:M8)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="19">
         <v>4800</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>4800</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="19">
         <v>4800</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="19">
         <v>4800</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="19">
         <v>4800</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="19">
         <v>4800</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="19">
         <v>4800</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="19">
         <v>4800</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="19">
         <v>4800</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="19">
         <v>4800</v>
       </c>
-      <c r="L9" s="15">
-        <v>0</v>
-      </c>
-      <c r="M9" s="15">
-        <v>0</v>
-      </c>
-      <c r="N9" s="15">
+      <c r="L9" s="19">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19">
+        <v>0</v>
+      </c>
+      <c r="N9" s="19">
         <f>SUM(B9:M9)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="A10" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="27">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="27">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="27">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="27">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="27">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="27">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="27">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="27">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="27">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="27">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="23" t="str">
+      <c r="L10" s="27" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="23" t="str">
+      <c r="M10" s="27" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="27">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="A12" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="15">
+      <c r="A13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="19">
         <v>11694</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="19">
         <v>11694</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="19">
         <v>11694</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="19">
         <v>11694</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="19">
         <v>11694</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="19">
         <v>11694</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="19">
         <v>11694</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="19">
         <v>11694</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="19">
         <v>11694</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="19">
         <v>11694</v>
       </c>
-      <c r="L13" s="15">
-        <v>0</v>
-      </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
-      <c r="N13" s="15">
+      <c r="L13" s="19">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0</v>
+      </c>
+      <c r="N13" s="19">
         <f>SUM(B13:M13)</f>
         <v>116944</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="15">
+      <c r="A14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="19">
         <v>9133</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="19">
         <v>9133</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="19">
         <v>9133</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="19">
         <v>9133</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="19">
         <v>9133</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="19">
         <v>9133</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="19">
         <v>9133</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="19">
         <v>9133</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="19">
         <v>9133</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="19">
         <v>9133</v>
       </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
-      <c r="N14" s="15">
+      <c r="L14" s="19">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19">
+        <v>0</v>
+      </c>
+      <c r="N14" s="19">
         <f>SUM(B14:M14)</f>
         <v>91328</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="A15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="19">
         <v>27844</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="19">
         <v>27844</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="19">
         <v>27844</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="19">
         <v>27844</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="19">
         <v>27844</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="19">
         <v>27844</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="19">
         <v>27844</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="19">
         <v>27844</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="19">
         <v>27844</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="19">
         <v>27844</v>
       </c>
-      <c r="L15" s="15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
+      <c r="L15" s="19">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19">
         <f>SUM(B15:M15)</f>
         <v>278438</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="A16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="19">
         <v>5903</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>5903</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="19">
         <v>5903</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <v>5903</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="19">
         <v>5903</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="19">
         <v>5903</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="19">
         <v>5903</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="19">
         <v>5903</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="19">
         <v>5903</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="19">
         <v>5903</v>
       </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15">
-        <v>0</v>
-      </c>
-      <c r="N16" s="15">
+      <c r="L16" s="19">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19">
+        <v>0</v>
+      </c>
+      <c r="N16" s="19">
         <f>SUM(B16:M16)</f>
         <v>59029</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="15">
+      <c r="A17" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="19">
         <v>8796</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="19">
         <v>8796</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="19">
         <v>8796</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="19">
         <v>8796</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="19">
         <v>8796</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="19">
         <v>8796</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="19">
         <v>8796</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="19">
         <v>8796</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="19">
         <v>8796</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="19">
         <v>8796</v>
       </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>0</v>
-      </c>
-      <c r="N17" s="15">
+      <c r="L17" s="19">
+        <v>0</v>
+      </c>
+      <c r="M17" s="19">
+        <v>0</v>
+      </c>
+      <c r="N17" s="19">
         <f>SUM(B17:M17)</f>
         <v>87955</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="19">
         <v>6905</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="19">
         <v>6905</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="19">
         <v>6905</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="19">
         <v>6905</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="19">
         <v>6905</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="19">
         <v>6905</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="19">
         <v>6905</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="19">
         <v>6905</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="19">
         <v>6905</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="19">
         <v>6905</v>
       </c>
-      <c r="L18" s="15">
-        <v>0</v>
-      </c>
-      <c r="M18" s="15">
-        <v>0</v>
-      </c>
-      <c r="N18" s="15">
+      <c r="L18" s="19">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19">
         <f>SUM(B18:M18)</f>
         <v>69053</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="15">
+      <c r="A19" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="19">
         <v>7779</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="19">
         <v>7779</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="19">
         <v>7779</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="19">
         <v>7779</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="19">
         <v>7779</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="19">
         <v>7779</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="19">
         <v>7779</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="19">
         <v>7779</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="19">
         <v>7779</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="19">
         <v>7779</v>
       </c>
-      <c r="L19" s="15">
-        <v>0</v>
-      </c>
-      <c r="M19" s="15">
-        <v>0</v>
-      </c>
-      <c r="N19" s="15">
+      <c r="L19" s="19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="19">
         <f>SUM(B19:M19)</f>
         <v>77790</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="23">
+      <c r="A20" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="27">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="27">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="27">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="27">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="27">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="27">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="27">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="27">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="27">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="27">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="23" t="str">
+      <c r="L20" s="27" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="23" t="str">
+      <c r="M20" s="27" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="27">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="A22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
+      <c r="A23" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="15">
+      <c r="A24" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="19">
         <v>6500</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="19">
         <v>6500</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="19">
         <v>6500</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="19">
         <v>6500</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="19">
         <v>6500</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="19">
         <v>6500</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="19">
         <v>6500</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="19">
         <v>6500</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="19">
         <v>6500</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="19">
         <v>6500</v>
       </c>
-      <c r="L24" s="15">
-        <v>0</v>
-      </c>
-      <c r="M24" s="15">
-        <v>0</v>
-      </c>
-      <c r="N24" s="15">
+      <c r="L24" s="19">
+        <v>0</v>
+      </c>
+      <c r="M24" s="19">
+        <v>0</v>
+      </c>
+      <c r="N24" s="19">
         <f>SUM(B24:M24)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B25" s="25">
+      <c r="A25" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="29">
         <v>6500</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="29">
         <v>6500</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="29">
         <v>6500</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="29">
         <v>6500</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="29">
         <v>6500</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="29">
         <v>6500</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="29">
         <v>6500</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="29">
         <v>6500</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="29">
         <v>6500</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="29">
         <v>6500</v>
       </c>
-      <c r="L25" s="25">
-        <v>0</v>
-      </c>
-      <c r="M25" s="25">
-        <v>0</v>
-      </c>
-      <c r="N25" s="25">
+      <c r="L25" s="29">
+        <v>0</v>
+      </c>
+      <c r="M25" s="29">
+        <v>0</v>
+      </c>
+      <c r="N25" s="29">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="A26" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="15">
+      <c r="A27" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="19">
         <v>4500</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="19">
         <v>4500</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="19">
         <v>4500</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="19">
         <v>4500</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="19">
         <v>4500</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="19">
         <v>4500</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="19">
         <v>4500</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="19">
         <v>4500</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="19">
         <v>4500</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="19">
         <v>4500</v>
       </c>
-      <c r="L27" s="15">
-        <v>0</v>
-      </c>
-      <c r="M27" s="15">
-        <v>0</v>
-      </c>
-      <c r="N27" s="15">
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
         <f>SUM(B27:M27)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B28" s="25">
+      <c r="A28" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="29">
         <v>4500</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="29">
         <v>4500</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="29">
         <v>4500</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="29">
         <v>4500</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="29">
         <v>4500</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="29">
         <v>4500</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="29">
         <v>4500</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="29">
         <v>4500</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="29">
         <v>4500</v>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="29">
         <v>4500</v>
       </c>
-      <c r="L28" s="25">
-        <v>0</v>
-      </c>
-      <c r="M28" s="25">
-        <v>0</v>
-      </c>
-      <c r="N28" s="25">
+      <c r="L28" s="29">
+        <v>0</v>
+      </c>
+      <c r="M28" s="29">
+        <v>0</v>
+      </c>
+      <c r="N28" s="29">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
+      <c r="A29" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="15">
+      <c r="A30" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="19">
         <v>22000</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="19">
         <v>22000</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="19">
         <v>22000</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="19">
         <v>22000</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="19">
         <v>22000</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="19">
         <v>22000</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="19">
         <v>22000</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="19">
         <v>22000</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="19">
         <v>22000</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="19">
         <v>22000</v>
       </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>0</v>
-      </c>
-      <c r="N30" s="15">
+      <c r="L30" s="19">
+        <v>0</v>
+      </c>
+      <c r="M30" s="19">
+        <v>0</v>
+      </c>
+      <c r="N30" s="19">
         <f>SUM(B30:M30)</f>
         <v>220000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="15">
+      <c r="A31" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="19">
         <v>3000</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="19">
         <v>3000</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="19">
         <v>3000</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="19">
         <v>3000</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="19">
         <v>3000</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="19">
         <v>3000</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="19">
         <v>3000</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="19">
         <v>3000</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="19">
         <v>3000</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="19">
         <v>3000</v>
       </c>
-      <c r="L31" s="15">
-        <v>0</v>
-      </c>
-      <c r="M31" s="15">
-        <v>0</v>
-      </c>
-      <c r="N31" s="15">
+      <c r="L31" s="19">
+        <v>0</v>
+      </c>
+      <c r="M31" s="19">
+        <v>0</v>
+      </c>
+      <c r="N31" s="19">
         <f>SUM(B31:M31)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="A32" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="19">
         <v>1833</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="19">
         <v>1833</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="19">
         <v>1833</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="19">
         <v>1833</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="19">
         <v>1833</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="19">
         <v>1833</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="19">
         <v>1833</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="19">
         <v>1833</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="19">
         <v>1833</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="19">
         <v>1833</v>
       </c>
-      <c r="L32" s="15">
-        <v>0</v>
-      </c>
-      <c r="M32" s="15">
-        <v>0</v>
-      </c>
-      <c r="N32" s="15">
+      <c r="L32" s="19">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19">
+        <v>0</v>
+      </c>
+      <c r="N32" s="19">
         <f>SUM(B32:M32)</f>
         <v>18333</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B33" s="25">
+      <c r="A33" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" s="29">
         <v>26833</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="29">
         <v>26833</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="29">
         <v>26833</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="29">
         <v>26833</v>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="29">
         <v>26833</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="29">
         <v>26833</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="29">
         <v>26833</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="29">
         <v>26833</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="29">
         <v>26833</v>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="29">
         <v>26833</v>
       </c>
-      <c r="L33" s="25">
-        <v>0</v>
-      </c>
-      <c r="M33" s="25">
-        <v>0</v>
-      </c>
-      <c r="N33" s="25">
+      <c r="L33" s="29">
+        <v>0</v>
+      </c>
+      <c r="M33" s="29">
+        <v>0</v>
+      </c>
+      <c r="N33" s="29">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
+      <c r="A34" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="A35" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B35" s="19">
         <v>2500</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="19">
         <v>2500</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="19">
         <v>2500</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="19">
         <v>2500</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="19">
         <v>2500</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="19">
         <v>2500</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="19">
         <v>2500</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="19">
         <v>2500</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="19">
         <v>2500</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="19">
         <v>2500</v>
       </c>
-      <c r="L35" s="15">
-        <v>0</v>
-      </c>
-      <c r="M35" s="15">
-        <v>0</v>
-      </c>
-      <c r="N35" s="15">
+      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19">
+        <v>0</v>
+      </c>
+      <c r="N35" s="19">
         <f>SUM(B35:M35)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="A36" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" s="19">
         <v>1000</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="19">
         <v>1000</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="19">
         <v>1000</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="19">
         <v>1000</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="19">
         <v>1000</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="19">
         <v>1000</v>
       </c>
-      <c r="H36" s="15">
+      <c r="H36" s="19">
         <v>1000</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="19">
         <v>1000</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="19">
         <v>1000</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="19">
         <v>1000</v>
       </c>
-      <c r="L36" s="15">
-        <v>0</v>
-      </c>
-      <c r="M36" s="15">
-        <v>0</v>
-      </c>
-      <c r="N36" s="15">
+      <c r="L36" s="19">
+        <v>0</v>
+      </c>
+      <c r="M36" s="19">
+        <v>0</v>
+      </c>
+      <c r="N36" s="19">
         <f>SUM(B36:M36)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="A37" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="19">
         <v>1500</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="19">
         <v>1500</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="19">
         <v>1500</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="19">
         <v>1500</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="19">
         <v>1500</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="19">
         <v>1500</v>
       </c>
-      <c r="H37" s="15">
+      <c r="H37" s="19">
         <v>1500</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="19">
         <v>1500</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="19">
         <v>1500</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="19">
         <v>1500</v>
       </c>
-      <c r="L37" s="15">
-        <v>0</v>
-      </c>
-      <c r="M37" s="15">
-        <v>0</v>
-      </c>
-      <c r="N37" s="15">
+      <c r="L37" s="19">
+        <v>0</v>
+      </c>
+      <c r="M37" s="19">
+        <v>0</v>
+      </c>
+      <c r="N37" s="19">
         <f>SUM(B37:M37)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="15">
+      <c r="A38" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B38" s="19">
         <v>7500</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="19">
         <v>7500</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="19">
         <v>7500</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="19">
         <v>7500</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="19">
         <v>7500</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="19">
         <v>7500</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H38" s="19">
         <v>7500</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="19">
         <v>7500</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="19">
         <v>7500</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="19">
         <v>7500</v>
       </c>
-      <c r="L38" s="15">
-        <v>0</v>
-      </c>
-      <c r="M38" s="15">
-        <v>0</v>
-      </c>
-      <c r="N38" s="15">
+      <c r="L38" s="19">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19">
+        <v>0</v>
+      </c>
+      <c r="N38" s="19">
         <f>SUM(B38:M38)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B39" s="25">
+      <c r="A39" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B39" s="29">
         <v>12500</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="29">
         <v>12500</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="29">
         <v>12500</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="29">
         <v>12500</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="29">
         <v>12500</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="29">
         <v>12500</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="29">
         <v>12500</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="29">
         <v>12500</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="29">
         <v>12500</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="29">
         <v>12500</v>
       </c>
-      <c r="L39" s="25">
-        <v>0</v>
-      </c>
-      <c r="M39" s="25">
-        <v>0</v>
-      </c>
-      <c r="N39" s="25">
+      <c r="L39" s="29">
+        <v>0</v>
+      </c>
+      <c r="M39" s="29">
+        <v>0</v>
+      </c>
+      <c r="N39" s="29">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" s="23">
+      <c r="A40" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="27">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="27">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="27">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="27">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="27">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="27">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="27">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="27">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="23">
+      <c r="J40" s="27">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="23">
+      <c r="K40" s="27">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="23" t="str">
+      <c r="L40" s="27" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="23" t="str">
+      <c r="M40" s="27" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="27">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B42" s="19">
         <v>8886</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="19">
         <v>8886</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="19">
         <v>8886</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="19">
         <v>8886</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="19">
         <v>8886</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="19">
         <v>8886</v>
       </c>
-      <c r="H42" s="15">
+      <c r="H42" s="19">
         <v>8886</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="19">
         <v>8886</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="19">
         <v>8886</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="19">
         <v>8886</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="19">
         <v>8886</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="19">
         <v>8886</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="19">
         <f>SUM(B42:M42)</f>
         <v>106629</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
+      <c r="A44" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B45" s="25">
+      <c r="A45" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" s="29">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="29">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="29">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="29">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="29">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="29">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="29">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="25">
+      <c r="I45" s="29">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="29">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K45" s="29">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="25">
+      <c r="L45" s="29">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="25">
+      <c r="M45" s="29">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="25">
+      <c r="N45" s="29">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B46" s="25">
+      <c r="A46" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="29">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="29">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="29">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="29">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="29">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="25">
+      <c r="G46" s="29">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="25">
+      <c r="H46" s="29">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="29">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="25">
+      <c r="J46" s="29">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="29">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="25">
+      <c r="L46" s="29">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="25">
+      <c r="M46" s="29">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="29">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B47" s="25">
+      <c r="A47" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" s="29">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="29">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="29">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="29">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="29">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="25">
+      <c r="G47" s="29">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="25">
+      <c r="H47" s="29">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="25">
+      <c r="I47" s="29">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="29">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="25">
+      <c r="K47" s="29">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="25">
+      <c r="L47" s="29">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="25">
+      <c r="M47" s="29">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="25">
+      <c r="N47" s="29">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
+      <c r="A49" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" s="15">
+      <c r="A50" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B50" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B51" s="25">
+      <c r="A51" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" s="29">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B52" s="15">
+      <c r="A52" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" s="19">
         <f>MIN(B47:M47)</f>
         <v>9227</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
+      <c r="A54" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
+      <c r="N54" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6182,6 +6404,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -6195,7 +6418,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6204,466 +6427,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
+      <c r="B3" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>242</v>
+      <c r="B5" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="36">
+      <c r="B6" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="40">
         <v>120</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="40">
         <v>200</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="40">
         <v>300</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="40">
         <v>400</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="40">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="37">
+      <c r="B7" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="41">
         <v>1414000</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="41">
         <v>2212650</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <v>3265600</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="41">
         <v>4342850</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="41">
         <v>5524700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="41">
+        <v>780535</v>
+      </c>
+      <c r="D8" s="41">
+        <v>936642</v>
+      </c>
+      <c r="E8" s="41">
+        <v>936642</v>
+      </c>
+      <c r="F8" s="41">
+        <v>936642</v>
+      </c>
+      <c r="G8" s="41">
+        <v>936642</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="41">
+        <v>604000</v>
+      </c>
+      <c r="D9" s="41">
+        <v>774860</v>
+      </c>
+      <c r="E9" s="41">
+        <v>994467.6</v>
+      </c>
+      <c r="F9" s="41">
+        <v>1226219.9279999998</v>
+      </c>
+      <c r="G9" s="41">
+        <v>1471949.32584</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="41">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="D10" s="41">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="E10" s="41">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="F10" s="41">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="G10" s="41">
+        <v>46628.6108154935</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="42">
+        <v>-17163.6108154935</v>
+      </c>
+      <c r="D11" s="43">
+        <v>454519.3891845065</v>
+      </c>
+      <c r="E11" s="43">
+        <v>1287861.7891845065</v>
+      </c>
+      <c r="F11" s="43">
+        <v>2133359.461184507</v>
+      </c>
+      <c r="G11" s="43">
+        <v>3069480.0633445065</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="42">
+        <v>-17163.6108154935</v>
+      </c>
+      <c r="D12" s="43">
+        <v>437355.778369013</v>
+      </c>
+      <c r="E12" s="43">
+        <v>1725217.5675535195</v>
+      </c>
+      <c r="F12" s="43">
+        <v>3858577.0287380265</v>
+      </c>
+      <c r="G12" s="43">
+        <v>6928057.092082533</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="44">
+        <v>-0.0121383386248186</v>
+      </c>
+      <c r="D13" s="45">
+        <v>0.20541856560436875</v>
+      </c>
+      <c r="E13" s="45">
+        <v>0.39437217944160535</v>
+      </c>
+      <c r="F13" s="45">
+        <v>0.49123489440908774</v>
+      </c>
+      <c r="G13" s="45">
+        <v>0.555592170315946</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="41">
+        <v>11783.333333333334</v>
+      </c>
+      <c r="D14" s="41">
+        <v>11063.25</v>
+      </c>
+      <c r="E14" s="41">
+        <v>10885.333333333334</v>
+      </c>
+      <c r="F14" s="41">
+        <v>10857.125</v>
+      </c>
+      <c r="G14" s="41">
+        <v>11049.4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="46">
+        <v>0.5520049504950495</v>
+      </c>
+      <c r="D15" s="45">
+        <v>0.4233123178089621</v>
+      </c>
+      <c r="E15" s="45">
+        <v>0.2868207986281235</v>
+      </c>
+      <c r="F15" s="45">
+        <v>0.21567449946463726</v>
+      </c>
+      <c r="G15" s="45">
+        <v>0.16953716943906458</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="45">
+        <v>0.12814710042432814</v>
+      </c>
+      <c r="D16" s="45">
+        <v>0.10505864009219713</v>
+      </c>
+      <c r="E16" s="45">
+        <v>0.09135848848603624</v>
+      </c>
+      <c r="F16" s="45">
+        <v>0.08470612118769931</v>
+      </c>
+      <c r="G16" s="45">
+        <v>0.07992919031838833</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" s="46">
+        <v>0.020838048090523337</v>
+      </c>
+      <c r="D17" s="45">
+        <v>0.22649221521704743</v>
+      </c>
+      <c r="E17" s="45">
+        <v>0.40865090641842233</v>
+      </c>
+      <c r="F17" s="45">
+        <v>0.5019717632430317</v>
+      </c>
+      <c r="G17" s="45">
+        <v>0.5640321961663076</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="47">
+        <v>0.6319081672107103</v>
+      </c>
+      <c r="D18" s="48">
+        <v>10.747650235238861</v>
+      </c>
+      <c r="E18" s="48">
+        <v>28.61956160951256</v>
+      </c>
+      <c r="F18" s="48">
+        <v>46.752155680255555</v>
+      </c>
+      <c r="G18" s="48">
+        <v>66.82825457722186</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="37">
-        <v>780535</v>
-      </c>
-      <c r="D8" s="37">
-        <v>936642</v>
-      </c>
-      <c r="E8" s="37">
-        <v>936642</v>
-      </c>
-      <c r="F8" s="37">
-        <v>936642</v>
-      </c>
-      <c r="G8" s="37">
-        <v>936642</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="37">
-        <v>604000</v>
-      </c>
-      <c r="D9" s="37">
-        <v>774860</v>
-      </c>
-      <c r="E9" s="37">
-        <v>994467.6</v>
-      </c>
-      <c r="F9" s="37">
-        <v>1226219.9279999998</v>
-      </c>
-      <c r="G9" s="37">
-        <v>1471949.32584</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="37">
-        <v>46628.6108154935</v>
-      </c>
-      <c r="D10" s="37">
-        <v>46628.6108154935</v>
-      </c>
-      <c r="E10" s="37">
-        <v>46628.6108154935</v>
-      </c>
-      <c r="F10" s="37">
-        <v>46628.6108154935</v>
-      </c>
-      <c r="G10" s="37">
-        <v>46628.6108154935</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="38">
-        <v>-17163.6108154935</v>
-      </c>
-      <c r="D11" s="39">
-        <v>454519.3891845065</v>
-      </c>
-      <c r="E11" s="39">
-        <v>1287861.7891845065</v>
-      </c>
-      <c r="F11" s="39">
-        <v>2133359.461184507</v>
-      </c>
-      <c r="G11" s="39">
-        <v>3069480.0633445065</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="38">
-        <v>-17163.6108154935</v>
-      </c>
-      <c r="D12" s="39">
-        <v>437355.778369013</v>
-      </c>
-      <c r="E12" s="39">
-        <v>1725217.5675535195</v>
-      </c>
-      <c r="F12" s="39">
-        <v>3858577.0287380265</v>
-      </c>
-      <c r="G12" s="39">
-        <v>6928057.092082533</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13" s="40">
-        <v>-0.0121383386248186</v>
-      </c>
-      <c r="D13" s="41">
-        <v>0.20541856560436875</v>
-      </c>
-      <c r="E13" s="41">
-        <v>0.39437217944160535</v>
-      </c>
-      <c r="F13" s="41">
-        <v>0.49123489440908774</v>
-      </c>
-      <c r="G13" s="41">
-        <v>0.555592170315946</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="37">
-        <v>11783.333333333334</v>
-      </c>
-      <c r="D14" s="37">
-        <v>11063.25</v>
-      </c>
-      <c r="E14" s="37">
-        <v>10885.333333333334</v>
-      </c>
-      <c r="F14" s="37">
-        <v>10857.125</v>
-      </c>
-      <c r="G14" s="37">
-        <v>11049.4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="42">
-        <v>0.5520049504950495</v>
-      </c>
-      <c r="D15" s="41">
-        <v>0.4233123178089621</v>
-      </c>
-      <c r="E15" s="41">
-        <v>0.2868207986281235</v>
-      </c>
-      <c r="F15" s="41">
-        <v>0.21567449946463726</v>
-      </c>
-      <c r="G15" s="41">
-        <v>0.16953716943906458</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="C16" s="41">
-        <v>0.12814710042432814</v>
-      </c>
-      <c r="D16" s="41">
-        <v>0.10505864009219713</v>
-      </c>
-      <c r="E16" s="41">
-        <v>0.09135848848603624</v>
-      </c>
-      <c r="F16" s="41">
-        <v>0.08470612118769931</v>
-      </c>
-      <c r="G16" s="41">
-        <v>0.07992919031838833</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="42">
-        <v>0.020838048090523337</v>
-      </c>
-      <c r="D17" s="41">
-        <v>0.22649221521704743</v>
-      </c>
-      <c r="E17" s="41">
-        <v>0.40865090641842233</v>
-      </c>
-      <c r="F17" s="41">
-        <v>0.5019717632430317</v>
-      </c>
-      <c r="G17" s="41">
-        <v>0.5640321961663076</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C18" s="43">
-        <v>0.6319081672107103</v>
-      </c>
-      <c r="D18" s="44">
-        <v>10.747650235238861</v>
-      </c>
-      <c r="E18" s="44">
-        <v>28.61956160951256</v>
-      </c>
-      <c r="F18" s="44">
-        <v>46.752155680255555</v>
-      </c>
-      <c r="G18" s="44">
-        <v>66.82825457722186</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="C20" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
+      <c r="B20" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="G22" s="6"/>
+      <c r="B22" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="G23" s="50"/>
+      <c r="B23" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="E23" s="53"/>
+      <c r="F23" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="G23" s="54"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>266</v>
-      </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50" t="s">
+      <c r="B24" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="53"/>
+      <c r="F24" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="G24" s="54"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="G24" s="50"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="47" t="s">
-        <v>268</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="G25" s="50"/>
+      <c r="D25" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="E25" s="53"/>
+      <c r="F25" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="G25" s="54"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>272</v>
-      </c>
-      <c r="E26" s="49"/>
-      <c r="F26" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="G26" s="50"/>
+      <c r="B26" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="53"/>
+      <c r="F26" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" s="54"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>275</v>
-      </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="G27" s="50"/>
+      <c r="B27" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" s="53"/>
+      <c r="F27" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" s="54"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D28" s="49" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="G28" s="50"/>
+      <c r="B28" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54" t="s">
+        <v>285</v>
+      </c>
+      <c r="G28" s="54"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
-        <v>280</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D29" s="49" t="s">
-        <v>281</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" s="50"/>
+      <c r="B29" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="G29" s="54"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="B31" s="51" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
+      <c r="B33" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -6690,6 +6913,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="291">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1093,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1105,6 +1105,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1895,1108 +1896,1111 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <v>120</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <v>200</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <v>300</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <v>400</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="16">
         <v>500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <v>8500</v>
       </c>
-      <c r="E20" s="17">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
         <v>12</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="18">
         <v>1</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>750</v>
       </c>
-      <c r="E21" s="17">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="E21" s="18">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
         <v>12</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>1100</v>
       </c>
-      <c r="E22" s="17">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
         <v>12</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="18">
         <v>1</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>150000</v>
       </c>
-      <c r="E23" s="17">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="18">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
         <v>12</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="18">
         <v>1</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>25000</v>
       </c>
-      <c r="E24" s="17">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="E24" s="18">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
         <v>12</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="18">
         <v>1</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>400</v>
       </c>
-      <c r="E25" s="17">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
+      <c r="E25" s="18">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
         <v>12</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="18">
         <v>1</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>105000</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="18">
         <v>0.26</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="19">
         <v>1</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>82000</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="18">
         <v>0.26</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="19">
         <v>5</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>50000</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="18">
         <v>0.26</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="19">
         <v>1</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>53000</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="18">
         <v>0.26</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="19">
         <v>3</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="17">
         <v>28000</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="18">
         <v>0.18</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="19">
         <v>1</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="17">
         <v>62000</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="18">
         <v>0.26</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="19">
         <v>2</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="17">
         <v>36000</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="18">
         <v>0.22</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="18">
         <v>0.0765</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="10"/>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>22000</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G42" s="10"/>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <v>22000</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="18">
         <v>0.03</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="17">
         <v>3000</v>
       </c>
-      <c r="E44" s="17">
-        <v>0</v>
-      </c>
-      <c r="F44" s="11" t="s">
+      <c r="E44" s="18">
+        <v>0</v>
+      </c>
+      <c r="F44" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <v>22000</v>
       </c>
-      <c r="E45" s="17">
-        <v>0</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="E45" s="18">
+        <v>0</v>
+      </c>
+      <c r="F45" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <v>650</v>
       </c>
-      <c r="E46" s="17">
-        <v>0</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="E46" s="18">
+        <v>0</v>
+      </c>
+      <c r="F46" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <v>450</v>
       </c>
-      <c r="E47" s="17">
-        <v>0</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="E47" s="18">
+        <v>0</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="17">
         <v>30000</v>
       </c>
-      <c r="E48" s="17">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="E48" s="18">
+        <v>0</v>
+      </c>
+      <c r="F48" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <v>12000</v>
       </c>
-      <c r="E49" s="17">
-        <v>0</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="E49" s="18">
+        <v>0</v>
+      </c>
+      <c r="F49" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="17">
         <v>18000</v>
       </c>
-      <c r="E50" s="17">
-        <v>0</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="E50" s="18">
+        <v>0</v>
+      </c>
+      <c r="F50" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <v>750</v>
       </c>
-      <c r="E51" s="17">
-        <v>0</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="E51" s="18">
+        <v>0</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C54" s="19">
-        <v>0</v>
-      </c>
-      <c r="D54" s="16">
+      <c r="C54" s="20">
+        <v>0</v>
+      </c>
+      <c r="D54" s="17">
         <v>350000</v>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="21">
         <v>0.06</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <v>10</v>
       </c>
-      <c r="G54" s="19">
+      <c r="G54" s="20">
         <v>46629</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="17">
         <v>60000</v>
       </c>
-      <c r="D55" s="11">
-        <v>0</v>
-      </c>
-      <c r="E55" s="11" t="s">
+      <c r="D55" s="12">
+        <v>0</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="19">
         <v>0.8333333333333334</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="22" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="18">
         <v>0.03</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="13" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="23">
         <v>0.95</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="D72" s="23" t="s">
+      <c r="D72" s="24" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="17">
         <v>8200</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="17">
         <v>9100</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="17">
         <v>10500</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D75" s="23" t="s">
+      <c r="D75" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="E75" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="24" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="14">
         <v>80</v>
       </c>
-      <c r="C76" s="13">
+      <c r="C76" s="14">
         <v>130</v>
       </c>
-      <c r="D76" s="13">
+      <c r="D76" s="14">
         <v>180</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="14">
         <v>230</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="14">
         <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="14">
         <v>40</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C77" s="14">
         <v>70</v>
       </c>
-      <c r="D77" s="13">
+      <c r="D77" s="14">
         <v>100</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="14">
         <v>120</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B78" s="13">
-        <v>0</v>
-      </c>
-      <c r="C78" s="13">
-        <v>0</v>
-      </c>
-      <c r="D78" s="13">
+      <c r="B78" s="14">
+        <v>0</v>
+      </c>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
         <v>20</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="14">
         <v>50</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="14">
         <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3037,921 +3041,921 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>807500</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>1617850</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>2466200</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>3327850</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>4233200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>75000</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>153000</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>234000</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>318400</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>406000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>110000</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>224400</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>343200</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>466800</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>595500</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>125000</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>100000</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>50000</v>
       </c>
-      <c r="E9" s="19">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19">
+      <c r="E9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <v>20833</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>35000</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>45000</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>55000</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <v>65000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <v>40000</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>82400</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>127200</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>174800</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <v>225000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUM(B6:B11)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>SUM(C6:C11)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>SUM(D6:D11)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <f>SUM(E6:E11)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <f>SUM(F6:F11)</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>116944</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>140333</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>140333</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>140333</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>140333</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>91328</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>109593</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>109593</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>109593</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <v>109593</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>278438</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>334125</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>334125</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>334125</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>334125</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>59029</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>70835</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>70835</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>70835</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>70835</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>87955</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>105546</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>105546</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>105546</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>105546</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>69053</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <v>82863</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>82863</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <v>82863</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <v>82863</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>77790</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <v>93348</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>93348</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>93348</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <v>93348</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>SUM(B15:B21)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>SUM(C15:C21)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>SUM(D15:D21)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>SUM(E15:E21)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="28">
         <f>SUM(F15:F21)</f>
         <v>936642</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <v>65000</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <v>134000</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <v>207000</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <v>284000</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <v>366000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <v>65000</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>134000</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>207000</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <v>284000</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="30">
         <v>366000</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <v>45000</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <v>92800</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <v>143400</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <v>196800</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="20">
         <v>253500</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="30">
         <v>45000</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <v>92800</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <v>143400</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <v>196800</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="30">
         <v>253500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <v>220000</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>271920</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <v>280078</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <v>288480</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <v>297134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="20">
         <v>30000</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="20">
         <v>37080</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="20">
         <v>38196</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="20">
         <v>39336</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="20">
         <v>40524</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="20">
         <v>18333</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>22660</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <v>23340</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <v>24040</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <v>24761</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <v>268333</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <v>331660</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="30">
         <v>341614</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="30">
         <v>351856</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="30">
         <v>362419</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="20">
         <v>25000</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <v>30900</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="20">
         <v>31827</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>32782</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>33765</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="20">
         <v>10000</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="20">
         <v>12360</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="20">
         <v>12731</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <v>13113</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <v>13506</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="20">
         <v>15000</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="20">
         <v>18540</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="20">
         <v>19096</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <v>19669</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <v>20259</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="20">
         <v>75000</v>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="20">
         <v>154600</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="20">
         <v>238800</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <v>328000</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <v>422500</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <v>125000</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <v>216400</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>302454</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <v>393564</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <v>490030</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="28">
         <f>B27+B30+B35+B41</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>C27+C30+C35+C41</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="28">
         <f>D27+D30+D35+D41</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="28">
         <f>E27+E30+E35+E41</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="28">
         <f>F27+F30+F35+F41</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="20">
         <v>46629</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="20">
         <v>46629</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="20">
         <v>46629</v>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="20">
         <v>46629</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="20">
         <v>46629</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="20">
         <v>60000</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="20">
         <v>20000</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="20">
         <v>25000</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="20">
         <v>10000</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="20">
         <v>10000</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="28">
         <f>SUM(B45:B46)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="28">
         <f>SUM(C45:C46)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="28">
         <f>SUM(D45:D46)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="28">
         <f>SUM(E45:E46)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="28">
         <f>SUM(F45:F46)</f>
         <v>56629</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="30">
         <f>B12</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <f>C12</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="30">
         <f>D12</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="30">
         <f>E12</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="30">
         <f>F12</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="20">
         <f>B22</f>
         <v>780535</v>
       </c>
-      <c r="C51" s="19">
+      <c r="C51" s="20">
         <f>C22</f>
         <v>936642</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="20">
         <f>D22</f>
         <v>936642</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="20">
         <f>E22</f>
         <v>936642</v>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="20">
         <f>F22</f>
         <v>936642</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="20">
         <f>B42</f>
         <v>503333</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="20">
         <f>C42</f>
         <v>774860</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="20">
         <f>D42</f>
         <v>994468</v>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="20">
         <f>E42</f>
         <v>1226220</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="20">
         <f>F42</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="20">
         <f>B47</f>
         <v>106629</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="20">
         <f>C47</f>
         <v>66629</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="20">
         <f>D47</f>
         <v>71629</v>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="20">
         <f>E47</f>
         <v>56629</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="20">
         <f>F47</f>
         <v>56629</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="30">
         <f>B51+B52+B53</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="30">
         <f>C51+C52+C53</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="30">
         <f>D51+D52+D53</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="30">
         <f>E51+E52+E53</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="29">
+      <c r="F54" s="30">
         <f>F51+F52+F53</f>
         <v>2465220</v>
       </c>
@@ -3962,569 +3966,569 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <f>B50-B54</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <f>C50-C54</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <f>D50-D54</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <f>E50-E54</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <f>F50-F54</f>
         <v>3059480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="34">
         <f>IF(B50=0,"",B56/B50)</f>
         <v>-0.18</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <f>IF(C50=0,"",C56/C50)</f>
         <v>0.2</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <f>IF(D50=0,"",D56/D50)</f>
         <v>0.39</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <f>IF(E50=0,"",E56/E50)</f>
         <v>0.49</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <f>IF(F50=0,"",F56/F50)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="20">
         <f>B56</f>
         <v>-212164</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="20">
         <f>B58+C56</f>
         <v>222355</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="20">
         <f>C58+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="20">
         <f>D58+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="20">
         <f>E58+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="30">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="30">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="29">
+      <c r="D61" s="30">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="29">
+      <c r="E61" s="30">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="29">
+      <c r="F61" s="30">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="20">
         <f>B53</f>
         <v>106629</v>
       </c>
-      <c r="C62" s="19">
+      <c r="C62" s="20">
         <f>C53</f>
         <v>66629</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="20">
         <f>D53</f>
         <v>71629</v>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="20">
         <f>E53</f>
         <v>56629</v>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="20">
         <f>F53</f>
         <v>56629</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="25" t="s">
+      <c r="A63" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="B63" s="34">
+      <c r="B63" s="35">
         <f>IF(B62=0,"N/A",B61/B62)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <f>IF(C62=0,"N/A",C61/C62)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <f>IF(D62=0,"N/A",D61/D62)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <f>IF(E62=0,"N/A",E61/E62)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <f>IF(F62=0,"N/A",F61/F62)</f>
         <v>55.03</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="19" t="str">
+      <c r="B64" s="20" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C64" s="19">
+      <c r="C64" s="20">
         <f>B65</f>
         <v>-212164</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="20">
         <f>C65</f>
         <v>222355</v>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="20">
         <f>D65</f>
         <v>1485216</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="20">
         <f>E65</f>
         <v>3608575</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="25" t="s">
+      <c r="A65" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="30">
         <f>B64+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="30">
         <f>C64+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="29">
+      <c r="D65" s="30">
         <f>D64+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="29">
+      <c r="E65" s="30">
         <f>E64+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="29">
+      <c r="F65" s="30">
         <f>F64+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="36">
         <f>IF(B54=0,"",B65/B54*365)</f>
         <v>-56</v>
       </c>
-      <c r="C66" s="35">
+      <c r="C66" s="36">
         <f>IF(C54=0,"",C65/C54*365)</f>
         <v>46</v>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="36">
         <f>IF(D54=0,"",D65/D54*365)</f>
         <v>271</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="36">
         <f>IF(E54=0,"",E65/E54*365)</f>
         <v>593</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="36">
         <f>IF(F54=0,"",F65/F54*365)</f>
         <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B67" s="36">
+      <c r="B67" s="37">
         <f>IF(B54=0,"",B65/(B54/12))</f>
         <v>-1.8</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="37">
         <f>IF(C54=0,"",C65/(C54/12))</f>
         <v>1.5</v>
       </c>
-      <c r="D67" s="36">
+      <c r="D67" s="37">
         <f>IF(D54=0,"",D65/(D54/12))</f>
         <v>8.9</v>
       </c>
-      <c r="E67" s="36">
+      <c r="E67" s="37">
         <f>IF(E54=0,"",E65/(E54/12))</f>
         <v>19.5</v>
       </c>
-      <c r="F67" s="36">
+      <c r="F67" s="37">
         <f>IF(F54=0,"",F65/(F54/12))</f>
         <v>32.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="34">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B71" s="11" t="str">
+      <c r="B71" s="12" t="str">
         <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C71" s="11" t="str">
+      <c r="C71" s="12" t="str">
         <f>IF(C62=0,"N/A",IF(C63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D71" s="11" t="str">
+      <c r="D71" s="12" t="str">
         <f>IF(D62=0,"N/A",IF(D63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E71" s="11" t="str">
+      <c r="E71" s="12" t="str">
         <f>IF(E62=0,"N/A",IF(E63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F71" s="11" t="str">
+      <c r="F71" s="12" t="str">
         <f>IF(F62=0,"N/A",IF(F63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B72" s="11" t="str">
+      <c r="B72" s="12" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C72" s="11" t="str">
+      <c r="C72" s="12" t="str">
         <f>IF(C56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D72" s="11" t="str">
+      <c r="D72" s="12" t="str">
         <f>IF(D56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E72" s="11" t="str">
+      <c r="E72" s="12" t="str">
         <f>IF(E56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F72" s="11" t="str">
+      <c r="F72" s="12" t="str">
         <f>IF(F56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B73" s="11" t="str">
+      <c r="B73" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C73" s="11" t="str">
+      <c r="C73" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D73" s="11" t="str">
+      <c r="D73" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E73" s="11" t="str">
+      <c r="E73" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="F73" s="11" t="str">
+      <c r="F73" s="12" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B74" s="11" t="str">
+      <c r="B74" s="12" t="str">
         <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C74" s="11" t="str">
+      <c r="C74" s="12" t="str">
         <f>IF(C54=0,"N/A",IF(C65/(C54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D74" s="11" t="str">
+      <c r="D74" s="12" t="str">
         <f>IF(D54=0,"N/A",IF(D65/(D54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E74" s="11" t="str">
+      <c r="E74" s="12" t="str">
         <f>IF(E54=0,"N/A",IF(E65/(E54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F74" s="11" t="str">
+      <c r="F74" s="12" t="str">
         <f>IF(F54=0,"N/A",IF(F65/(F54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="19">
+      <c r="B77" s="20">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>9819</v>
       </c>
-      <c r="C77" s="19">
+      <c r="C77" s="20">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>11063</v>
       </c>
-      <c r="D77" s="19">
+      <c r="D77" s="20">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>10885</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="20">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>10857</v>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="20">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>11049</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B78" s="19">
+      <c r="B78" s="20">
         <f>IF(B3=0,"",B54/B3)</f>
         <v>11587</v>
       </c>
-      <c r="C78" s="19">
+      <c r="C78" s="20">
         <f>IF(C3=0,"",C54/C3)</f>
         <v>8891</v>
       </c>
-      <c r="D78" s="19">
+      <c r="D78" s="20">
         <f>IF(D3=0,"",D54/D3)</f>
         <v>6676</v>
       </c>
-      <c r="E78" s="19">
+      <c r="E78" s="20">
         <f>IF(E3=0,"",E54/E3)</f>
         <v>5549</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="20">
         <f>IF(F3=0,"",F54/F3)</f>
         <v>4930</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B79" s="19">
+      <c r="B79" s="20">
         <f>B51+B53</f>
         <v>887164</v>
       </c>
-      <c r="C79" s="19">
+      <c r="C79" s="20">
         <f>C51+C53</f>
         <v>1003271</v>
       </c>
-      <c r="D79" s="19">
+      <c r="D79" s="20">
         <f>D51+D53</f>
         <v>1008271</v>
       </c>
-      <c r="E79" s="19">
+      <c r="E79" s="20">
         <f>E51+E53</f>
         <v>993271</v>
       </c>
-      <c r="F79" s="19">
+      <c r="F79" s="20">
         <f>F51+F53</f>
         <v>993271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="19">
+      <c r="B80" s="20">
         <f>IF(B3=0,"",B52/B3)</f>
         <v>4194</v>
       </c>
-      <c r="C80" s="19">
+      <c r="C80" s="20">
         <f>IF(C3=0,"",C52/C3)</f>
         <v>3874</v>
       </c>
-      <c r="D80" s="19">
+      <c r="D80" s="20">
         <f>IF(D3=0,"",D52/D3)</f>
         <v>3315</v>
       </c>
-      <c r="E80" s="19">
+      <c r="E80" s="20">
         <f>IF(E3=0,"",E52/E3)</f>
         <v>3066</v>
       </c>
-      <c r="F80" s="19">
+      <c r="F80" s="20">
         <f>IF(F3=0,"",F52/F3)</f>
         <v>2944</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="19">
+      <c r="B81" s="20">
         <f>IF(B3=0,"",B77-B80)</f>
         <v>5625</v>
       </c>
-      <c r="C81" s="19">
+      <c r="C81" s="20">
         <f>IF(C3=0,"",C77-C80)</f>
         <v>7189</v>
       </c>
-      <c r="D81" s="19">
+      <c r="D81" s="20">
         <f>IF(D3=0,"",D77-D80)</f>
         <v>7570</v>
       </c>
-      <c r="E81" s="19">
+      <c r="E81" s="20">
         <f>IF(E3=0,"",E77-E80)</f>
         <v>7792</v>
       </c>
-      <c r="F81" s="19">
+      <c r="F81" s="20">
         <f>IF(F3=0,"",F77-F80)</f>
         <v>8106</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="37" t="s">
+      <c r="A82" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="B82" s="38">
+      <c r="B82" s="39">
         <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="38">
+      <c r="C82" s="39">
         <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="38">
+      <c r="D82" s="39">
         <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="38">
+      <c r="E82" s="39">
         <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="38">
+      <c r="F82" s="39">
         <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="24" t="s">
+      <c r="A84" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4572,390 +4576,390 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="24" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <v>96900</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="20">
         <v>96900</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <v>96900</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <v>96900</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="20">
         <v>96900</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <v>96900</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <v>96900</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="20">
         <v>96900</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="20">
         <v>96900</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="20">
         <v>96900</v>
       </c>
-      <c r="L4" s="19">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
+      <c r="L4" s="20">
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <v>0</v>
+      </c>
+      <c r="N4" s="20">
         <f>SUM(B4:M4)</f>
         <v>807500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <v>9000</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <v>9000</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>9000</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <v>9000</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <v>9000</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <v>9000</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <v>9000</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="20">
         <v>9000</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="20">
         <v>9000</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="20">
         <v>9000</v>
       </c>
-      <c r="L5" s="19">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
+      <c r="L5" s="20">
+        <v>0</v>
+      </c>
+      <c r="M5" s="20">
+        <v>0</v>
+      </c>
+      <c r="N5" s="20">
         <f>SUM(B5:M5)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>13200</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>13200</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>13200</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>13200</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>13200</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>13200</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>13200</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <v>13200</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="20">
         <v>13200</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <v>13200</v>
       </c>
-      <c r="L6" s="19">
-        <v>0</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19">
+      <c r="L6" s="20">
+        <v>0</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0</v>
+      </c>
+      <c r="N6" s="20">
         <f>SUM(B6:M6)</f>
         <v>110000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <v>15000</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>15000</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>15000</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>15000</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>15000</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="20">
         <v>15000</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <v>15000</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="20">
         <v>15000</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="20">
         <v>15000</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <v>15000</v>
       </c>
-      <c r="L7" s="19">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
+      <c r="L7" s="20">
+        <v>0</v>
+      </c>
+      <c r="M7" s="20">
+        <v>0</v>
+      </c>
+      <c r="N7" s="20">
         <f>SUM(B7:M7)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <v>2500</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>2500</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>2500</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>2500</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>2500</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="20">
         <v>2500</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <v>2500</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="20">
         <v>2500</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="20">
         <v>2500</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="20">
         <v>2500</v>
       </c>
-      <c r="L8" s="19">
-        <v>0</v>
-      </c>
-      <c r="M8" s="19">
-        <v>0</v>
-      </c>
-      <c r="N8" s="19">
+      <c r="L8" s="20">
+        <v>0</v>
+      </c>
+      <c r="M8" s="20">
+        <v>0</v>
+      </c>
+      <c r="N8" s="20">
         <f>SUM(B8:M8)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>4800</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>4800</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>4800</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>4800</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <v>4800</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="20">
         <v>4800</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <v>4800</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="20">
         <v>4800</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="20">
         <v>4800</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <v>4800</v>
       </c>
-      <c r="L9" s="19">
-        <v>0</v>
-      </c>
-      <c r="M9" s="19">
-        <v>0</v>
-      </c>
-      <c r="N9" s="19">
+      <c r="L9" s="20">
+        <v>0</v>
+      </c>
+      <c r="M9" s="20">
+        <v>0</v>
+      </c>
+      <c r="N9" s="20">
         <f>SUM(B9:M9)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="28">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="28">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="28">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="28">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="27" t="str">
+      <c r="L10" s="28" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="27" t="str">
+      <c r="M10" s="28" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="28">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
@@ -4966,391 +4970,391 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>11694</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>11694</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>11694</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <v>11694</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <v>11694</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <v>11694</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <v>11694</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <v>11694</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <v>11694</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <v>11694</v>
       </c>
-      <c r="L13" s="19">
-        <v>0</v>
-      </c>
-      <c r="M13" s="19">
-        <v>0</v>
-      </c>
-      <c r="N13" s="19">
+      <c r="L13" s="20">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0</v>
+      </c>
+      <c r="N13" s="20">
         <f>SUM(B13:M13)</f>
         <v>116944</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>9133</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>9133</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>9133</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <v>9133</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <v>9133</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <v>9133</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <v>9133</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <v>9133</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <v>9133</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <v>9133</v>
       </c>
-      <c r="L14" s="19">
-        <v>0</v>
-      </c>
-      <c r="M14" s="19">
-        <v>0</v>
-      </c>
-      <c r="N14" s="19">
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
         <f>SUM(B14:M14)</f>
         <v>91328</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>27844</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>27844</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>27844</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <v>27844</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>27844</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <v>27844</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <v>27844</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>27844</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <v>27844</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="20">
         <v>27844</v>
       </c>
-      <c r="L15" s="19">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19">
-        <v>0</v>
-      </c>
-      <c r="N15" s="19">
+      <c r="L15" s="20">
+        <v>0</v>
+      </c>
+      <c r="M15" s="20">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20">
         <f>SUM(B15:M15)</f>
         <v>278438</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>5903</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>5903</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>5903</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <v>5903</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <v>5903</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <v>5903</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <v>5903</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <v>5903</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <v>5903</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <v>5903</v>
       </c>
-      <c r="L16" s="19">
-        <v>0</v>
-      </c>
-      <c r="M16" s="19">
-        <v>0</v>
-      </c>
-      <c r="N16" s="19">
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
         <f>SUM(B16:M16)</f>
         <v>59029</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>8796</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>8796</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>8796</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>8796</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>8796</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="20">
         <v>8796</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <v>8796</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <v>8796</v>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="20">
         <v>8796</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="20">
         <v>8796</v>
       </c>
-      <c r="L17" s="19">
-        <v>0</v>
-      </c>
-      <c r="M17" s="19">
-        <v>0</v>
-      </c>
-      <c r="N17" s="19">
+      <c r="L17" s="20">
+        <v>0</v>
+      </c>
+      <c r="M17" s="20">
+        <v>0</v>
+      </c>
+      <c r="N17" s="20">
         <f>SUM(B17:M17)</f>
         <v>87955</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>6905</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>6905</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>6905</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>6905</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>6905</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <v>6905</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <v>6905</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <v>6905</v>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="20">
         <v>6905</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <v>6905</v>
       </c>
-      <c r="L18" s="19">
-        <v>0</v>
-      </c>
-      <c r="M18" s="19">
-        <v>0</v>
-      </c>
-      <c r="N18" s="19">
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
         <f>SUM(B18:M18)</f>
         <v>69053</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>7779</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="20">
         <v>7779</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>7779</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>7779</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>7779</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <v>7779</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <v>7779</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <v>7779</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="20">
         <v>7779</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="20">
         <v>7779</v>
       </c>
-      <c r="L19" s="19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19">
+      <c r="L19" s="20">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20">
+        <v>0</v>
+      </c>
+      <c r="N19" s="20">
         <f>SUM(B19:M19)</f>
         <v>77790</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="28">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="28">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="28">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="28">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="28">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="28">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="28">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="27" t="str">
+      <c r="L20" s="28" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="27" t="str">
+      <c r="M20" s="28" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N20" s="28">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
@@ -5361,733 +5365,733 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>6500</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <v>6500</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <v>6500</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <v>6500</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <v>6500</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <v>6500</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <v>6500</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <v>6500</v>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <v>6500</v>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <v>6500</v>
       </c>
-      <c r="L24" s="19">
-        <v>0</v>
-      </c>
-      <c r="M24" s="19">
-        <v>0</v>
-      </c>
-      <c r="N24" s="19">
+      <c r="L24" s="20">
+        <v>0</v>
+      </c>
+      <c r="M24" s="20">
+        <v>0</v>
+      </c>
+      <c r="N24" s="20">
         <f>SUM(B24:M24)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <v>6500</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>6500</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>6500</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>6500</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>6500</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <v>6500</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="30">
         <v>6500</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="30">
         <v>6500</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="30">
         <v>6500</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="30">
         <v>6500</v>
       </c>
-      <c r="L25" s="29">
-        <v>0</v>
-      </c>
-      <c r="M25" s="29">
-        <v>0</v>
-      </c>
-      <c r="N25" s="29">
+      <c r="L25" s="30">
+        <v>0</v>
+      </c>
+      <c r="M25" s="30">
+        <v>0</v>
+      </c>
+      <c r="N25" s="30">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <v>4500</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <v>4500</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <v>4500</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>4500</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <v>4500</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <v>4500</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <v>4500</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <v>4500</v>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="20">
         <v>4500</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="20">
         <v>4500</v>
       </c>
-      <c r="L27" s="19">
-        <v>0</v>
-      </c>
-      <c r="M27" s="19">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19">
+      <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20">
+        <v>0</v>
+      </c>
+      <c r="N27" s="20">
         <f>SUM(B27:M27)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="30">
         <v>4500</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <v>4500</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <v>4500</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <v>4500</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="30">
         <v>4500</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="30">
         <v>4500</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="30">
         <v>4500</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="30">
         <v>4500</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="30">
         <v>4500</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="30">
         <v>4500</v>
       </c>
-      <c r="L28" s="29">
-        <v>0</v>
-      </c>
-      <c r="M28" s="29">
-        <v>0</v>
-      </c>
-      <c r="N28" s="29">
+      <c r="L28" s="30">
+        <v>0</v>
+      </c>
+      <c r="M28" s="30">
+        <v>0</v>
+      </c>
+      <c r="N28" s="30">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="20">
         <v>22000</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="20">
         <v>22000</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="20">
         <v>22000</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <v>22000</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <v>22000</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="20">
         <v>22000</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <v>22000</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <v>22000</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="20">
         <v>22000</v>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="20">
         <v>22000</v>
       </c>
-      <c r="L30" s="19">
-        <v>0</v>
-      </c>
-      <c r="M30" s="19">
-        <v>0</v>
-      </c>
-      <c r="N30" s="19">
+      <c r="L30" s="20">
+        <v>0</v>
+      </c>
+      <c r="M30" s="20">
+        <v>0</v>
+      </c>
+      <c r="N30" s="20">
         <f>SUM(B30:M30)</f>
         <v>220000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="20">
         <v>3000</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <v>3000</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <v>3000</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <v>3000</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <v>3000</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="20">
         <v>3000</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="20">
         <v>3000</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <v>3000</v>
       </c>
-      <c r="J31" s="19">
+      <c r="J31" s="20">
         <v>3000</v>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="20">
         <v>3000</v>
       </c>
-      <c r="L31" s="19">
-        <v>0</v>
-      </c>
-      <c r="M31" s="19">
-        <v>0</v>
-      </c>
-      <c r="N31" s="19">
+      <c r="L31" s="20">
+        <v>0</v>
+      </c>
+      <c r="M31" s="20">
+        <v>0</v>
+      </c>
+      <c r="N31" s="20">
         <f>SUM(B31:M31)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="20">
         <v>1833</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <v>1833</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <v>1833</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <v>1833</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <v>1833</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="20">
         <v>1833</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="20">
         <v>1833</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <v>1833</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="20">
         <v>1833</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="20">
         <v>1833</v>
       </c>
-      <c r="L32" s="19">
-        <v>0</v>
-      </c>
-      <c r="M32" s="19">
-        <v>0</v>
-      </c>
-      <c r="N32" s="19">
+      <c r="L32" s="20">
+        <v>0</v>
+      </c>
+      <c r="M32" s="20">
+        <v>0</v>
+      </c>
+      <c r="N32" s="20">
         <f>SUM(B32:M32)</f>
         <v>18333</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <v>26833</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <v>26833</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <v>26833</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <v>26833</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="30">
         <v>26833</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="30">
         <v>26833</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="30">
         <v>26833</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="30">
         <v>26833</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="30">
         <v>26833</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="30">
         <v>26833</v>
       </c>
-      <c r="L33" s="29">
-        <v>0</v>
-      </c>
-      <c r="M33" s="29">
-        <v>0</v>
-      </c>
-      <c r="N33" s="29">
+      <c r="L33" s="30">
+        <v>0</v>
+      </c>
+      <c r="M33" s="30">
+        <v>0</v>
+      </c>
+      <c r="N33" s="30">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="20">
         <v>2500</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <v>2500</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="20">
         <v>2500</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <v>2500</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <v>2500</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="20">
         <v>2500</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="20">
         <v>2500</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <v>2500</v>
       </c>
-      <c r="J35" s="19">
+      <c r="J35" s="20">
         <v>2500</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="20">
         <v>2500</v>
       </c>
-      <c r="L35" s="19">
-        <v>0</v>
-      </c>
-      <c r="M35" s="19">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19">
+      <c r="L35" s="20">
+        <v>0</v>
+      </c>
+      <c r="M35" s="20">
+        <v>0</v>
+      </c>
+      <c r="N35" s="20">
         <f>SUM(B35:M35)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="20">
         <v>1000</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <v>1000</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <v>1000</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <v>1000</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <v>1000</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="20">
         <v>1000</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="20">
         <v>1000</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <v>1000</v>
       </c>
-      <c r="J36" s="19">
+      <c r="J36" s="20">
         <v>1000</v>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="20">
         <v>1000</v>
       </c>
-      <c r="L36" s="19">
-        <v>0</v>
-      </c>
-      <c r="M36" s="19">
-        <v>0</v>
-      </c>
-      <c r="N36" s="19">
+      <c r="L36" s="20">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0</v>
+      </c>
+      <c r="N36" s="20">
         <f>SUM(B36:M36)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="20">
         <v>1500</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <v>1500</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="20">
         <v>1500</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>1500</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>1500</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="20">
         <v>1500</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="20">
         <v>1500</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <v>1500</v>
       </c>
-      <c r="J37" s="19">
+      <c r="J37" s="20">
         <v>1500</v>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="20">
         <v>1500</v>
       </c>
-      <c r="L37" s="19">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
         <f>SUM(B37:M37)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="20">
         <v>7500</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="20">
         <v>7500</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="20">
         <v>7500</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <v>7500</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <v>7500</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="20">
         <v>7500</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="20">
         <v>7500</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <v>7500</v>
       </c>
-      <c r="J38" s="19">
+      <c r="J38" s="20">
         <v>7500</v>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="20">
         <v>7500</v>
       </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
+      <c r="L38" s="20">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
         <f>SUM(B38:M38)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <v>12500</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <v>12500</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <v>12500</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <v>12500</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="30">
         <v>12500</v>
       </c>
-      <c r="G39" s="29">
+      <c r="G39" s="30">
         <v>12500</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="30">
         <v>12500</v>
       </c>
-      <c r="I39" s="29">
+      <c r="I39" s="30">
         <v>12500</v>
       </c>
-      <c r="J39" s="29">
+      <c r="J39" s="30">
         <v>12500</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="30">
         <v>12500</v>
       </c>
-      <c r="L39" s="29">
-        <v>0</v>
-      </c>
-      <c r="M39" s="29">
-        <v>0</v>
-      </c>
-      <c r="N39" s="29">
+      <c r="L39" s="30">
+        <v>0</v>
+      </c>
+      <c r="M39" s="30">
+        <v>0</v>
+      </c>
+      <c r="N39" s="30">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="28">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="28">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="28">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="28">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="28">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="28">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="28">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="28">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="28">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="27">
+      <c r="K40" s="28">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="27" t="str">
+      <c r="L40" s="28" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="27" t="str">
+      <c r="M40" s="28" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="27">
+      <c r="N40" s="28">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
@@ -6098,46 +6102,46 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="20">
         <v>8886</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="20">
         <v>8886</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="20">
         <v>8886</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <v>8886</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <v>8886</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="20">
         <v>8886</v>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="20">
         <v>8886</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="20">
         <v>8886</v>
       </c>
-      <c r="J42" s="19">
+      <c r="J42" s="20">
         <v>8886</v>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <v>8886</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="20">
         <v>8886</v>
       </c>
-      <c r="M42" s="19">
+      <c r="M42" s="20">
         <v>8886</v>
       </c>
-      <c r="N42" s="19">
+      <c r="N42" s="20">
         <f>SUM(B42:M42)</f>
         <v>106629</v>
       </c>
@@ -6148,244 +6152,244 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="30">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="30">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="30">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="30">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="29">
+      <c r="G45" s="30">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="29">
+      <c r="H45" s="30">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="30">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="29">
+      <c r="J45" s="30">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="30">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="29">
+      <c r="L45" s="30">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="29">
+      <c r="M45" s="30">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="29">
+      <c r="N45" s="30">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="30">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="30">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="30">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="30">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="29">
+      <c r="G46" s="30">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="29">
+      <c r="H46" s="30">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="29">
+      <c r="I46" s="30">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="30">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="29">
+      <c r="K46" s="30">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="29">
+      <c r="L46" s="30">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="29">
+      <c r="M46" s="30">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="29">
+      <c r="N46" s="30">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="30">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="30">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="30">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="29">
+      <c r="G47" s="30">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="29">
+      <c r="H47" s="30">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="29">
+      <c r="I47" s="30">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="29">
+      <c r="J47" s="30">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="29">
+      <c r="K47" s="30">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="29">
+      <c r="L47" s="30">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="29">
+      <c r="M47" s="30">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="29">
+      <c r="N47" s="30">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="30">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="20">
         <f>MIN(B47:M47)</f>
         <v>9227</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="24"/>
-      <c r="N54" s="24"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6427,466 +6431,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="41">
         <v>120</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="41">
         <v>200</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="41">
         <v>300</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="41">
         <v>400</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="41">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="42">
         <v>1414000</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="42">
         <v>2212650</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="42">
         <v>3265600</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="42">
         <v>4342850</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="42">
         <v>5524700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="42">
         <v>780535</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="42">
         <v>936642</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="42">
         <v>936642</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="42">
         <v>936642</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="42">
         <v>936642</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="42">
         <v>604000</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <v>774860</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="42">
         <v>994467.6</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <v>1226219.9279999998</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="42">
         <v>1471949.32584</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="42">
         <v>46628.6108154935</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="42">
         <v>46628.6108154935</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="42">
         <v>46628.6108154935</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="42">
         <v>46628.6108154935</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="42">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="43">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <v>454519.3891845065</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <v>1287861.7891845065</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="44">
         <v>2133359.461184507</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <v>3069480.0633445065</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <v>437355.778369013</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="44">
         <v>1725217.5675535195</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="44">
         <v>3858577.0287380265</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>6928057.092082533</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="45">
         <v>-0.0121383386248186</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="46">
         <v>0.20541856560436875</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="46">
         <v>0.39437217944160535</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="46">
         <v>0.49123489440908774</v>
       </c>
-      <c r="G13" s="45">
+      <c r="G13" s="46">
         <v>0.555592170315946</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="42">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="42">
         <v>11063.25</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <v>10885.333333333334</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <v>10857.125</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="42">
         <v>11049.4</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="47">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <v>0.16953716943906458</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="46">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="46">
         <v>0.10505864009219713</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="46">
         <v>0.09135848848603624</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="46">
         <v>0.08470612118769931</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="46">
         <v>0.07992919031838833</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="47">
         <v>0.020838048090523337</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <v>0.22649221521704743</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <v>0.40865090641842233</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="46">
         <v>0.5019717632430317</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="46">
         <v>0.5640321961663076</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="48">
         <v>0.6319081672107103</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="49">
         <v>10.747650235238861</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="49">
         <v>28.61956160951256</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="49">
         <v>46.752155680255555</v>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="49">
         <v>66.82825457722186</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="54" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="G23" s="54"/>
+      <c r="G23" s="55"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="56" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="E24" s="53"/>
-      <c r="F24" s="54" t="s">
+      <c r="E24" s="54"/>
+      <c r="F24" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="G24" s="54"/>
+      <c r="G24" s="55"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="53"/>
-      <c r="F25" s="54" t="s">
+      <c r="E25" s="54"/>
+      <c r="F25" s="55" t="s">
         <v>276</v>
       </c>
-      <c r="G25" s="54"/>
+      <c r="G25" s="55"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54" t="s">
+      <c r="E26" s="54"/>
+      <c r="F26" s="55" t="s">
         <v>279</v>
       </c>
-      <c r="G26" s="54"/>
+      <c r="G26" s="55"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54" t="s">
+      <c r="E27" s="54"/>
+      <c r="F27" s="55" t="s">
         <v>282</v>
       </c>
-      <c r="G27" s="54"/>
+      <c r="G27" s="55"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54" t="s">
+      <c r="E28" s="54"/>
+      <c r="F28" s="55" t="s">
         <v>285</v>
       </c>
-      <c r="G28" s="54"/>
+      <c r="G28" s="55"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="52" t="s">
         <v>286</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54" t="s">
+      <c r="E29" s="54"/>
+      <c r="F29" s="55" t="s">
         <v>288</v>
       </c>
-      <c r="G29" s="54"/>
+      <c r="G29" s="55"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="292">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -122,7 +122,10 @@
     <t>Heritage Academy Charter - Financial Model Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells in this workbook are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1013,7 +1016,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1028,6 +1031,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1051,12 +1059,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1093,7 +1110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1107,82 +1124,83 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1896,1111 +1914,1117 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="D2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="A4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="13" t="s">
         <v>35</v>
       </c>
+      <c r="B6" s="14" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="13" t="s">
         <v>37</v>
       </c>
+      <c r="B7" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="13" t="s">
         <v>39</v>
       </c>
+      <c r="B8" s="14" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="15">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="17">
+        <v>120</v>
+      </c>
+      <c r="C17" s="17">
+        <v>200</v>
+      </c>
+      <c r="D17" s="17">
+        <v>300</v>
+      </c>
+      <c r="E17" s="17">
+        <v>400</v>
+      </c>
+      <c r="F17" s="17">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="18">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>12</v>
+      </c>
+      <c r="G20" s="19">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="18">
+        <v>750</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
+        <v>12</v>
+      </c>
+      <c r="G21" s="19">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>12</v>
+      </c>
+      <c r="G22" s="19">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="18">
+        <v>150000</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>12</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="18">
+        <v>25000</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15">
+        <v>12</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="18">
+        <v>400</v>
+      </c>
+      <c r="E25" s="19">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15">
+        <v>12</v>
+      </c>
+      <c r="G25" s="19">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="20">
+        <v>1</v>
+      </c>
+      <c r="E29" s="18">
+        <v>105000</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="20">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18">
+        <v>82000</v>
+      </c>
+      <c r="F30" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="G30" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="20">
+        <v>5</v>
+      </c>
+      <c r="E31" s="18">
+        <v>50000</v>
+      </c>
+      <c r="F31" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="20">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18">
+        <v>53000</v>
+      </c>
+      <c r="F32" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="G32" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="20">
+        <v>3</v>
+      </c>
+      <c r="E33" s="18">
+        <v>28000</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0.18</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="20">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18">
+        <v>62000</v>
+      </c>
+      <c r="F34" s="19">
+        <v>0.26</v>
+      </c>
+      <c r="G34" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="20">
+        <v>2</v>
+      </c>
+      <c r="E35" s="18">
+        <v>36000</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0.22</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0.0765</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="18">
+        <v>22000</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="18">
+        <v>22000</v>
+      </c>
+      <c r="E43" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="18">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="19">
+        <v>0</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" s="18">
+        <v>22000</v>
+      </c>
+      <c r="E45" s="19">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="18">
+        <v>650</v>
+      </c>
+      <c r="E46" s="19">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="18">
+        <v>450</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="18">
+        <v>30000</v>
+      </c>
+      <c r="E48" s="19">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="18">
+        <v>12000</v>
+      </c>
+      <c r="E49" s="19">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="18">
+        <v>18000</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="18">
+        <v>750</v>
+      </c>
+      <c r="E51" s="19">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="21">
+        <v>0</v>
+      </c>
+      <c r="D54" s="18">
+        <v>350000</v>
+      </c>
+      <c r="E54" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="F54" s="15">
+        <v>10</v>
+      </c>
+      <c r="G54" s="21">
+        <v>46629</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="18">
+        <v>60000</v>
+      </c>
+      <c r="D55" s="13">
+        <v>0</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="20">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="24">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" s="18">
+        <v>8200</v>
+      </c>
+      <c r="C73" s="18">
+        <v>9100</v>
+      </c>
+      <c r="D73" s="18">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E75" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="15">
+        <v>80</v>
+      </c>
+      <c r="C76" s="15">
+        <v>130</v>
+      </c>
+      <c r="D76" s="15">
+        <v>180</v>
+      </c>
+      <c r="E76" s="15">
+        <v>230</v>
+      </c>
+      <c r="F76" s="15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" s="15">
         <v>40</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="14">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="C77" s="15">
+        <v>70</v>
+      </c>
+      <c r="D77" s="15">
+        <v>100</v>
+      </c>
+      <c r="E77" s="15">
+        <v>120</v>
+      </c>
+      <c r="F77" s="15">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="15">
+        <v>0</v>
+      </c>
+      <c r="C78" s="15">
+        <v>0</v>
+      </c>
+      <c r="D78" s="15">
+        <v>20</v>
+      </c>
+      <c r="E78" s="15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="16">
-        <v>120</v>
-      </c>
-      <c r="C17" s="16">
-        <v>200</v>
-      </c>
-      <c r="D17" s="16">
-        <v>300</v>
-      </c>
-      <c r="E17" s="16">
-        <v>400</v>
-      </c>
-      <c r="F17" s="16">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="17">
-        <v>8500</v>
-      </c>
-      <c r="E20" s="18">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>12</v>
-      </c>
-      <c r="G20" s="18">
-        <v>1</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="17">
-        <v>750</v>
-      </c>
-      <c r="E21" s="18">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14">
-        <v>12</v>
-      </c>
-      <c r="G21" s="18">
-        <v>1</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="17">
-        <v>1100</v>
-      </c>
-      <c r="E22" s="18">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>12</v>
-      </c>
-      <c r="G22" s="18">
-        <v>1</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="17">
-        <v>150000</v>
-      </c>
-      <c r="E23" s="18">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="18">
-        <v>1</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="17">
-        <v>25000</v>
-      </c>
-      <c r="E24" s="18">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>12</v>
-      </c>
-      <c r="G24" s="18">
-        <v>1</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="17">
-        <v>400</v>
-      </c>
-      <c r="E25" s="18">
-        <v>0</v>
-      </c>
-      <c r="F25" s="14">
-        <v>12</v>
-      </c>
-      <c r="G25" s="18">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="19">
-        <v>1</v>
-      </c>
-      <c r="E29" s="17">
-        <v>105000</v>
-      </c>
-      <c r="F29" s="18">
-        <v>0.26</v>
-      </c>
-      <c r="G29" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="19">
-        <v>1</v>
-      </c>
-      <c r="E30" s="17">
-        <v>82000</v>
-      </c>
-      <c r="F30" s="18">
-        <v>0.26</v>
-      </c>
-      <c r="G30" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="19">
-        <v>5</v>
-      </c>
-      <c r="E31" s="17">
-        <v>50000</v>
-      </c>
-      <c r="F31" s="18">
-        <v>0.26</v>
-      </c>
-      <c r="G31" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="19">
-        <v>1</v>
-      </c>
-      <c r="E32" s="17">
-        <v>53000</v>
-      </c>
-      <c r="F32" s="18">
-        <v>0.26</v>
-      </c>
-      <c r="G32" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="19">
-        <v>3</v>
-      </c>
-      <c r="E33" s="17">
-        <v>28000</v>
-      </c>
-      <c r="F33" s="18">
-        <v>0.18</v>
-      </c>
-      <c r="G33" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="19">
-        <v>1</v>
-      </c>
-      <c r="E34" s="17">
-        <v>62000</v>
-      </c>
-      <c r="F34" s="18">
-        <v>0.26</v>
-      </c>
-      <c r="G34" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="19">
-        <v>2</v>
-      </c>
-      <c r="E35" s="17">
-        <v>36000</v>
-      </c>
-      <c r="F35" s="18">
-        <v>0.22</v>
-      </c>
-      <c r="G35" s="18">
-        <v>0.0765</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="11" t="s">
+      <c r="F78" s="15">
         <v>100</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" s="11"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="17">
-        <v>22000</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="18">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G42" s="11"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" s="17">
-        <v>22000</v>
-      </c>
-      <c r="E43" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="17">
-        <v>3000</v>
-      </c>
-      <c r="E44" s="18">
-        <v>0</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" s="17">
-        <v>22000</v>
-      </c>
-      <c r="E45" s="18">
-        <v>0</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="17">
-        <v>650</v>
-      </c>
-      <c r="E46" s="18">
-        <v>0</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="17">
-        <v>450</v>
-      </c>
-      <c r="E47" s="18">
-        <v>0</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="17">
-        <v>30000</v>
-      </c>
-      <c r="E48" s="18">
-        <v>0</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D49" s="17">
-        <v>12000</v>
-      </c>
-      <c r="E49" s="18">
-        <v>0</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="17">
-        <v>18000</v>
-      </c>
-      <c r="E50" s="18">
-        <v>0</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" s="17">
-        <v>750</v>
-      </c>
-      <c r="E51" s="18">
-        <v>0</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="20">
-        <v>0</v>
-      </c>
-      <c r="D54" s="17">
-        <v>350000</v>
-      </c>
-      <c r="E54" s="21">
-        <v>0.06</v>
-      </c>
-      <c r="F54" s="14">
-        <v>10</v>
-      </c>
-      <c r="G54" s="20">
-        <v>46629</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="17">
-        <v>60000</v>
-      </c>
-      <c r="D55" s="12">
-        <v>0</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="B60" s="19">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B61" s="18">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B63" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B68" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="B69" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B70" s="23">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B73" s="17">
-        <v>8200</v>
-      </c>
-      <c r="C73" s="17">
-        <v>9100</v>
-      </c>
-      <c r="D73" s="17">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D75" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="E75" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="F75" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" s="14">
-        <v>80</v>
-      </c>
-      <c r="C76" s="14">
-        <v>130</v>
-      </c>
-      <c r="D76" s="14">
-        <v>180</v>
-      </c>
-      <c r="E76" s="14">
-        <v>230</v>
-      </c>
-      <c r="F76" s="14">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="14">
-        <v>40</v>
-      </c>
-      <c r="C77" s="14">
-        <v>70</v>
-      </c>
-      <c r="D77" s="14">
-        <v>100</v>
-      </c>
-      <c r="E77" s="14">
-        <v>120</v>
-      </c>
-      <c r="F77" s="14">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="14">
-        <v>0</v>
-      </c>
-      <c r="C78" s="14">
-        <v>0</v>
-      </c>
-      <c r="D78" s="14">
-        <v>20</v>
-      </c>
-      <c r="E78" s="14">
-        <v>50</v>
-      </c>
-      <c r="F78" s="14">
-        <v>100</v>
-      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
+      <c r="A80" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3032,7 +3056,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3041,921 +3065,921 @@
       <c r="F1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="C2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>56</v>
       </c>
+      <c r="F2" s="25" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="28">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="28">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="28">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="28">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="28">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="21">
         <v>807500</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>1617850</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>2466200</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>3327850</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>4233200</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="21">
         <v>75000</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>153000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>234000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>318400</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>406000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="21">
         <v>110000</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <v>224400</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>343200</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>466800</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>595500</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="21">
         <v>125000</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <v>100000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>50000</v>
       </c>
-      <c r="E9" s="20">
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
+      <c r="E9" s="21">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="21">
         <v>20833</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <v>35000</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <v>45000</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>55000</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>65000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="21">
         <v>40000</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <v>82400</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <v>127200</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <v>174800</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <v>225000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="28">
+      <c r="A12" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="29">
         <f>SUM(B6:B11)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>SUM(C6:C11)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>SUM(D6:D11)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>SUM(E6:E11)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>SUM(F6:F11)</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="A14" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="21">
         <v>116944</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <v>140333</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>140333</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>140333</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>140333</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="21">
         <v>91328</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>109593</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>109593</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>109593</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>109593</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="A17" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="21">
         <v>278438</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>334125</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>334125</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>334125</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>334125</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="20">
+      <c r="A18" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="21">
         <v>59029</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <v>70835</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <v>70835</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <v>70835</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>70835</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="21">
         <v>87955</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>105546</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>105546</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>105546</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>105546</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="21">
         <v>69053</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <v>82863</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <v>82863</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <v>82863</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <v>82863</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="20">
+      <c r="A21" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="21">
         <v>77790</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <v>93348</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <v>93348</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <v>93348</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <v>93348</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" s="28">
+      <c r="A22" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="29">
         <f>SUM(B15:B21)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>SUM(C15:C21)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>SUM(D15:D21)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>SUM(E15:E21)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="29">
         <f>SUM(F15:F21)</f>
         <v>936642</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="A24" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="A25" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="20">
+      <c r="A26" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="21">
         <v>65000</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="21">
         <v>134000</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="21">
         <v>207000</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="21">
         <v>284000</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <v>366000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="31">
         <v>65000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>134000</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>207000</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>284000</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>366000</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B29" s="20">
+      <c r="A29" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="21">
         <v>45000</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="21">
         <v>92800</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="21">
         <v>143400</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="21">
         <v>196800</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="21">
         <v>253500</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30" s="30">
+      <c r="A30" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="31">
         <v>45000</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>92800</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>143400</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>196800</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>253500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="B32" s="20">
+      <c r="A32" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="21">
         <v>220000</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <v>271920</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <v>280078</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <v>288480</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <v>297134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B33" s="20">
+      <c r="A33" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" s="21">
         <v>30000</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="21">
         <v>37080</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="21">
         <v>38196</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <v>39336</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="21">
         <v>40524</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B34" s="20">
+      <c r="A34" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="21">
         <v>18333</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <v>22660</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <v>23340</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <v>24040</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <v>24761</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B35" s="30">
+      <c r="A35" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="31">
         <v>268333</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>331660</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>341614</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>351856</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>362419</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+      <c r="A36" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="20">
+      <c r="A37" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B37" s="21">
         <v>25000</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <v>30900</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="21">
         <v>31827</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <v>32782</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <v>33765</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B38" s="20">
+      <c r="A38" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="21">
         <v>10000</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="21">
         <v>12360</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="21">
         <v>12731</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="21">
         <v>13113</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="21">
         <v>13506</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B39" s="20">
+      <c r="A39" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="21">
         <v>15000</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="21">
         <v>18540</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="21">
         <v>19096</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="21">
         <v>19669</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="21">
         <v>20259</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B40" s="20">
+      <c r="A40" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="21">
         <v>75000</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="21">
         <v>154600</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="21">
         <v>238800</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="21">
         <v>328000</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="21">
         <v>422500</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="B41" s="30">
+      <c r="A41" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="31">
         <v>125000</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="31">
         <v>216400</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="31">
         <v>302454</v>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="31">
         <v>393564</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <v>490030</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B42" s="28">
+      <c r="A42" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="29">
         <f>B27+B30+B35+B41</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>C27+C30+C35+C41</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="29">
         <f>D27+D30+D35+D41</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="28">
+      <c r="E42" s="29">
         <f>E27+E30+E35+E41</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="29">
         <f>F27+F30+F35+F41</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
+      <c r="A44" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="20">
+      <c r="A45" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="21">
         <v>46629</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="21">
         <v>46629</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D45" s="21">
         <v>46629</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="21">
         <v>46629</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="21">
         <v>46629</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B46" s="20">
+      <c r="A46" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="21">
         <v>60000</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="21">
         <v>20000</v>
       </c>
-      <c r="D46" s="20">
+      <c r="D46" s="21">
         <v>25000</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="21">
         <v>10000</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="21">
         <v>10000</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B47" s="28">
+      <c r="A47" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="29">
         <f>SUM(B45:B46)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="29">
         <f>SUM(C45:C46)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="29">
         <f>SUM(D45:D46)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="28">
+      <c r="E47" s="29">
         <f>SUM(E45:E46)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="28">
+      <c r="F47" s="29">
         <f>SUM(F45:F46)</f>
         <v>56629</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
+      <c r="A49" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B50" s="30">
+      <c r="A50" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="31">
         <f>B12</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <f>C12</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="31">
         <f>D12</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="31">
         <f>E12</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="31">
         <f>F12</f>
         <v>5524700</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B51" s="20">
+      <c r="A51" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="21">
         <f>B22</f>
         <v>780535</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="21">
         <f>C22</f>
         <v>936642</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="21">
         <f>D22</f>
         <v>936642</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="21">
         <f>E22</f>
         <v>936642</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="21">
         <f>F22</f>
         <v>936642</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B52" s="20">
+      <c r="A52" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="21">
         <f>B42</f>
         <v>503333</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="21">
         <f>C42</f>
         <v>774860</v>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="21">
         <f>D42</f>
         <v>994468</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="21">
         <f>E42</f>
         <v>1226220</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="21">
         <f>F42</f>
         <v>1471949</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B53" s="20">
+      <c r="A53" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="21">
         <f>B47</f>
         <v>106629</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="21">
         <f>C47</f>
         <v>66629</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="21">
         <f>D47</f>
         <v>71629</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <f>E47</f>
         <v>56629</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="21">
         <f>F47</f>
         <v>56629</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="B54" s="30">
+      <c r="A54" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="31">
         <f>B51+B52+B53</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <f>C51+C52+C53</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="31">
         <f>D51+D52+D53</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="30">
+      <c r="E54" s="31">
         <f>E51+E52+E53</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="30">
+      <c r="F54" s="31">
         <f>F51+F52+F53</f>
         <v>2465220</v>
       </c>
@@ -3966,569 +3990,569 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B56" s="33">
         <f>B50-B54</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <f>C50-C54</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <f>D50-D54</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <f>E50-E54</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <f>F50-F54</f>
         <v>3059480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B57" s="34">
+      <c r="A57" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="35">
         <f>IF(B50=0,"",B56/B50)</f>
         <v>-0.18</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <f>IF(C50=0,"",C56/C50)</f>
         <v>0.2</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <f>IF(D50=0,"",D56/D50)</f>
         <v>0.39</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <f>IF(E50=0,"",E56/E50)</f>
         <v>0.49</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <f>IF(F50=0,"",F56/F50)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B58" s="20">
+      <c r="A58" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="21">
         <f>B56</f>
         <v>-212164</v>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="21">
         <f>B58+C56</f>
         <v>222355</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="21">
         <f>C58+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="21">
         <f>D58+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="21">
         <f>E58+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
+      <c r="A60" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B61" s="30">
+      <c r="A61" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" s="31">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="31">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="31">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="31">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="30">
+      <c r="F61" s="31">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B62" s="20">
+      <c r="A62" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" s="21">
         <f>B53</f>
         <v>106629</v>
       </c>
-      <c r="C62" s="20">
+      <c r="C62" s="21">
         <f>C53</f>
         <v>66629</v>
       </c>
-      <c r="D62" s="20">
+      <c r="D62" s="21">
         <f>D53</f>
         <v>71629</v>
       </c>
-      <c r="E62" s="20">
+      <c r="E62" s="21">
         <f>E53</f>
         <v>56629</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="21">
         <f>F53</f>
         <v>56629</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B63" s="35">
+      <c r="A63" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" s="36">
         <f>IF(B62=0,"N/A",B61/B62)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="35">
+      <c r="C63" s="36">
         <f>IF(C62=0,"N/A",C61/C62)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="35">
+      <c r="D63" s="36">
         <f>IF(D62=0,"N/A",D61/D62)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="35">
+      <c r="E63" s="36">
         <f>IF(E62=0,"N/A",E61/E62)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="36">
         <f>IF(F62=0,"N/A",F61/F62)</f>
         <v>55.03</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" s="20" t="str">
+      <c r="A64" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="21" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C64" s="20">
+      <c r="C64" s="21">
         <f>B65</f>
         <v>-212164</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="21">
         <f>C65</f>
         <v>222355</v>
       </c>
-      <c r="E64" s="20">
+      <c r="E64" s="21">
         <f>D65</f>
         <v>1485216</v>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="21">
         <f>E65</f>
         <v>3608575</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="B65" s="30">
+      <c r="A65" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="31">
         <f>B64+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C65" s="31">
         <f>C64+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="31">
         <f>D64+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="30">
+      <c r="E65" s="31">
         <f>E64+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="31">
         <f>F64+F56</f>
         <v>6668055</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B66" s="36">
+      <c r="A66" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" s="37">
         <f>IF(B54=0,"",B65/B54*365)</f>
         <v>-56</v>
       </c>
-      <c r="C66" s="36">
+      <c r="C66" s="37">
         <f>IF(C54=0,"",C65/C54*365)</f>
         <v>46</v>
       </c>
-      <c r="D66" s="36">
+      <c r="D66" s="37">
         <f>IF(D54=0,"",D65/D54*365)</f>
         <v>271</v>
       </c>
-      <c r="E66" s="36">
+      <c r="E66" s="37">
         <f>IF(E54=0,"",E65/E54*365)</f>
         <v>593</v>
       </c>
-      <c r="F66" s="36">
+      <c r="F66" s="37">
         <f>IF(F54=0,"",F65/F54*365)</f>
         <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B67" s="37">
+      <c r="A67" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="38">
         <f>IF(B54=0,"",B65/(B54/12))</f>
         <v>-1.8</v>
       </c>
-      <c r="C67" s="37">
+      <c r="C67" s="38">
         <f>IF(C54=0,"",C65/(C54/12))</f>
         <v>1.5</v>
       </c>
-      <c r="D67" s="37">
+      <c r="D67" s="38">
         <f>IF(D54=0,"",D65/(D54/12))</f>
         <v>8.9</v>
       </c>
-      <c r="E67" s="37">
+      <c r="E67" s="38">
         <f>IF(E54=0,"",E65/(E54/12))</f>
         <v>19.5</v>
       </c>
-      <c r="F67" s="37">
+      <c r="F67" s="38">
         <f>IF(F54=0,"",F65/(F54/12))</f>
         <v>32.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68" s="35">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
+      <c r="A70" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B71" s="12" t="str">
+      <c r="A71" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B71" s="13" t="str">
         <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C71" s="12" t="str">
+      <c r="C71" s="13" t="str">
         <f>IF(C62=0,"N/A",IF(C63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="D71" s="12" t="str">
+      <c r="D71" s="13" t="str">
         <f>IF(D62=0,"N/A",IF(D63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E71" s="12" t="str">
+      <c r="E71" s="13" t="str">
         <f>IF(E62=0,"N/A",IF(E63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F71" s="12" t="str">
+      <c r="F71" s="13" t="str">
         <f>IF(F62=0,"N/A",IF(F63&gt;=1.2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="B72" s="12" t="str">
+      <c r="A72" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" s="13" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C72" s="12" t="str">
+      <c r="C72" s="13" t="str">
         <f>IF(C56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D72" s="12" t="str">
+      <c r="D72" s="13" t="str">
         <f>IF(D56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E72" s="12" t="str">
+      <c r="E72" s="13" t="str">
         <f>IF(E56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F72" s="12" t="str">
+      <c r="F72" s="13" t="str">
         <f>IF(F56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B73" s="12" t="str">
+      <c r="A73" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B73" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C73" s="12" t="str">
+      <c r="C73" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D73" s="12" t="str">
+      <c r="D73" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E73" s="12" t="str">
+      <c r="E73" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="F73" s="12" t="str">
+      <c r="F73" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B74" s="12" t="str">
+      <c r="A74" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" s="13" t="str">
         <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C74" s="12" t="str">
+      <c r="C74" s="13" t="str">
         <f>IF(C54=0,"N/A",IF(C65/(C54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D74" s="12" t="str">
+      <c r="D74" s="13" t="str">
         <f>IF(D54=0,"N/A",IF(D65/(D54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E74" s="12" t="str">
+      <c r="E74" s="13" t="str">
         <f>IF(E54=0,"N/A",IF(E65/(E54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F74" s="12" t="str">
+      <c r="F74" s="13" t="str">
         <f>IF(F54=0,"N/A",IF(F65/(F54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
+      <c r="A76" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B77" s="20">
+      <c r="A77" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B77" s="21">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>9819</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C77" s="21">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>11063</v>
       </c>
-      <c r="D77" s="20">
+      <c r="D77" s="21">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>10885</v>
       </c>
-      <c r="E77" s="20">
+      <c r="E77" s="21">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>10857</v>
       </c>
-      <c r="F77" s="20">
+      <c r="F77" s="21">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>11049</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B78" s="20">
+      <c r="A78" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" s="21">
         <f>IF(B3=0,"",B54/B3)</f>
         <v>11587</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C78" s="21">
         <f>IF(C3=0,"",C54/C3)</f>
         <v>8891</v>
       </c>
-      <c r="D78" s="20">
+      <c r="D78" s="21">
         <f>IF(D3=0,"",D54/D3)</f>
         <v>6676</v>
       </c>
-      <c r="E78" s="20">
+      <c r="E78" s="21">
         <f>IF(E3=0,"",E54/E3)</f>
         <v>5549</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="21">
         <f>IF(F3=0,"",F54/F3)</f>
         <v>4930</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B79" s="20">
+      <c r="A79" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B79" s="21">
         <f>B51+B53</f>
         <v>887164</v>
       </c>
-      <c r="C79" s="20">
+      <c r="C79" s="21">
         <f>C51+C53</f>
         <v>1003271</v>
       </c>
-      <c r="D79" s="20">
+      <c r="D79" s="21">
         <f>D51+D53</f>
         <v>1008271</v>
       </c>
-      <c r="E79" s="20">
+      <c r="E79" s="21">
         <f>E51+E53</f>
         <v>993271</v>
       </c>
-      <c r="F79" s="20">
+      <c r="F79" s="21">
         <f>F51+F53</f>
         <v>993271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="B80" s="20">
+      <c r="A80" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" s="21">
         <f>IF(B3=0,"",B52/B3)</f>
         <v>4194</v>
       </c>
-      <c r="C80" s="20">
+      <c r="C80" s="21">
         <f>IF(C3=0,"",C52/C3)</f>
         <v>3874</v>
       </c>
-      <c r="D80" s="20">
+      <c r="D80" s="21">
         <f>IF(D3=0,"",D52/D3)</f>
         <v>3315</v>
       </c>
-      <c r="E80" s="20">
+      <c r="E80" s="21">
         <f>IF(E3=0,"",E52/E3)</f>
         <v>3066</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="21">
         <f>IF(F3=0,"",F52/F3)</f>
         <v>2944</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B81" s="20">
+      <c r="A81" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="21">
         <f>IF(B3=0,"",B77-B80)</f>
         <v>5625</v>
       </c>
-      <c r="C81" s="20">
+      <c r="C81" s="21">
         <f>IF(C3=0,"",C77-C80)</f>
         <v>7189</v>
       </c>
-      <c r="D81" s="20">
+      <c r="D81" s="21">
         <f>IF(D3=0,"",D77-D80)</f>
         <v>7570</v>
       </c>
-      <c r="E81" s="20">
+      <c r="E81" s="21">
         <f>IF(E3=0,"",E77-E80)</f>
         <v>7792</v>
       </c>
-      <c r="F81" s="20">
+      <c r="F81" s="21">
         <f>IF(F3=0,"",F77-F80)</f>
         <v>8106</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="B82" s="39">
+      <c r="A82" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B82" s="40">
         <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="39">
+      <c r="C82" s="40">
         <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="39">
+      <c r="D82" s="40">
         <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="39">
+      <c r="E82" s="40">
         <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="39">
+      <c r="F82" s="40">
         <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
         <v>123</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
+      <c r="A84" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4559,7 +4583,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4576,390 +4600,390 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="D2" s="24" t="s">
+      <c r="B2" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="G2" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="H2" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="I2" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="J2" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="K2" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="L2" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="M2" s="25" t="s">
         <v>224</v>
       </c>
+      <c r="N2" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="A3" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="20">
+      <c r="A4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="21">
         <v>96900</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>96900</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>96900</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>96900</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>96900</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <v>96900</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="21">
         <v>96900</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="21">
         <v>96900</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="21">
         <v>96900</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="21">
         <v>96900</v>
       </c>
-      <c r="L4" s="20">
-        <v>0</v>
-      </c>
-      <c r="M4" s="20">
-        <v>0</v>
-      </c>
-      <c r="N4" s="20">
+      <c r="L4" s="21">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21">
         <f>SUM(B4:M4)</f>
         <v>807500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="20">
+      <c r="A5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="21">
         <v>9000</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <v>9000</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>9000</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>9000</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>9000</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <v>9000</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="21">
         <v>9000</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <v>9000</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="21">
         <v>9000</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="21">
         <v>9000</v>
       </c>
-      <c r="L5" s="20">
-        <v>0</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
+      <c r="L5" s="21">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21">
         <f>SUM(B5:M5)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="20">
+      <c r="A6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="21">
         <v>13200</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>13200</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>13200</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>13200</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>13200</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <v>13200</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <v>13200</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <v>13200</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <v>13200</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="21">
         <v>13200</v>
       </c>
-      <c r="L6" s="20">
-        <v>0</v>
-      </c>
-      <c r="M6" s="20">
-        <v>0</v>
-      </c>
-      <c r="N6" s="20">
+      <c r="L6" s="21">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21">
         <f>SUM(B6:M6)</f>
         <v>110000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="20">
+      <c r="A7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="21">
         <v>15000</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <v>15000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>15000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>15000</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>15000</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <v>15000</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="21">
         <v>15000</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <v>15000</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="21">
         <v>15000</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="21">
         <v>15000</v>
       </c>
-      <c r="L7" s="20">
-        <v>0</v>
-      </c>
-      <c r="M7" s="20">
-        <v>0</v>
-      </c>
-      <c r="N7" s="20">
+      <c r="L7" s="21">
+        <v>0</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21">
         <f>SUM(B7:M7)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="20">
+      <c r="A8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="21">
         <v>2500</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <v>2500</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>2500</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>2500</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>2500</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <v>2500</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="21">
         <v>2500</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <v>2500</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="21">
         <v>2500</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="21">
         <v>2500</v>
       </c>
-      <c r="L8" s="20">
-        <v>0</v>
-      </c>
-      <c r="M8" s="20">
-        <v>0</v>
-      </c>
-      <c r="N8" s="20">
+      <c r="L8" s="21">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21">
         <f>SUM(B8:M8)</f>
         <v>20833</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="20">
+      <c r="A9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="21">
         <v>4800</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <v>4800</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>4800</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <v>4800</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>4800</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <v>4800</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="21">
         <v>4800</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <v>4800</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="21">
         <v>4800</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="21">
         <v>4800</v>
       </c>
-      <c r="L9" s="20">
-        <v>0</v>
-      </c>
-      <c r="M9" s="20">
-        <v>0</v>
-      </c>
-      <c r="N9" s="20">
+      <c r="L9" s="21">
+        <v>0</v>
+      </c>
+      <c r="M9" s="21">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21">
         <f>SUM(B9:M9)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="28">
+      <c r="A10" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="29">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="28" t="str">
+      <c r="L10" s="29" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="28" t="str">
+      <c r="M10" s="29" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
@@ -4970,391 +4994,391 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="A12" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="20">
+      <c r="A13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="21">
         <v>11694</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <v>11694</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>11694</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <v>11694</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <v>11694</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <v>11694</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <v>11694</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <v>11694</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <v>11694</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="21">
         <v>11694</v>
       </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
+      <c r="L13" s="21">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21">
         <f>SUM(B13:M13)</f>
         <v>116944</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="21">
         <v>9133</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <v>9133</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>9133</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>9133</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <v>9133</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <v>9133</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <v>9133</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="21">
         <v>9133</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <v>9133</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="21">
         <v>9133</v>
       </c>
-      <c r="L14" s="20">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20">
-        <v>0</v>
-      </c>
-      <c r="N14" s="20">
+      <c r="L14" s="21">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21">
         <f>SUM(B14:M14)</f>
         <v>91328</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="20">
+      <c r="A15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="21">
         <v>27844</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <v>27844</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>27844</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <v>27844</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>27844</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <v>27844</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <v>27844</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="21">
         <v>27844</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="21">
         <v>27844</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K15" s="21">
         <v>27844</v>
       </c>
-      <c r="L15" s="20">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0</v>
-      </c>
-      <c r="N15" s="20">
+      <c r="L15" s="21">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21">
         <f>SUM(B15:M15)</f>
         <v>278438</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="20">
+      <c r="A16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="21">
         <v>5903</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>5903</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>5903</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <v>5903</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>5903</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <v>5903</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <v>5903</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <v>5903</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <v>5903</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="21">
         <v>5903</v>
       </c>
-      <c r="L16" s="20">
-        <v>0</v>
-      </c>
-      <c r="M16" s="20">
-        <v>0</v>
-      </c>
-      <c r="N16" s="20">
+      <c r="L16" s="21">
+        <v>0</v>
+      </c>
+      <c r="M16" s="21">
+        <v>0</v>
+      </c>
+      <c r="N16" s="21">
         <f>SUM(B16:M16)</f>
         <v>59029</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="A17" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="21">
         <v>8796</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>8796</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>8796</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>8796</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>8796</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="21">
         <v>8796</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="21">
         <v>8796</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="21">
         <v>8796</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="21">
         <v>8796</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="21">
         <v>8796</v>
       </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
-      <c r="M17" s="20">
-        <v>0</v>
-      </c>
-      <c r="N17" s="20">
+      <c r="L17" s="21">
+        <v>0</v>
+      </c>
+      <c r="M17" s="21">
+        <v>0</v>
+      </c>
+      <c r="N17" s="21">
         <f>SUM(B17:M17)</f>
         <v>87955</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="20">
+      <c r="A18" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="21">
         <v>6905</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <v>6905</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <v>6905</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <v>6905</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>6905</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <v>6905</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="21">
         <v>6905</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="21">
         <v>6905</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="21">
         <v>6905</v>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="21">
         <v>6905</v>
       </c>
-      <c r="L18" s="20">
-        <v>0</v>
-      </c>
-      <c r="M18" s="20">
-        <v>0</v>
-      </c>
-      <c r="N18" s="20">
+      <c r="L18" s="21">
+        <v>0</v>
+      </c>
+      <c r="M18" s="21">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21">
         <f>SUM(B18:M18)</f>
         <v>69053</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="21">
         <v>7779</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>7779</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>7779</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="21">
         <v>7779</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>7779</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="21">
         <v>7779</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="21">
         <v>7779</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="21">
         <v>7779</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="21">
         <v>7779</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="21">
         <v>7779</v>
       </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
+      <c r="L19" s="21">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21">
         <f>SUM(B19:M19)</f>
         <v>77790</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B20" s="28">
+      <c r="A20" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="29">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="29">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="29">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="28">
+      <c r="I20" s="29">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="28">
+      <c r="J20" s="29">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="28" t="str">
+      <c r="L20" s="29" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="28" t="str">
+      <c r="M20" s="29" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="28">
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
@@ -5365,733 +5389,733 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
+      <c r="A22" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
+      <c r="A23" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B24" s="20">
+      <c r="A24" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B24" s="21">
         <v>6500</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="21">
         <v>6500</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="21">
         <v>6500</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <v>6500</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="21">
         <v>6500</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="21">
         <v>6500</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="21">
         <v>6500</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="21">
         <v>6500</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="21">
         <v>6500</v>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="21">
         <v>6500</v>
       </c>
-      <c r="L24" s="20">
-        <v>0</v>
-      </c>
-      <c r="M24" s="20">
-        <v>0</v>
-      </c>
-      <c r="N24" s="20">
+      <c r="L24" s="21">
+        <v>0</v>
+      </c>
+      <c r="M24" s="21">
+        <v>0</v>
+      </c>
+      <c r="N24" s="21">
         <f>SUM(B24:M24)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="31">
         <v>6500</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>6500</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>6500</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>6500</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>6500</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>6500</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>6500</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>6500</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>6500</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>6500</v>
       </c>
-      <c r="L25" s="30">
-        <v>0</v>
-      </c>
-      <c r="M25" s="30">
-        <v>0</v>
-      </c>
-      <c r="N25" s="30">
+      <c r="L25" s="31">
+        <v>0</v>
+      </c>
+      <c r="M25" s="31">
+        <v>0</v>
+      </c>
+      <c r="N25" s="31">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
+      <c r="A26" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="20">
+      <c r="A27" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="21">
         <v>4500</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="21">
         <v>4500</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <v>4500</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="21">
         <v>4500</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <v>4500</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="21">
         <v>4500</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="21">
         <v>4500</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="21">
         <v>4500</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="21">
         <v>4500</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="21">
         <v>4500</v>
       </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20">
-        <v>0</v>
-      </c>
-      <c r="N27" s="20">
+      <c r="L27" s="21">
+        <v>0</v>
+      </c>
+      <c r="M27" s="21">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21">
         <f>SUM(B27:M27)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" s="31">
         <v>4500</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>4500</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>4500</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>4500</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>4500</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>4500</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="31">
         <v>4500</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>4500</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="31">
         <v>4500</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <v>4500</v>
       </c>
-      <c r="L28" s="30">
-        <v>0</v>
-      </c>
-      <c r="M28" s="30">
-        <v>0</v>
-      </c>
-      <c r="N28" s="30">
+      <c r="L28" s="31">
+        <v>0</v>
+      </c>
+      <c r="M28" s="31">
+        <v>0</v>
+      </c>
+      <c r="N28" s="31">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
+      <c r="A29" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" s="20">
+      <c r="A30" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B30" s="21">
         <v>22000</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="21">
         <v>22000</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="21">
         <v>22000</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="21">
         <v>22000</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="21">
         <v>22000</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="21">
         <v>22000</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="21">
         <v>22000</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="21">
         <v>22000</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="21">
         <v>22000</v>
       </c>
-      <c r="K30" s="20">
+      <c r="K30" s="21">
         <v>22000</v>
       </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
+      <c r="L30" s="21">
+        <v>0</v>
+      </c>
+      <c r="M30" s="21">
+        <v>0</v>
+      </c>
+      <c r="N30" s="21">
         <f>SUM(B30:M30)</f>
         <v>220000</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="B31" s="20">
+      <c r="A31" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="21">
         <v>3000</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="21">
         <v>3000</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="21">
         <v>3000</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="21">
         <v>3000</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="21">
         <v>3000</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="21">
         <v>3000</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="21">
         <v>3000</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="21">
         <v>3000</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="21">
         <v>3000</v>
       </c>
-      <c r="K31" s="20">
+      <c r="K31" s="21">
         <v>3000</v>
       </c>
-      <c r="L31" s="20">
-        <v>0</v>
-      </c>
-      <c r="M31" s="20">
-        <v>0</v>
-      </c>
-      <c r="N31" s="20">
+      <c r="L31" s="21">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21">
+        <v>0</v>
+      </c>
+      <c r="N31" s="21">
         <f>SUM(B31:M31)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="B32" s="20">
+      <c r="A32" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B32" s="21">
         <v>1833</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <v>1833</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <v>1833</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <v>1833</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <v>1833</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <v>1833</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="21">
         <v>1833</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="21">
         <v>1833</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="21">
         <v>1833</v>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="21">
         <v>1833</v>
       </c>
-      <c r="L32" s="20">
-        <v>0</v>
-      </c>
-      <c r="M32" s="20">
-        <v>0</v>
-      </c>
-      <c r="N32" s="20">
+      <c r="L32" s="21">
+        <v>0</v>
+      </c>
+      <c r="M32" s="21">
+        <v>0</v>
+      </c>
+      <c r="N32" s="21">
         <f>SUM(B32:M32)</f>
         <v>18333</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B33" s="30">
+      <c r="A33" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="31">
         <v>26833</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <v>26833</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="31">
         <v>26833</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="31">
         <v>26833</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="31">
         <v>26833</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <v>26833</v>
       </c>
-      <c r="H33" s="30">
+      <c r="H33" s="31">
         <v>26833</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="31">
         <v>26833</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="31">
         <v>26833</v>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="31">
         <v>26833</v>
       </c>
-      <c r="L33" s="30">
-        <v>0</v>
-      </c>
-      <c r="M33" s="30">
-        <v>0</v>
-      </c>
-      <c r="N33" s="30">
+      <c r="L33" s="31">
+        <v>0</v>
+      </c>
+      <c r="M33" s="31">
+        <v>0</v>
+      </c>
+      <c r="N33" s="31">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
+      <c r="A34" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="B35" s="20">
+      <c r="A35" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="21">
         <v>2500</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <v>2500</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="21">
         <v>2500</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <v>2500</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <v>2500</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <v>2500</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="21">
         <v>2500</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="21">
         <v>2500</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J35" s="21">
         <v>2500</v>
       </c>
-      <c r="K35" s="20">
+      <c r="K35" s="21">
         <v>2500</v>
       </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>0</v>
-      </c>
-      <c r="N35" s="20">
+      <c r="L35" s="21">
+        <v>0</v>
+      </c>
+      <c r="M35" s="21">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21">
         <f>SUM(B35:M35)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B36" s="20">
+      <c r="A36" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B36" s="21">
         <v>1000</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="21">
         <v>1000</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="21">
         <v>1000</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="21">
         <v>1000</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="21">
         <v>1000</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="21">
         <v>1000</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="21">
         <v>1000</v>
       </c>
-      <c r="I36" s="20">
+      <c r="I36" s="21">
         <v>1000</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="21">
         <v>1000</v>
       </c>
-      <c r="K36" s="20">
+      <c r="K36" s="21">
         <v>1000</v>
       </c>
-      <c r="L36" s="20">
-        <v>0</v>
-      </c>
-      <c r="M36" s="20">
-        <v>0</v>
-      </c>
-      <c r="N36" s="20">
+      <c r="L36" s="21">
+        <v>0</v>
+      </c>
+      <c r="M36" s="21">
+        <v>0</v>
+      </c>
+      <c r="N36" s="21">
         <f>SUM(B36:M36)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="B37" s="20">
+      <c r="A37" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" s="21">
         <v>1500</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="21">
         <v>1500</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="21">
         <v>1500</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="21">
         <v>1500</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="21">
         <v>1500</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="21">
         <v>1500</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="21">
         <v>1500</v>
       </c>
-      <c r="I37" s="20">
+      <c r="I37" s="21">
         <v>1500</v>
       </c>
-      <c r="J37" s="20">
+      <c r="J37" s="21">
         <v>1500</v>
       </c>
-      <c r="K37" s="20">
+      <c r="K37" s="21">
         <v>1500</v>
       </c>
-      <c r="L37" s="20">
-        <v>0</v>
-      </c>
-      <c r="M37" s="20">
-        <v>0</v>
-      </c>
-      <c r="N37" s="20">
+      <c r="L37" s="21">
+        <v>0</v>
+      </c>
+      <c r="M37" s="21">
+        <v>0</v>
+      </c>
+      <c r="N37" s="21">
         <f>SUM(B37:M37)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B38" s="20">
+      <c r="A38" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="21">
         <v>7500</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="21">
         <v>7500</v>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="21">
         <v>7500</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="21">
         <v>7500</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="21">
         <v>7500</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="21">
         <v>7500</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="21">
         <v>7500</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="21">
         <v>7500</v>
       </c>
-      <c r="J38" s="20">
+      <c r="J38" s="21">
         <v>7500</v>
       </c>
-      <c r="K38" s="20">
+      <c r="K38" s="21">
         <v>7500</v>
       </c>
-      <c r="L38" s="20">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20">
-        <v>0</v>
-      </c>
-      <c r="N38" s="20">
+      <c r="L38" s="21">
+        <v>0</v>
+      </c>
+      <c r="M38" s="21">
+        <v>0</v>
+      </c>
+      <c r="N38" s="21">
         <f>SUM(B38:M38)</f>
         <v>75000</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="B39" s="30">
+      <c r="A39" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="31">
         <v>12500</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <v>12500</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <v>12500</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <v>12500</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <v>12500</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="31">
         <v>12500</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="31">
         <v>12500</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="31">
         <v>12500</v>
       </c>
-      <c r="J39" s="30">
+      <c r="J39" s="31">
         <v>12500</v>
       </c>
-      <c r="K39" s="30">
+      <c r="K39" s="31">
         <v>12500</v>
       </c>
-      <c r="L39" s="30">
-        <v>0</v>
-      </c>
-      <c r="M39" s="30">
-        <v>0</v>
-      </c>
-      <c r="N39" s="30">
+      <c r="L39" s="31">
+        <v>0</v>
+      </c>
+      <c r="M39" s="31">
+        <v>0</v>
+      </c>
+      <c r="N39" s="31">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B40" s="28">
+      <c r="A40" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B40" s="29">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="29">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="28">
+      <c r="E40" s="29">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="29">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="28">
+      <c r="G40" s="29">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="29">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="28">
+      <c r="I40" s="29">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="28">
+      <c r="J40" s="29">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="28">
+      <c r="K40" s="29">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="28" t="str">
+      <c r="L40" s="29" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="28" t="str">
+      <c r="M40" s="29" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="28">
+      <c r="N40" s="29">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
@@ -6102,46 +6126,46 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="B42" s="20">
+      <c r="A42" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="21">
         <v>8886</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="21">
         <v>8886</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="21">
         <v>8886</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="21">
         <v>8886</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="21">
         <v>8886</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="21">
         <v>8886</v>
       </c>
-      <c r="H42" s="20">
+      <c r="H42" s="21">
         <v>8886</v>
       </c>
-      <c r="I42" s="20">
+      <c r="I42" s="21">
         <v>8886</v>
       </c>
-      <c r="J42" s="20">
+      <c r="J42" s="21">
         <v>8886</v>
       </c>
-      <c r="K42" s="20">
+      <c r="K42" s="21">
         <v>8886</v>
       </c>
-      <c r="L42" s="20">
+      <c r="L42" s="21">
         <v>8886</v>
       </c>
-      <c r="M42" s="20">
+      <c r="M42" s="21">
         <v>8886</v>
       </c>
-      <c r="N42" s="20">
+      <c r="N42" s="21">
         <f>SUM(B42:M42)</f>
         <v>106629</v>
       </c>
@@ -6152,244 +6176,244 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
+      <c r="A44" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="B45" s="30">
+      <c r="A45" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B45" s="31">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="31">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="31">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="31">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="30">
+      <c r="F45" s="31">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="31">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="30">
+      <c r="H45" s="31">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="30">
+      <c r="I45" s="31">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="30">
+      <c r="J45" s="31">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="30">
+      <c r="K45" s="31">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="30">
+      <c r="L45" s="31">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="30">
+      <c r="M45" s="31">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="30">
+      <c r="N45" s="31">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="B46" s="30">
+      <c r="A46" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="31">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="31">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="31">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="31">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="31">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="31">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="30">
+      <c r="H46" s="31">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="30">
+      <c r="I46" s="31">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="30">
+      <c r="J46" s="31">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="30">
+      <c r="K46" s="31">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="30">
+      <c r="L46" s="31">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="30">
+      <c r="M46" s="31">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="30">
+      <c r="N46" s="31">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B47" s="30">
+      <c r="A47" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="B47" s="31">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="31">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="31">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="31">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="31">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="31">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="30">
+      <c r="H47" s="31">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="30">
+      <c r="I47" s="31">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="30">
+      <c r="J47" s="31">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="30">
+      <c r="K47" s="31">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="30">
+      <c r="L47" s="31">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="30">
+      <c r="M47" s="31">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="30">
+      <c r="N47" s="31">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
+      <c r="A49" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B50" s="20">
+      <c r="A50" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B51" s="30">
+      <c r="A51" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B51" s="31">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B52" s="20">
+      <c r="A52" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" s="21">
         <f>MIN(B47:M47)</f>
         <v>9227</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
+      <c r="A54" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6422,7 +6446,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6431,466 +6455,466 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
+      <c r="B3" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="16" t="s">
         <v>248</v>
       </c>
+      <c r="G5" s="16" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" s="41">
+      <c r="B6" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="42">
         <v>120</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="42">
         <v>200</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="42">
         <v>300</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="42">
         <v>400</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="42">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="42">
+      <c r="B7" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" s="43">
         <v>1414000</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>2212650</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="43">
         <v>3265600</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="43">
         <v>4342850</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="43">
         <v>5524700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C8" s="42">
+      <c r="B8" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="43">
         <v>780535</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <v>936642</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="43">
         <v>936642</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="43">
         <v>936642</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="43">
         <v>936642</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="42">
+      <c r="B9" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="43">
         <v>604000</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <v>774860</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="43">
         <v>994467.6</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="43">
         <v>1226219.9279999998</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="43">
         <v>1471949.32584</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="42">
+      <c r="B10" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="43">
         <v>46628.6108154935</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <v>46628.6108154935</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <v>46628.6108154935</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="43">
         <v>46628.6108154935</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="43">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="43">
+      <c r="B11" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="44">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="45">
         <v>454519.3891845065</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="45">
         <v>1287861.7891845065</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="45">
         <v>2133359.461184507</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="45">
         <v>3069480.0633445065</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="43">
+      <c r="B12" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="44">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="45">
         <v>437355.778369013</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <v>1725217.5675535195</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="45">
         <v>3858577.0287380265</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="45">
         <v>6928057.092082533</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13" s="45">
+      <c r="B13" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="46">
         <v>-0.0121383386248186</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="47">
         <v>0.20541856560436875</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="47">
         <v>0.39437217944160535</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="47">
         <v>0.49123489440908774</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="47">
         <v>0.555592170315946</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="42">
+      <c r="B14" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="43">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="43">
         <v>11063.25</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="43">
         <v>10885.333333333334</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="43">
         <v>10857.125</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="43">
         <v>11049.4</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="47">
+      <c r="B15" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="48">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="47">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="47">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="47">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="47">
         <v>0.16953716943906458</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="46">
+      <c r="B16" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" s="47">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="47">
         <v>0.10505864009219713</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="47">
         <v>0.09135848848603624</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="47">
         <v>0.08470612118769931</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="47">
         <v>0.07992919031838833</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="47">
+      <c r="B17" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="48">
         <v>0.020838048090523337</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="47">
         <v>0.22649221521704743</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="47">
         <v>0.40865090641842233</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="47">
         <v>0.5019717632430317</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="47">
         <v>0.5640321961663076</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="B18" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C18" s="49">
         <v>0.6319081672107103</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="50">
         <v>10.747650235238861</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="50">
         <v>28.61956160951256</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="50">
         <v>46.752155680255555</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="50">
         <v>66.82825457722186</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
+      <c r="B19" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="C20" s="51" t="s">
+      <c r="B20" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
+      <c r="C20" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="C23" s="53" t="s">
+      <c r="B23" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="C23" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="55" t="s">
+      <c r="D23" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="G23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="G23" s="56"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="52" t="s">
-        <v>270</v>
-      </c>
-      <c r="C24" s="56" t="s">
+      <c r="B24" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="C24" s="57" t="s">
         <v>272</v>
       </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="55" t="s">
+      <c r="D24" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="G24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="G24" s="56"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="52" t="s">
-        <v>274</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25" s="54" t="s">
+      <c r="B25" s="53" t="s">
         <v>275</v>
       </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55" t="s">
+      <c r="C25" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D25" s="55" t="s">
         <v>276</v>
       </c>
-      <c r="G25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="G25" s="56"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="52" t="s">
-        <v>277</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D26" s="54" t="s">
+      <c r="B26" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="55" t="s">
+      <c r="C26" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D26" s="55" t="s">
         <v>279</v>
       </c>
-      <c r="G26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="G26" s="56"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D27" s="54" t="s">
+      <c r="B27" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55" t="s">
+      <c r="C27" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" s="55" t="s">
         <v>282</v>
       </c>
-      <c r="G27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" s="56"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D28" s="54" t="s">
+      <c r="B28" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55" t="s">
+      <c r="C28" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" s="55" t="s">
         <v>285</v>
       </c>
-      <c r="G28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="56" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="56"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="C29" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D29" s="54" t="s">
+      <c r="B29" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55" t="s">
+      <c r="C29" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="55" t="s">
         <v>288</v>
       </c>
-      <c r="G29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="G29" s="56"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="C31" s="26" t="s">
+      <c r="B31" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="C31" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
+      <c r="B33" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$G33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="304">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -761,6 +761,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -779,6 +788,9 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Enrollment</t>
   </si>
   <si>
@@ -797,18 +809,39 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
   </si>
   <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -816,6 +849,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -916,7 +952,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1015,6 +1051,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1110,7 +1152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1161,6 +1203,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1179,9 +1224,14 @@
     <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1210,7 +1260,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6432,19 +6503,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>242</v>
       </c>
@@ -6453,8 +6525,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="41" t="s">
         <v>243</v>
       </c>
@@ -6463,559 +6536,632 @@
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
       <c r="G3" s="41"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+      <c r="H3" s="41"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D4" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="F4" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="16" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="E6" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="42">
-        <v>120</v>
-      </c>
-      <c r="D6" s="42">
-        <v>200</v>
-      </c>
-      <c r="E6" s="42">
-        <v>300</v>
-      </c>
-      <c r="F6" s="42">
-        <v>400</v>
-      </c>
-      <c r="G6" s="42">
-        <v>500</v>
+      <c r="F6" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="43">
-        <v>1414000</v>
-      </c>
-      <c r="D7" s="43">
-        <v>2212650</v>
-      </c>
-      <c r="E7" s="43">
-        <v>3265600</v>
-      </c>
-      <c r="F7" s="43">
-        <v>4342850</v>
-      </c>
-      <c r="G7" s="43">
-        <v>5524700</v>
+        <v>254</v>
+      </c>
+      <c r="C7" s="45">
+        <v>120</v>
+      </c>
+      <c r="D7" s="45">
+        <v>200</v>
+      </c>
+      <c r="E7" s="45">
+        <v>300</v>
+      </c>
+      <c r="F7" s="45">
+        <v>400</v>
+      </c>
+      <c r="G7" s="45">
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="43">
-        <v>780535</v>
-      </c>
-      <c r="D8" s="43">
-        <v>936642</v>
-      </c>
-      <c r="E8" s="43">
-        <v>936642</v>
-      </c>
-      <c r="F8" s="43">
-        <v>936642</v>
-      </c>
-      <c r="G8" s="43">
-        <v>936642</v>
+        <v>255</v>
+      </c>
+      <c r="C8" s="46">
+        <v>1414000</v>
+      </c>
+      <c r="D8" s="46">
+        <v>2212650</v>
+      </c>
+      <c r="E8" s="46">
+        <v>3265600</v>
+      </c>
+      <c r="F8" s="46">
+        <v>4342850</v>
+      </c>
+      <c r="G8" s="46">
+        <v>5524700</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="43">
-        <v>604000</v>
-      </c>
-      <c r="D9" s="43">
-        <v>774860</v>
-      </c>
-      <c r="E9" s="43">
-        <v>994467.6</v>
-      </c>
-      <c r="F9" s="43">
-        <v>1226219.9279999998</v>
-      </c>
-      <c r="G9" s="43">
-        <v>1471949.32584</v>
+        <v>256</v>
+      </c>
+      <c r="C9" s="46">
+        <v>780535</v>
+      </c>
+      <c r="D9" s="46">
+        <v>936642</v>
+      </c>
+      <c r="E9" s="46">
+        <v>936642</v>
+      </c>
+      <c r="F9" s="46">
+        <v>936642</v>
+      </c>
+      <c r="G9" s="46">
+        <v>936642</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="46">
+        <v>604000</v>
+      </c>
+      <c r="D10" s="46">
+        <v>774860</v>
+      </c>
+      <c r="E10" s="46">
+        <v>994467.6</v>
+      </c>
+      <c r="F10" s="46">
+        <v>1226219.9279999998</v>
+      </c>
+      <c r="G10" s="46">
+        <v>1471949.32584</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C11" s="46">
         <v>46628.6108154935</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D11" s="46">
         <v>46628.6108154935</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E11" s="46">
         <v>46628.6108154935</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F11" s="46">
         <v>46628.6108154935</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G11" s="46">
         <v>46628.6108154935</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="44">
-        <v>-17163.6108154935</v>
-      </c>
-      <c r="D11" s="45">
-        <v>454519.3891845065</v>
-      </c>
-      <c r="E11" s="45">
-        <v>1287861.7891845065</v>
-      </c>
-      <c r="F11" s="45">
-        <v>2133359.461184507</v>
-      </c>
-      <c r="G11" s="45">
-        <v>3069480.0633445065</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="44">
+        <v>190</v>
+      </c>
+      <c r="C12" s="47">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D12" s="45">
-        <v>437355.778369013</v>
-      </c>
-      <c r="E12" s="45">
-        <v>1725217.5675535195</v>
-      </c>
-      <c r="F12" s="45">
-        <v>3858577.0287380265</v>
-      </c>
-      <c r="G12" s="45">
-        <v>6928057.092082533</v>
+      <c r="D12" s="48">
+        <v>454519.3891845065</v>
+      </c>
+      <c r="E12" s="48">
+        <v>1287861.7891845065</v>
+      </c>
+      <c r="F12" s="48">
+        <v>2133359.461184507</v>
+      </c>
+      <c r="G12" s="48">
+        <v>3069480.0633445065</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="46">
-        <v>-0.0121383386248186</v>
-      </c>
-      <c r="D13" s="47">
-        <v>0.20541856560436875</v>
-      </c>
-      <c r="E13" s="47">
-        <v>0.39437217944160535</v>
-      </c>
-      <c r="F13" s="47">
-        <v>0.49123489440908774</v>
-      </c>
-      <c r="G13" s="47">
-        <v>0.555592170315946</v>
+        <v>197</v>
+      </c>
+      <c r="C13" s="47">
+        <v>-17163.6108154935</v>
+      </c>
+      <c r="D13" s="48">
+        <v>437355.778369013</v>
+      </c>
+      <c r="E13" s="48">
+        <v>1725217.5675535195</v>
+      </c>
+      <c r="F13" s="48">
+        <v>3858577.0287380265</v>
+      </c>
+      <c r="G13" s="48">
+        <v>6928057.092082533</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="43">
+        <v>258</v>
+      </c>
+      <c r="C14" s="49">
+        <v>-0.0121383386248186</v>
+      </c>
+      <c r="D14" s="50">
+        <v>0.20541856560436875</v>
+      </c>
+      <c r="E14" s="50">
+        <v>0.39437217944160535</v>
+      </c>
+      <c r="F14" s="50">
+        <v>0.49123489440908774</v>
+      </c>
+      <c r="G14" s="50">
+        <v>0.555592170315946</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="51">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D15" s="51">
         <v>11063.25</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E15" s="51">
         <v>10885.333333333334</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F15" s="51">
         <v>10857.125</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G15" s="51">
         <v>11049.4</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="48">
+      <c r="H15" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="53">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D16" s="50">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E16" s="50">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F16" s="50">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G16" s="50">
         <v>0.16953716943906458</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C16" s="47">
+      <c r="H16" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="50">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D17" s="50">
         <v>0.10505864009219713</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E17" s="50">
         <v>0.09135848848603624</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F17" s="50">
         <v>0.08470612118769931</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G17" s="50">
         <v>0.07992919031838833</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C17" s="48">
+      <c r="H17" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="53">
         <v>0.020838048090523337</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D18" s="50">
         <v>0.22649221521704743</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E18" s="50">
         <v>0.40865090641842233</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F18" s="50">
         <v>0.5019717632430317</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G18" s="50">
         <v>0.5640321961663076</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="49">
+      <c r="H18" s="52" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="54">
+        <v>1</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="52" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="55">
         <v>0.6319081672107103</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D20" s="56">
         <v>10.747650235238861</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E20" s="56">
         <v>28.61956160951256</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F20" s="56">
         <v>46.752155680255555</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G20" s="56">
         <v>66.82825457722186</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D23" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="E23" s="55"/>
-      <c r="F23" s="56" t="s">
+      <c r="H20" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="G23" s="56"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="53" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C21" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="52" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="C22" s="58" t="s">
         <v>273</v>
       </c>
-      <c r="E24" s="55"/>
-      <c r="F24" s="56" t="s">
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="G24" s="56"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="53" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D25" s="55" t="s">
+      <c r="C24" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56" t="s">
+      <c r="D24" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="G25" s="56"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="53" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C26" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D26" s="55" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="59" t="s">
         <v>279</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="56" t="s">
+      <c r="C25" s="60" t="s">
         <v>280</v>
       </c>
-      <c r="G26" s="56"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
+      <c r="D25" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="C27" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D27" s="55" t="s">
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="55"/>
-      <c r="F27" s="56" t="s">
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="G27" s="56"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="53" t="s">
+      <c r="C26" s="63" t="s">
         <v>284</v>
       </c>
-      <c r="C28" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D28" s="55" t="s">
+      <c r="D26" s="61" t="s">
         <v>285</v>
       </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56" t="s">
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>286</v>
       </c>
-      <c r="G28" s="56"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="53" t="s">
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="59" t="s">
         <v>287</v>
       </c>
-      <c r="C29" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="D29" s="55" t="s">
+      <c r="C27" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="61" t="s">
         <v>288</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="56" t="s">
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="G29" s="56"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="53" t="s">
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
         <v>290</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C28" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="61" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="58" t="s">
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>294</v>
+      </c>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="59" t="s">
+        <v>296</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>297</v>
+      </c>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="C31" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>300</v>
+      </c>
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="64" t="s">
         <v>155</v>
       </c>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F85</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="306">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -606,6 +606,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>CASH FLOW &amp; DEBT COVERAGE</t>
@@ -1040,14 +1046,14 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF6B7280"/>
+      <b/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF16A34A"/>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1152,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1197,13 +1203,19 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1227,27 +1239,24 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3118,7 +3127,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -4135,500 +4144,520 @@
         <v>6668055</v>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
+      <c r="B59" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="B61" s="31">
+      <c r="D59" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B62" s="31">
         <f>B50-B51-B52</f>
         <v>-105535</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C62" s="31">
         <f>C50-C51-C52</f>
         <v>501148</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D62" s="31">
         <f>D50-D51-D52</f>
         <v>1334490</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E62" s="31">
         <f>E50-E51-E52</f>
         <v>2179988</v>
       </c>
-      <c r="F61" s="31">
+      <c r="F62" s="31">
         <f>F50-F51-F52</f>
         <v>3116109</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B62" s="21">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" s="21">
         <f>B53</f>
         <v>106629</v>
       </c>
-      <c r="C62" s="21">
+      <c r="C63" s="21">
         <f>C53</f>
         <v>66629</v>
       </c>
-      <c r="D62" s="21">
+      <c r="D63" s="21">
         <f>D53</f>
         <v>71629</v>
       </c>
-      <c r="E62" s="21">
+      <c r="E63" s="21">
         <f>E53</f>
         <v>56629</v>
       </c>
-      <c r="F62" s="21">
+      <c r="F63" s="21">
         <f>F53</f>
         <v>56629</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="B63" s="36">
-        <f>IF(B62=0,"N/A",B61/B62)</f>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="38">
+        <f>IF(B63=0,"N/A",B62/B63)</f>
         <v>-0.99</v>
       </c>
-      <c r="C63" s="36">
-        <f>IF(C62=0,"N/A",C61/C62)</f>
+      <c r="C64" s="38">
+        <f>IF(C63=0,"N/A",C62/C63)</f>
         <v>7.52</v>
       </c>
-      <c r="D63" s="36">
-        <f>IF(D62=0,"N/A",D61/D62)</f>
+      <c r="D64" s="38">
+        <f>IF(D63=0,"N/A",D62/D63)</f>
         <v>18.63</v>
       </c>
-      <c r="E63" s="36">
-        <f>IF(E62=0,"N/A",E61/E62)</f>
+      <c r="E64" s="38">
+        <f>IF(E63=0,"N/A",E62/E63)</f>
         <v>38.5</v>
       </c>
-      <c r="F63" s="36">
-        <f>IF(F62=0,"N/A",F61/F62)</f>
+      <c r="F64" s="38">
+        <f>IF(F63=0,"N/A",F62/F63)</f>
         <v>55.03</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B64" s="21" t="str">
+      <c r="B65" s="21" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C64" s="21">
-        <f>B65</f>
+      <c r="C65" s="21">
+        <f>B66</f>
         <v>-212164</v>
       </c>
-      <c r="D64" s="21">
-        <f>C65</f>
+      <c r="D65" s="21">
+        <f>C66</f>
         <v>222355</v>
       </c>
-      <c r="E64" s="21">
-        <f>D65</f>
+      <c r="E65" s="21">
+        <f>D66</f>
         <v>1485216</v>
       </c>
-      <c r="F64" s="21">
-        <f>E65</f>
+      <c r="F65" s="21">
+        <f>E66</f>
         <v>3608575</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="B65" s="31">
-        <f>B64+B56</f>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="31">
+        <f>B65+B56</f>
         <v>-212164</v>
       </c>
-      <c r="C65" s="31">
-        <f>C64+C56</f>
+      <c r="C66" s="31">
+        <f>C65+C56</f>
         <v>222355</v>
       </c>
-      <c r="D65" s="31">
-        <f>D64+D56</f>
+      <c r="D66" s="31">
+        <f>D65+D56</f>
         <v>1485216</v>
       </c>
-      <c r="E65" s="31">
-        <f>E64+E56</f>
+      <c r="E66" s="31">
+        <f>E65+E56</f>
         <v>3608575</v>
       </c>
-      <c r="F65" s="31">
-        <f>F64+F56</f>
+      <c r="F66" s="31">
+        <f>F65+F56</f>
         <v>6668055</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="B66" s="37">
-        <f>IF(B54=0,"",B65/B54*365)</f>
-        <v>-56</v>
-      </c>
-      <c r="C66" s="37">
-        <f>IF(C54=0,"",C65/C54*365)</f>
-        <v>46</v>
-      </c>
-      <c r="D66" s="37">
-        <f>IF(D54=0,"",D65/D54*365)</f>
-        <v>271</v>
-      </c>
-      <c r="E66" s="37">
-        <f>IF(E54=0,"",E65/E54*365)</f>
-        <v>593</v>
-      </c>
-      <c r="F66" s="37">
-        <f>IF(F54=0,"",F65/F54*365)</f>
-        <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" s="38">
-        <f>IF(B54=0,"",B65/(B54/12))</f>
-        <v>-1.8</v>
-      </c>
-      <c r="C67" s="38">
-        <f>IF(C54=0,"",C65/(C54/12))</f>
-        <v>1.5</v>
-      </c>
-      <c r="D67" s="38">
-        <f>IF(D54=0,"",D65/(D54/12))</f>
-        <v>8.9</v>
-      </c>
-      <c r="E67" s="38">
-        <f>IF(E54=0,"",E65/(E54/12))</f>
-        <v>19.5</v>
-      </c>
-      <c r="F67" s="38">
-        <f>IF(F54=0,"",F65/(F54/12))</f>
-        <v>32.5</v>
+        <v>200</v>
+      </c>
+      <c r="B67" s="39">
+        <f>IF(B54=0,"",B66/B54*365)</f>
+        <v>-56</v>
+      </c>
+      <c r="C67" s="39">
+        <f>IF(C54=0,"",C66/C54*365)</f>
+        <v>46</v>
+      </c>
+      <c r="D67" s="39">
+        <f>IF(D54=0,"",D66/D54*365)</f>
+        <v>271</v>
+      </c>
+      <c r="E67" s="39">
+        <f>IF(E54=0,"",E66/E54*365)</f>
+        <v>593</v>
+      </c>
+      <c r="F67" s="39">
+        <f>IF(F54=0,"",F66/F54*365)</f>
+        <v>987</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B68" s="35">
+        <v>201</v>
+      </c>
+      <c r="B68" s="40">
+        <f>IF(B54=0,"",B66/(B54/12))</f>
+        <v>-1.8</v>
+      </c>
+      <c r="C68" s="40">
+        <f>IF(C54=0,"",C66/(C54/12))</f>
+        <v>1.5</v>
+      </c>
+      <c r="D68" s="40">
+        <f>IF(D54=0,"",D66/(D54/12))</f>
+        <v>8.9</v>
+      </c>
+      <c r="E68" s="40">
+        <f>IF(E54=0,"",E66/(E54/12))</f>
+        <v>19.5</v>
+      </c>
+      <c r="F68" s="40">
+        <f>IF(F54=0,"",F66/(F54/12))</f>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="35">
         <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C68" s="35">
+      <c r="C69" s="35">
         <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
         <v>0.33</v>
       </c>
-      <c r="D68" s="35">
+      <c r="D69" s="35">
         <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E68" s="35">
+      <c r="E69" s="35">
         <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
         <v>0.67</v>
       </c>
-      <c r="F68" s="35">
+      <c r="F69" s="35">
         <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
         <v>0.83</v>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="B71" s="13" t="str">
-        <f>IF(B62=0,"N/A",IF(B63&gt;=1.2,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="C71" s="13" t="str">
-        <f>IF(C62=0,"N/A",IF(C63&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D71" s="13" t="str">
-        <f>IF(D62=0,"N/A",IF(D63&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E71" s="13" t="str">
-        <f>IF(E62=0,"N/A",IF(E63&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F71" s="13" t="str">
-        <f>IF(F62=0,"N/A",IF(F63&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+    <row r="71" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B72" s="13" t="str">
+        <f>IF(B63=0,"N/A",IF(B64&gt;=1.2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C72" s="13" t="str">
+        <f>IF(C63=0,"N/A",IF(C64&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D72" s="13" t="str">
+        <f>IF(D63=0,"N/A",IF(D64&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E72" s="13" t="str">
+        <f>IF(E63=0,"N/A",IF(E64&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F72" s="13" t="str">
+        <f>IF(F63=0,"N/A",IF(F64&gt;=1.2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B73" s="13" t="str">
         <f>IF(B56&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C72" s="13" t="str">
+      <c r="C73" s="13" t="str">
         <f>IF(C56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D72" s="13" t="str">
+      <c r="D73" s="13" t="str">
         <f>IF(D56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E72" s="13" t="str">
+      <c r="E73" s="13" t="str">
         <f>IF(E56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F72" s="13" t="str">
+      <c r="F73" s="13" t="str">
         <f>IF(F56&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B73" s="13" t="str">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B74" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C73" s="13" t="str">
+      <c r="C74" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D73" s="13" t="str">
+      <c r="D74" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="E73" s="13" t="str">
+      <c r="E74" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="F73" s="13" t="str">
+      <c r="F74" s="13" t="str">
         <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B74" s="13" t="str">
-        <f>IF(B54=0,"N/A",IF(B65/(B54/12)&gt;=2,"PASS","FAIL"))</f>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B75" s="13" t="str">
+        <f>IF(B54=0,"N/A",IF(B66/(B54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="C74" s="13" t="str">
-        <f>IF(C54=0,"N/A",IF(C65/(C54/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="C75" s="13" t="str">
+        <f>IF(C54=0,"N/A",IF(C66/(C54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
-      <c r="D74" s="13" t="str">
-        <f>IF(D54=0,"N/A",IF(D65/(D54/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="D75" s="13" t="str">
+        <f>IF(D54=0,"N/A",IF(D66/(D54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E74" s="13" t="str">
-        <f>IF(E54=0,"N/A",IF(E65/(E54/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="E75" s="13" t="str">
+        <f>IF(E54=0,"N/A",IF(E66/(E54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F74" s="13" t="str">
-        <f>IF(F54=0,"N/A",IF(F65/(F54/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="F75" s="13" t="str">
+        <f>IF(F54=0,"N/A",IF(F66/(F54/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B77" s="21">
+    <row r="77" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B78" s="21">
         <f>IF(B3=0,"",B12/B3)</f>
         <v>9819</v>
       </c>
-      <c r="C77" s="21">
+      <c r="C78" s="21">
         <f>IF(C3=0,"",C12/C3)</f>
         <v>11063</v>
       </c>
-      <c r="D77" s="21">
+      <c r="D78" s="21">
         <f>IF(D3=0,"",D12/D3)</f>
         <v>10885</v>
       </c>
-      <c r="E77" s="21">
+      <c r="E78" s="21">
         <f>IF(E3=0,"",E12/E3)</f>
         <v>10857</v>
       </c>
-      <c r="F77" s="21">
+      <c r="F78" s="21">
         <f>IF(F3=0,"",F12/F3)</f>
         <v>11049</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="B78" s="21">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="21">
         <f>IF(B3=0,"",B54/B3)</f>
         <v>11587</v>
       </c>
-      <c r="C78" s="21">
+      <c r="C79" s="21">
         <f>IF(C3=0,"",C54/C3)</f>
         <v>8891</v>
       </c>
-      <c r="D78" s="21">
+      <c r="D79" s="21">
         <f>IF(D3=0,"",D54/D3)</f>
         <v>6676</v>
       </c>
-      <c r="E78" s="21">
+      <c r="E79" s="21">
         <f>IF(E3=0,"",E54/E3)</f>
         <v>5549</v>
       </c>
-      <c r="F78" s="21">
+      <c r="F79" s="21">
         <f>IF(F3=0,"",F54/F3)</f>
         <v>4930</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="B79" s="21">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B80" s="21">
         <f>B51+B53</f>
         <v>887164</v>
       </c>
-      <c r="C79" s="21">
+      <c r="C80" s="21">
         <f>C51+C53</f>
         <v>1003271</v>
       </c>
-      <c r="D79" s="21">
+      <c r="D80" s="21">
         <f>D51+D53</f>
         <v>1008271</v>
       </c>
-      <c r="E79" s="21">
+      <c r="E80" s="21">
         <f>E51+E53</f>
         <v>993271</v>
       </c>
-      <c r="F79" s="21">
+      <c r="F80" s="21">
         <f>F51+F53</f>
         <v>993271</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" s="21">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B81" s="21">
         <f>IF(B3=0,"",B52/B3)</f>
         <v>4194</v>
       </c>
-      <c r="C80" s="21">
+      <c r="C81" s="21">
         <f>IF(C3=0,"",C52/C3)</f>
         <v>3874</v>
       </c>
-      <c r="D80" s="21">
+      <c r="D81" s="21">
         <f>IF(D3=0,"",D52/D3)</f>
         <v>3315</v>
       </c>
-      <c r="E80" s="21">
+      <c r="E81" s="21">
         <f>IF(E3=0,"",E52/E3)</f>
         <v>3066</v>
       </c>
-      <c r="F80" s="21">
+      <c r="F81" s="21">
         <f>IF(F3=0,"",F52/F3)</f>
         <v>2944</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="B81" s="21">
-        <f>IF(B3=0,"",B77-B80)</f>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B82" s="21">
+        <f>IF(B3=0,"",B78-B81)</f>
         <v>5625</v>
       </c>
-      <c r="C81" s="21">
-        <f>IF(C3=0,"",C77-C80)</f>
+      <c r="C82" s="21">
+        <f>IF(C3=0,"",C78-C81)</f>
         <v>7189</v>
       </c>
-      <c r="D81" s="21">
-        <f>IF(D3=0,"",D77-D80)</f>
+      <c r="D82" s="21">
+        <f>IF(D3=0,"",D78-D81)</f>
         <v>7570</v>
       </c>
-      <c r="E81" s="21">
-        <f>IF(E3=0,"",E77-E80)</f>
+      <c r="E82" s="21">
+        <f>IF(E3=0,"",E78-E81)</f>
         <v>7792</v>
       </c>
-      <c r="F81" s="21">
-        <f>IF(F3=0,"",F77-F80)</f>
+      <c r="F82" s="21">
+        <f>IF(F3=0,"",F78-F81)</f>
         <v>8106</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="B82" s="40">
-        <f>IF(B81&lt;=0,"N/A",ROUNDUP(B79/B81,0))</f>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" s="42">
+        <f>IF(B82&lt;=0,"N/A",ROUNDUP(B80/B82,0))</f>
         <v>158</v>
       </c>
-      <c r="C82" s="40">
-        <f>IF(C81&lt;=0,"N/A",ROUNDUP(C79/C81,0))</f>
+      <c r="C83" s="42">
+        <f>IF(C82&lt;=0,"N/A",ROUNDUP(C80/C82,0))</f>
         <v>140</v>
       </c>
-      <c r="D82" s="40">
-        <f>IF(D81&lt;=0,"N/A",ROUNDUP(D79/D81,0))</f>
+      <c r="D83" s="42">
+        <f>IF(D82&lt;=0,"N/A",ROUNDUP(D80/D82,0))</f>
         <v>134</v>
       </c>
-      <c r="E82" s="40">
-        <f>IF(E81&lt;=0,"N/A",ROUNDUP(E79/E81,0))</f>
+      <c r="E83" s="42">
+        <f>IF(E82&lt;=0,"N/A",ROUNDUP(E80/E82,0))</f>
         <v>128</v>
       </c>
-      <c r="F82" s="40">
-        <f>IF(F81&lt;=0,"N/A",ROUNDUP(F79/F81,0))</f>
+      <c r="F83" s="42">
+        <f>IF(F82&lt;=0,"N/A",ROUNDUP(F80/F82,0))</f>
         <v>123</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="26" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -4654,7 +4683,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4678,40 +4707,40 @@
         <v>46</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -5497,7 +5526,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" s="21">
         <v>6500</v>
@@ -5605,7 +5634,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B27" s="21">
         <v>4500</v>
@@ -5713,7 +5742,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B30" s="21">
         <v>22000</v>
@@ -5758,7 +5787,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B31" s="21">
         <v>3000</v>
@@ -5803,7 +5832,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B32" s="21">
         <v>1833</v>
@@ -5911,7 +5940,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B35" s="21">
         <v>2500</v>
@@ -5956,7 +5985,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B36" s="21">
         <v>1000</v>
@@ -6001,7 +6030,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B37" s="21">
         <v>1500</v>
@@ -6046,7 +6075,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B38" s="21">
         <v>7500</v>
@@ -6198,7 +6227,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B42" s="21">
         <v>8886</v>
@@ -6248,7 +6277,7 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -6323,7 +6352,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="27" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B46" s="31">
         <f>B10-B45</f>
@@ -6380,7 +6409,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B47" s="31">
         <f>0+B46</f>
@@ -6437,7 +6466,7 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -6452,7 +6481,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B51" s="31">
         <f>M47</f>
@@ -6461,7 +6490,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B52" s="21">
         <f>MIN(B47:M47)</f>
@@ -6518,7 +6547,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6528,147 +6557,147 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>245</v>
-      </c>
-      <c r="F4" s="44" t="s">
+      <c r="B4" s="44" t="s">
         <v>246</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="45">
+        <v>256</v>
+      </c>
+      <c r="C7" s="47">
         <v>120</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="47">
         <v>200</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="47">
         <v>300</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="47">
         <v>400</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="47">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="46">
+        <v>257</v>
+      </c>
+      <c r="C8" s="48">
         <v>1414000</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="48">
         <v>2212650</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="48">
         <v>3265600</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="48">
         <v>4342850</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="48">
         <v>5524700</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" s="46">
+        <v>258</v>
+      </c>
+      <c r="C9" s="48">
         <v>780535</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <v>936642</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="48">
         <v>936642</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="48">
         <v>936642</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="48">
         <v>936642</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C10" s="46">
+        <v>259</v>
+      </c>
+      <c r="C10" s="48">
         <v>604000</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <v>774860</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="48">
         <v>994467.6</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="48">
         <v>1226219.9279999998</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="48">
         <v>1471949.32584</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="46">
+        <v>197</v>
+      </c>
+      <c r="C11" s="48">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="48">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="48">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="48">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="48">
         <v>46628.6108154935</v>
       </c>
     </row>
@@ -6676,379 +6705,379 @@
       <c r="B12" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="49">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="50">
         <v>454519.3891845065</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="50">
         <v>1287861.7891845065</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="50">
         <v>2133359.461184507</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="50">
         <v>3069480.0633445065</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="47">
+        <v>199</v>
+      </c>
+      <c r="C13" s="49">
         <v>-17163.6108154935</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="50">
         <v>437355.778369013</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="50">
         <v>1725217.5675535195</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="50">
         <v>3858577.0287380265</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="50">
         <v>6928057.092082533</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="49">
+        <v>260</v>
+      </c>
+      <c r="C14" s="51">
         <v>-0.0121383386248186</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="52">
         <v>0.20541856560436875</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="52">
         <v>0.39437217944160535</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="52">
         <v>0.49123489440908774</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="52">
         <v>0.555592170315946</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C15" s="51">
+        <v>261</v>
+      </c>
+      <c r="C15" s="53">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="53">
         <v>11063.25</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="53">
         <v>10885.333333333334</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="53">
         <v>10857.125</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="53">
         <v>11049.4</v>
       </c>
-      <c r="H15" s="52" t="s">
-        <v>260</v>
+      <c r="H15" s="54" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="53">
+        <v>263</v>
+      </c>
+      <c r="C16" s="55">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="52">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="52">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="52">
         <v>0.16953716943906458</v>
       </c>
-      <c r="H16" s="52" t="s">
-        <v>262</v>
+      <c r="H16" s="54" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C17" s="50">
+        <v>265</v>
+      </c>
+      <c r="C17" s="52">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="52">
         <v>0.10505864009219713</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <v>0.09135848848603624</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="52">
         <v>0.08470612118769931</v>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="52">
         <v>0.07992919031838833</v>
       </c>
-      <c r="H17" s="52" t="s">
-        <v>264</v>
+      <c r="H17" s="54" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C18" s="53">
+        <v>267</v>
+      </c>
+      <c r="C18" s="55">
         <v>0.020838048090523337</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="52">
         <v>0.22649221521704743</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <v>0.40865090641842233</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="52">
         <v>0.5019717632430317</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="52">
         <v>0.5640321961663076</v>
       </c>
-      <c r="H18" s="52" t="s">
-        <v>266</v>
+      <c r="H18" s="54" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C19" s="54">
-        <v>1</v>
-      </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="52" t="s">
-        <v>268</v>
+        <v>269</v>
+      </c>
+      <c r="C19" s="56">
+        <v>3</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="54" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="55">
+        <v>271</v>
+      </c>
+      <c r="C20" s="57">
         <v>0.6319081672107103</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="58">
         <v>10.747650235238861</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="58">
         <v>28.61956160951256</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="58">
         <v>46.752155680255555</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="58">
         <v>66.82825457722186</v>
       </c>
-      <c r="H20" s="52" t="s">
-        <v>270</v>
+      <c r="H20" s="54" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="52" t="s">
-        <v>248</v>
+        <v>273</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="54" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C22" s="58" t="s">
-        <v>273</v>
-      </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="52" t="s">
         <v>274</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="54" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D25" s="61" t="s">
+      <c r="B25" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="C25" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
+      <c r="D25" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="63" t="s">
-        <v>284</v>
-      </c>
-      <c r="D26" s="61" t="s">
+      <c r="B26" s="61" t="s">
         <v>285</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="C26" s="64" t="s">
         <v>286</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="D26" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="59" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>288</v>
-      </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="B27" s="61" t="s">
         <v>289</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
+      <c r="C27" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
+        <v>291</v>
+      </c>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
-        <v>290</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>291</v>
-      </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="B28" s="61" t="s">
         <v>292</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="C28" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D28" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
-        <v>293</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="B29" s="61" t="s">
         <v>295</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
+      <c r="C29" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>296</v>
+      </c>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
-        <v>296</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="B30" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="C30" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
+        <v>300</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
-        <v>299</v>
-      </c>
-      <c r="C31" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>300</v>
-      </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
+      <c r="B31" s="61" t="s">
         <v>301</v>
       </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
+      <c r="C31" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>302</v>
+      </c>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
+        <v>303</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
-        <v>302</v>
+      <c r="B33" s="61" t="s">
+        <v>304</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
       <c r="F33" s="27"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -7187,10 +7187,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="306">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1250,7 +1250,9 @@
     <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6895,13 +6897,26 @@
       <c r="B21" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="59" t="s">
-        <v>251</v>
-      </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
+      <c r="C21" s="59" t="str">
+        <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="37" t="str">
+        <f>IF('5-Year Model'!C58&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="59" t="str">
+        <f>IF('5-Year Model'!D58&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="59" t="str">
+        <f>IF('5-Year Model'!E58&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="59" t="str">
+        <f>IF('5-Year Model'!F58&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="54" t="s">
         <v>250</v>
       </c>
@@ -7080,11 +7095,10 @@
       <c r="H35" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -7165,10 +7179,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="305">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -851,13 +851,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1158,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1243,7 +1240,9 @@
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1253,7 +1252,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6862,10 +6866,18 @@
       <c r="C19" s="56">
         <v>3</v>
       </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="D19" s="56">
+        <v>3</v>
+      </c>
+      <c r="E19" s="56">
+        <v>3</v>
+      </c>
+      <c r="F19" s="56">
+        <v>3</v>
+      </c>
+      <c r="G19" s="56">
+        <v>3</v>
+      </c>
       <c r="H19" s="54" t="s">
         <v>270</v>
       </c>
@@ -6902,19 +6914,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="37" t="str">
-        <f>IF('5-Year Model'!C58&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="E21" s="59" t="str">
-        <f>IF('5-Year Model'!D58&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="59" t="str">
-        <f>IF('5-Year Model'!E58&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="59" t="str">
-        <f>IF('5-Year Model'!F58&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="54" t="s">
@@ -6925,181 +6937,187 @@
       <c r="B22" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="60">
+        <v>0</v>
+      </c>
+      <c r="D22" s="60">
+        <v>3</v>
+      </c>
+      <c r="E22" s="60">
+        <v>10</v>
+      </c>
+      <c r="F22" s="61">
+        <v>21</v>
+      </c>
+      <c r="G22" s="56">
+        <v>34</v>
+      </c>
+      <c r="H22" s="54" t="s">
         <v>275</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="54" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="D25" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="E25" s="63"/>
+      <c r="F25" s="64" t="s">
         <v>283</v>
       </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="C26" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="D26" s="63" t="s">
         <v>286</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="E26" s="63"/>
+      <c r="F26" s="64" t="s">
         <v>287</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="61" t="s">
+      <c r="C27" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="63" t="s">
         <v>289</v>
       </c>
-      <c r="C27" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D27" s="62" t="s">
+      <c r="E27" s="63"/>
+      <c r="F27" s="64" t="s">
         <v>290</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="61" t="s">
+      <c r="C28" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="63" t="s">
         <v>292</v>
       </c>
-      <c r="C28" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D28" s="62" t="s">
+      <c r="E28" s="63"/>
+      <c r="F28" s="64" t="s">
         <v>293</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
+      <c r="C29" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="C29" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D29" s="62" t="s">
+      <c r="E29" s="63"/>
+      <c r="F29" s="64" t="s">
         <v>296</v>
       </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="62" t="s">
         <v>297</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
+      <c r="C30" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D30" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="C30" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="62" t="s">
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
         <v>299</v>
       </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63" t="s">
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+      <c r="C31" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" s="63" t="s">
         <v>301</v>
       </c>
-      <c r="C31" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D31" s="62" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63" t="s">
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="61" t="s">
+      <c r="C33" s="27" t="s">
         <v>304</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>305</v>
       </c>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
       <c r="F33" s="27"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -905,7 +905,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -6817,20 +6817,20 @@
       <c r="B17" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="C17" s="52">
-        <v>0.12814710042432814</v>
+      <c r="C17" s="51">
+        <v>0.22772277227722773</v>
       </c>
       <c r="D17" s="52">
-        <v>0.10505864009219713</v>
+        <v>0.1498926626443405</v>
       </c>
       <c r="E17" s="52">
-        <v>0.09135848848603624</v>
+        <v>0.10460975012248896</v>
       </c>
       <c r="F17" s="52">
-        <v>0.08470612118769931</v>
+        <v>0.08101959036116835</v>
       </c>
       <c r="G17" s="52">
-        <v>0.07992919031838833</v>
+        <v>0.06559982005176752</v>
       </c>
       <c r="H17" s="54" t="s">
         <v>266</v>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -35,7 +35,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -764,7 +764,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="306">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -855,6 +855,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -6541,7 +6544,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6956,170 +6959,191 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="60">
+        <v>0</v>
+      </c>
+      <c r="D23" s="56">
+        <v>91</v>
+      </c>
+      <c r="E23" s="56">
+        <v>318</v>
+      </c>
+      <c r="F23" s="56">
+        <v>637</v>
+      </c>
+      <c r="G23" s="56">
+        <v>1030</v>
+      </c>
+      <c r="H23" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="12" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="C25" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>282</v>
-      </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
-        <v>283</v>
-      </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="62" t="s">
-        <v>284</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>285</v>
+        <v>281</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>282</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E26" s="63"/>
       <c r="F26" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="62" t="s">
-        <v>288</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>281</v>
+        <v>285</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>286</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="64" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G27" s="64"/>
       <c r="H27" s="64"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="62" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E28" s="63"/>
       <c r="F28" s="64" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="62" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E29" s="63"/>
       <c r="F29" s="64" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="62" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D30" s="63" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E30" s="63"/>
       <c r="F30" s="64" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G30" s="64"/>
       <c r="H30" s="64"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="62" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E31" s="63"/>
       <c r="F31" s="64" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G31" s="64"/>
       <c r="H31" s="64"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>302</v>
+      </c>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
         <v>304</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
+      <c r="C34" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -7134,8 +7158,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="311">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -816,6 +816,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1158,7 +1173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1240,6 +1255,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6544,7 +6571,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6793,365 +6820,440 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>263</v>
       </c>
       <c r="C16" s="55">
-        <v>0.5520049504950495</v>
-      </c>
-      <c r="D16" s="52">
-        <v>0.4233123178089621</v>
-      </c>
-      <c r="E16" s="52">
-        <v>0.2868207986281235</v>
-      </c>
-      <c r="F16" s="52">
-        <v>0.21567449946463726</v>
-      </c>
-      <c r="G16" s="52">
-        <v>0.16953716943906458</v>
-      </c>
-      <c r="H16" s="54" t="s">
+        <v>11926.363423462444</v>
+      </c>
+      <c r="D16" s="55">
+        <v>8790.653054077467</v>
+      </c>
+      <c r="E16" s="55">
+        <v>6592.460702718312</v>
+      </c>
+      <c r="F16" s="55">
+        <v>5523.726347038733</v>
+      </c>
+      <c r="G16" s="55">
+        <v>4910.4398733109865</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
+      <c r="C17" s="48">
+        <v>650</v>
+      </c>
+      <c r="D17" s="48">
+        <v>670</v>
+      </c>
+      <c r="E17" s="48">
+        <v>690</v>
+      </c>
+      <c r="F17" s="48">
+        <v>710</v>
+      </c>
+      <c r="G17" s="48">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D17" s="52">
-        <v>0.1498926626443405</v>
-      </c>
-      <c r="E17" s="52">
-        <v>0.10460975012248896</v>
-      </c>
-      <c r="F17" s="52">
-        <v>0.08101959036116835</v>
-      </c>
-      <c r="G17" s="52">
-        <v>0.06559982005176752</v>
-      </c>
-      <c r="H17" s="54" t="s">
+      <c r="C18" s="56">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="53">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="53">
+        <v>1138.712</v>
+      </c>
+      <c r="F18" s="53">
+        <v>879.6398199999999</v>
+      </c>
+      <c r="G18" s="53">
+        <v>724.8386516800001</v>
+      </c>
+      <c r="H18" s="54" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="C18" s="55">
-        <v>0.020838048090523337</v>
-      </c>
-      <c r="D18" s="52">
-        <v>0.22649221521704743</v>
-      </c>
-      <c r="E18" s="52">
-        <v>0.40865090641842233</v>
-      </c>
-      <c r="F18" s="52">
-        <v>0.5019717632430317</v>
-      </c>
-      <c r="G18" s="52">
-        <v>0.5640321961663076</v>
-      </c>
-      <c r="H18" s="54" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="56">
-        <v>3</v>
-      </c>
-      <c r="D19" s="56">
-        <v>3</v>
-      </c>
-      <c r="E19" s="56">
-        <v>3</v>
-      </c>
-      <c r="F19" s="56">
-        <v>3</v>
-      </c>
-      <c r="G19" s="56">
-        <v>3</v>
-      </c>
-      <c r="H19" s="54" t="s">
-        <v>270</v>
+      <c r="C19" s="57">
+        <v>-143.0300901291125</v>
+      </c>
+      <c r="D19" s="58">
+        <v>2272.5969459225325</v>
+      </c>
+      <c r="E19" s="58">
+        <v>4292.872630615022</v>
+      </c>
+      <c r="F19" s="58">
+        <v>5333.398652961267</v>
+      </c>
+      <c r="G19" s="58">
+        <v>6138.960126689013</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C20" s="57">
-        <v>0.6319081672107103</v>
-      </c>
-      <c r="D20" s="58">
-        <v>10.747650235238861</v>
-      </c>
-      <c r="E20" s="58">
-        <v>28.61956160951256</v>
-      </c>
-      <c r="F20" s="58">
-        <v>46.752155680255555</v>
-      </c>
-      <c r="G20" s="58">
-        <v>66.82825457722186</v>
+        <v>268</v>
+      </c>
+      <c r="C20" s="59">
+        <v>0.5520049504950495</v>
+      </c>
+      <c r="D20" s="52">
+        <v>0.4233123178089621</v>
+      </c>
+      <c r="E20" s="52">
+        <v>0.2868207986281235</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0.21567449946463726</v>
+      </c>
+      <c r="G20" s="52">
+        <v>0.16953716943906458</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" s="51">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D21" s="52">
+        <v>0.1498926626443405</v>
+      </c>
+      <c r="E21" s="52">
+        <v>0.10460975012248896</v>
+      </c>
+      <c r="F21" s="52">
+        <v>0.08101959036116835</v>
+      </c>
+      <c r="G21" s="52">
+        <v>0.06559982005176752</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="59">
+        <v>0.020838048090523337</v>
+      </c>
+      <c r="D22" s="52">
+        <v>0.22649221521704743</v>
+      </c>
+      <c r="E22" s="52">
+        <v>0.40865090641842233</v>
+      </c>
+      <c r="F22" s="52">
+        <v>0.5019717632430317</v>
+      </c>
+      <c r="G22" s="52">
+        <v>0.5640321961663076</v>
+      </c>
+      <c r="H22" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="59" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="60">
+        <v>3</v>
+      </c>
+      <c r="D23" s="60">
+        <v>3</v>
+      </c>
+      <c r="E23" s="60">
+        <v>3</v>
+      </c>
+      <c r="F23" s="60">
+        <v>3</v>
+      </c>
+      <c r="G23" s="60">
+        <v>3</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="61">
+        <v>0.6319081672107103</v>
+      </c>
+      <c r="D24" s="62">
+        <v>10.747650235238861</v>
+      </c>
+      <c r="E24" s="62">
+        <v>28.61956160951256</v>
+      </c>
+      <c r="F24" s="62">
+        <v>46.752155680255555</v>
+      </c>
+      <c r="G24" s="62">
+        <v>66.82825457722186</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="63" t="str">
         <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="37" t="str">
+      <c r="D25" s="37" t="str">
         <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="59" t="str">
+      <c r="E25" s="63" t="str">
         <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="59" t="str">
+      <c r="F25" s="63" t="str">
         <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="59" t="str">
+      <c r="G25" s="63" t="str">
         <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="H25" s="54" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="60">
-        <v>0</v>
-      </c>
-      <c r="D22" s="60">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26" s="64">
+        <v>0</v>
+      </c>
+      <c r="D26" s="64">
         <v>3</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E26" s="64">
         <v>10</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F26" s="65">
         <v>21</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G26" s="60">
         <v>34</v>
       </c>
-      <c r="H22" s="54" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="27" t="s">
+      <c r="H26" s="54" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="C23" s="60">
-        <v>0</v>
-      </c>
-      <c r="D23" s="56">
+      <c r="C27" s="64">
+        <v>0</v>
+      </c>
+      <c r="D27" s="60">
         <v>91</v>
       </c>
-      <c r="E23" s="56">
+      <c r="E27" s="60">
         <v>318</v>
       </c>
-      <c r="F23" s="56">
+      <c r="F27" s="60">
         <v>637</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G27" s="60">
         <v>1030</v>
       </c>
-      <c r="H23" s="54" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+      <c r="H27" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="C26" s="37" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="C29" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
+      <c r="D29" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
         <v>286</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="C30" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
+      <c r="D30" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="E30" s="67"/>
+      <c r="F30" s="68" t="s">
         <v>289</v>
       </c>
-      <c r="C28" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D28" s="63" t="s">
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
+      <c r="C31" s="69" t="s">
         <v>291</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
+      <c r="D31" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="C29" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D29" s="63" t="s">
+      <c r="E31" s="67"/>
+      <c r="F31" s="68" t="s">
         <v>293</v>
       </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64" t="s">
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
         <v>294</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="C32" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="C30" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="63" t="s">
+      <c r="E32" s="67"/>
+      <c r="F32" s="68" t="s">
         <v>296</v>
       </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
         <v>297</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
+      <c r="C33" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D33" s="67" t="s">
         <v>298</v>
       </c>
-      <c r="C31" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D31" s="63" t="s">
+      <c r="E33" s="67"/>
+      <c r="F33" s="68" t="s">
         <v>299</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
+      <c r="G33" s="68"/>
+      <c r="H33" s="68"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="66" t="s">
         <v>300</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
+      <c r="C34" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D34" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="C32" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="63" t="s">
+      <c r="E34" s="67"/>
+      <c r="F34" s="68" t="s">
         <v>302</v>
       </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64" t="s">
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="62" t="s">
+      <c r="C35" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="67" t="s">
         <v>304</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="E35" s="67"/>
+      <c r="F35" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="66" t="s">
+        <v>306</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D36" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="E36" s="67"/>
+      <c r="F36" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="66" t="s">
+        <v>309</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -7160,8 +7262,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7207,48 +7317,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="305">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -818,21 +818,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -870,9 +855,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1173,7 +1155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1255,18 +1237,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6571,7 +6541,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6820,458 +6790,352 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>263</v>
       </c>
       <c r="C16" s="55">
-        <v>11926.363423462444</v>
-      </c>
-      <c r="D16" s="55">
-        <v>8790.653054077467</v>
-      </c>
-      <c r="E16" s="55">
-        <v>6592.460702718312</v>
-      </c>
-      <c r="F16" s="55">
-        <v>5523.726347038733</v>
-      </c>
-      <c r="G16" s="55">
-        <v>4910.4398733109865</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+        <v>0.5520049504950495</v>
+      </c>
+      <c r="D16" s="52">
+        <v>0.4233123178089621</v>
+      </c>
+      <c r="E16" s="52">
+        <v>0.2868207986281235</v>
+      </c>
+      <c r="F16" s="52">
+        <v>0.21567449946463726</v>
+      </c>
+      <c r="G16" s="52">
+        <v>0.16953716943906458</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="C17" s="48">
-        <v>650</v>
-      </c>
-      <c r="D17" s="48">
-        <v>670</v>
-      </c>
-      <c r="E17" s="48">
-        <v>690</v>
-      </c>
-      <c r="F17" s="48">
-        <v>710</v>
-      </c>
-      <c r="G17" s="48">
-        <v>732</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="51">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D17" s="52">
+        <v>0.1498926626443405</v>
+      </c>
+      <c r="E17" s="52">
+        <v>0.10460975012248896</v>
+      </c>
+      <c r="F17" s="52">
+        <v>0.08101959036116835</v>
+      </c>
+      <c r="G17" s="52">
+        <v>0.06559982005176752</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C18" s="56">
-        <v>2683.3333333333335</v>
-      </c>
-      <c r="D18" s="53">
-        <v>1658.3</v>
-      </c>
-      <c r="E18" s="53">
-        <v>1138.712</v>
-      </c>
-      <c r="F18" s="53">
-        <v>879.6398199999999</v>
-      </c>
-      <c r="G18" s="53">
-        <v>724.8386516800001</v>
+      <c r="B18" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="55">
+        <v>0.020838048090523337</v>
+      </c>
+      <c r="D18" s="52">
+        <v>0.22649221521704743</v>
+      </c>
+      <c r="E18" s="52">
+        <v>0.40865090641842233</v>
+      </c>
+      <c r="F18" s="52">
+        <v>0.5019717632430317</v>
+      </c>
+      <c r="G18" s="52">
+        <v>0.5640321961663076</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C19" s="57">
-        <v>-143.0300901291125</v>
-      </c>
-      <c r="D19" s="58">
-        <v>2272.5969459225325</v>
-      </c>
-      <c r="E19" s="58">
-        <v>4292.872630615022</v>
-      </c>
-      <c r="F19" s="58">
-        <v>5333.398652961267</v>
-      </c>
-      <c r="G19" s="58">
-        <v>6138.960126689013</v>
+        <v>269</v>
+      </c>
+      <c r="C19" s="56">
+        <v>3</v>
+      </c>
+      <c r="D19" s="56">
+        <v>3</v>
+      </c>
+      <c r="E19" s="56">
+        <v>3</v>
+      </c>
+      <c r="F19" s="56">
+        <v>3</v>
+      </c>
+      <c r="G19" s="56">
+        <v>3</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="59">
-        <v>0.5520049504950495</v>
-      </c>
-      <c r="D20" s="52">
-        <v>0.4233123178089621</v>
-      </c>
-      <c r="E20" s="52">
-        <v>0.2868207986281235</v>
-      </c>
-      <c r="F20" s="52">
-        <v>0.21567449946463726</v>
-      </c>
-      <c r="G20" s="52">
-        <v>0.16953716943906458</v>
+        <v>271</v>
+      </c>
+      <c r="C20" s="57">
+        <v>0.6319081672107103</v>
+      </c>
+      <c r="D20" s="58">
+        <v>10.747650235238861</v>
+      </c>
+      <c r="E20" s="58">
+        <v>28.61956160951256</v>
+      </c>
+      <c r="F20" s="58">
+        <v>46.752155680255555</v>
+      </c>
+      <c r="G20" s="58">
+        <v>66.82825457722186</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="C21" s="51">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D21" s="52">
-        <v>0.1498926626443405</v>
-      </c>
-      <c r="E21" s="52">
-        <v>0.10460975012248896</v>
-      </c>
-      <c r="F21" s="52">
-        <v>0.08101959036116835</v>
-      </c>
-      <c r="G21" s="52">
-        <v>0.06559982005176752</v>
+        <v>273</v>
+      </c>
+      <c r="C21" s="59" t="str">
+        <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="37" t="str">
+        <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="59" t="str">
+        <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="59" t="str">
+        <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="59" t="str">
+        <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C22" s="59">
-        <v>0.020838048090523337</v>
-      </c>
-      <c r="D22" s="52">
-        <v>0.22649221521704743</v>
-      </c>
-      <c r="E22" s="52">
-        <v>0.40865090641842233</v>
-      </c>
-      <c r="F22" s="52">
-        <v>0.5019717632430317</v>
-      </c>
-      <c r="G22" s="52">
-        <v>0.5640321961663076</v>
+        <v>274</v>
+      </c>
+      <c r="C22" s="60">
+        <v>0</v>
+      </c>
+      <c r="D22" s="60">
+        <v>3</v>
+      </c>
+      <c r="E22" s="60">
+        <v>10</v>
+      </c>
+      <c r="F22" s="61">
+        <v>21</v>
+      </c>
+      <c r="G22" s="56">
+        <v>34</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C23" s="60">
-        <v>3</v>
-      </c>
-      <c r="D23" s="60">
-        <v>3</v>
-      </c>
-      <c r="E23" s="60">
-        <v>3</v>
-      </c>
-      <c r="F23" s="60">
-        <v>3</v>
-      </c>
-      <c r="G23" s="60">
-        <v>3</v>
-      </c>
-      <c r="H23" s="54" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="27" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="61">
-        <v>0.6319081672107103</v>
-      </c>
-      <c r="D24" s="62">
-        <v>10.747650235238861</v>
-      </c>
-      <c r="E24" s="62">
-        <v>28.61956160951256</v>
-      </c>
-      <c r="F24" s="62">
-        <v>46.752155680255555</v>
-      </c>
-      <c r="G24" s="62">
-        <v>66.82825457722186</v>
-      </c>
-      <c r="H24" s="54" t="s">
+      <c r="C24" s="12" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
+      <c r="D24" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C25" s="63" t="str">
-        <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="37" t="str">
-        <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="54" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C26" s="64">
-        <v>0</v>
-      </c>
-      <c r="D26" s="64">
-        <v>3</v>
-      </c>
-      <c r="E26" s="64">
-        <v>10</v>
-      </c>
-      <c r="F26" s="65">
-        <v>21</v>
-      </c>
-      <c r="G26" s="60">
-        <v>34</v>
-      </c>
-      <c r="H26" s="54" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="64">
-        <v>0</v>
-      </c>
-      <c r="D27" s="60">
-        <v>91</v>
-      </c>
-      <c r="E27" s="60">
-        <v>318</v>
-      </c>
-      <c r="F27" s="60">
-        <v>637</v>
-      </c>
-      <c r="G27" s="60">
-        <v>1030</v>
-      </c>
-      <c r="H27" s="54" t="s">
+      <c r="C25" s="37" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="D25" s="63" t="s">
         <v>282</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="E25" s="63"/>
+      <c r="F25" s="64" t="s">
         <v>283</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12" t="s">
+      <c r="C26" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="D26" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E26" s="63"/>
+      <c r="F26" s="64" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>289</v>
+      </c>
+      <c r="E27" s="63"/>
+      <c r="F27" s="64" t="s">
+        <v>290</v>
+      </c>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" s="63"/>
+      <c r="F28" s="64" t="s">
+        <v>293</v>
+      </c>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="E29" s="63"/>
+      <c r="F29" s="64" t="s">
+        <v>296</v>
+      </c>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>286</v>
+      <c r="B30" s="62" t="s">
+        <v>297</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D30" s="67" t="s">
-        <v>288</v>
-      </c>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68" t="s">
-        <v>289</v>
-      </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
+        <v>281</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
+        <v>299</v>
+      </c>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>290</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>291</v>
-      </c>
-      <c r="D31" s="67" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
-        <v>294</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D32" s="67" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68" t="s">
-        <v>296</v>
-      </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
-        <v>297</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D33" s="67" t="s">
-        <v>298</v>
-      </c>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68" t="s">
-        <v>299</v>
-      </c>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
+      <c r="B31" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D34" s="67" t="s">
+      <c r="C31" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" s="63" t="s">
         <v>301</v>
       </c>
-      <c r="E34" s="67"/>
-      <c r="F34" s="68" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="66" t="s">
-        <v>303</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="67" t="s">
-        <v>304</v>
-      </c>
-      <c r="E35" s="67"/>
-      <c r="F35" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="66" t="s">
-        <v>306</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="67" t="s">
-        <v>307</v>
-      </c>
-      <c r="E36" s="67"/>
-      <c r="F36" s="68" t="s">
-        <v>308</v>
-      </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7317,48 +7181,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="311">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -818,6 +818,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -855,6 +870,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1155,7 +1173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1237,6 +1255,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6541,7 +6571,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6790,352 +6820,458 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>263</v>
       </c>
       <c r="C16" s="55">
-        <v>0.5520049504950495</v>
-      </c>
-      <c r="D16" s="52">
-        <v>0.4233123178089621</v>
-      </c>
-      <c r="E16" s="52">
-        <v>0.2868207986281235</v>
-      </c>
-      <c r="F16" s="52">
-        <v>0.21567449946463726</v>
-      </c>
-      <c r="G16" s="52">
-        <v>0.16953716943906458</v>
-      </c>
-      <c r="H16" s="54" t="s">
+        <v>11926.363423462444</v>
+      </c>
+      <c r="D16" s="55">
+        <v>8790.653054077467</v>
+      </c>
+      <c r="E16" s="55">
+        <v>6592.460702718312</v>
+      </c>
+      <c r="F16" s="55">
+        <v>5523.726347038733</v>
+      </c>
+      <c r="G16" s="55">
+        <v>4910.4398733109865</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
+      <c r="C17" s="48">
+        <v>650</v>
+      </c>
+      <c r="D17" s="48">
+        <v>670</v>
+      </c>
+      <c r="E17" s="48">
+        <v>690</v>
+      </c>
+      <c r="F17" s="48">
+        <v>710</v>
+      </c>
+      <c r="G17" s="48">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D17" s="52">
-        <v>0.1498926626443405</v>
-      </c>
-      <c r="E17" s="52">
-        <v>0.10460975012248896</v>
-      </c>
-      <c r="F17" s="52">
-        <v>0.08101959036116835</v>
-      </c>
-      <c r="G17" s="52">
-        <v>0.06559982005176752</v>
-      </c>
-      <c r="H17" s="54" t="s">
+      <c r="C18" s="56">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="53">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="53">
+        <v>1138.712</v>
+      </c>
+      <c r="F18" s="53">
+        <v>879.6398199999999</v>
+      </c>
+      <c r="G18" s="53">
+        <v>724.8386516800001</v>
+      </c>
+      <c r="H18" s="54" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="C18" s="55">
-        <v>0.020838048090523337</v>
-      </c>
-      <c r="D18" s="52">
-        <v>0.22649221521704743</v>
-      </c>
-      <c r="E18" s="52">
-        <v>0.40865090641842233</v>
-      </c>
-      <c r="F18" s="52">
-        <v>0.5019717632430317</v>
-      </c>
-      <c r="G18" s="52">
-        <v>0.5640321961663076</v>
-      </c>
-      <c r="H18" s="54" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C19" s="56">
-        <v>3</v>
-      </c>
-      <c r="D19" s="56">
-        <v>3</v>
-      </c>
-      <c r="E19" s="56">
-        <v>3</v>
-      </c>
-      <c r="F19" s="56">
-        <v>3</v>
-      </c>
-      <c r="G19" s="56">
-        <v>3</v>
-      </c>
-      <c r="H19" s="54" t="s">
-        <v>270</v>
+      <c r="C19" s="57">
+        <v>-143.0300901291125</v>
+      </c>
+      <c r="D19" s="58">
+        <v>2272.5969459225325</v>
+      </c>
+      <c r="E19" s="58">
+        <v>4292.872630615022</v>
+      </c>
+      <c r="F19" s="58">
+        <v>5333.398652961267</v>
+      </c>
+      <c r="G19" s="58">
+        <v>6138.960126689013</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C20" s="57">
-        <v>0.6319081672107103</v>
-      </c>
-      <c r="D20" s="58">
-        <v>10.747650235238861</v>
-      </c>
-      <c r="E20" s="58">
-        <v>28.61956160951256</v>
-      </c>
-      <c r="F20" s="58">
-        <v>46.752155680255555</v>
-      </c>
-      <c r="G20" s="58">
-        <v>66.82825457722186</v>
+        <v>268</v>
+      </c>
+      <c r="C20" s="59">
+        <v>0.5520049504950495</v>
+      </c>
+      <c r="D20" s="52">
+        <v>0.4233123178089621</v>
+      </c>
+      <c r="E20" s="52">
+        <v>0.2868207986281235</v>
+      </c>
+      <c r="F20" s="52">
+        <v>0.21567449946463726</v>
+      </c>
+      <c r="G20" s="52">
+        <v>0.16953716943906458</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" s="51">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D21" s="52">
+        <v>0.1498926626443405</v>
+      </c>
+      <c r="E21" s="52">
+        <v>0.10460975012248896</v>
+      </c>
+      <c r="F21" s="52">
+        <v>0.08101959036116835</v>
+      </c>
+      <c r="G21" s="52">
+        <v>0.06559982005176752</v>
+      </c>
+      <c r="H21" s="54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" s="59">
+        <v>0.020838048090523337</v>
+      </c>
+      <c r="D22" s="52">
+        <v>0.22649221521704743</v>
+      </c>
+      <c r="E22" s="52">
+        <v>0.40865090641842233</v>
+      </c>
+      <c r="F22" s="52">
+        <v>0.5019717632430317</v>
+      </c>
+      <c r="G22" s="52">
+        <v>0.5640321961663076</v>
+      </c>
+      <c r="H22" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="59" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="60">
+        <v>3</v>
+      </c>
+      <c r="D23" s="60">
+        <v>3</v>
+      </c>
+      <c r="E23" s="60">
+        <v>3</v>
+      </c>
+      <c r="F23" s="60">
+        <v>3</v>
+      </c>
+      <c r="G23" s="60">
+        <v>3</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="61">
+        <v>0.6319081672107103</v>
+      </c>
+      <c r="D24" s="62">
+        <v>10.747650235238861</v>
+      </c>
+      <c r="E24" s="62">
+        <v>28.61956160951256</v>
+      </c>
+      <c r="F24" s="62">
+        <v>46.752155680255555</v>
+      </c>
+      <c r="G24" s="62">
+        <v>66.82825457722186</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="63" t="str">
         <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="37" t="str">
+      <c r="D25" s="37" t="str">
         <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="59" t="str">
+      <c r="E25" s="63" t="str">
         <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="59" t="str">
+      <c r="F25" s="63" t="str">
         <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="59" t="str">
+      <c r="G25" s="63" t="str">
         <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="H25" s="54" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C22" s="60">
-        <v>0</v>
-      </c>
-      <c r="D22" s="60">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26" s="64">
+        <v>0</v>
+      </c>
+      <c r="D26" s="64">
         <v>3</v>
       </c>
-      <c r="E22" s="60">
+      <c r="E26" s="64">
         <v>10</v>
       </c>
-      <c r="F22" s="61">
+      <c r="F26" s="65">
         <v>21</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G26" s="60">
         <v>34</v>
       </c>
-      <c r="H22" s="54" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="H26" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="C25" s="37" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="64">
+        <v>0</v>
+      </c>
+      <c r="D27" s="60">
+        <v>91</v>
+      </c>
+      <c r="E27" s="60">
+        <v>318</v>
+      </c>
+      <c r="F27" s="60">
+        <v>637</v>
+      </c>
+      <c r="G27" s="60">
+        <v>1030</v>
+      </c>
+      <c r="H27" s="54" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="63" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64" t="s">
+      <c r="C29" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+      <c r="D29" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
         <v>286</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64" t="s">
+      <c r="C30" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="D30" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="C27" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="63" t="s">
+      <c r="E30" s="67"/>
+      <c r="F30" s="68" t="s">
         <v>289</v>
       </c>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64" t="s">
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
+      <c r="C31" s="69" t="s">
         <v>291</v>
       </c>
-      <c r="C28" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" s="63" t="s">
+      <c r="D31" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64" t="s">
+      <c r="E31" s="67"/>
+      <c r="F31" s="68" t="s">
         <v>293</v>
       </c>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="62" t="s">
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="66" t="s">
         <v>294</v>
       </c>
-      <c r="C29" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D29" s="63" t="s">
+      <c r="C32" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="67" t="s">
         <v>295</v>
       </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64" t="s">
+      <c r="E32" s="67"/>
+      <c r="F32" s="68" t="s">
         <v>296</v>
       </c>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
         <v>297</v>
       </c>
-      <c r="C30" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D30" s="63" t="s">
+      <c r="C33" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D33" s="67" t="s">
         <v>298</v>
       </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="E33" s="67"/>
+      <c r="F33" s="68" t="s">
         <v>299</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
+      <c r="G33" s="68"/>
+      <c r="H33" s="68"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="66" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" s="63" t="s">
+      <c r="C34" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D34" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
+      <c r="E34" s="67"/>
+      <c r="F34" s="68" t="s">
         <v>302</v>
       </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C35" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="67" t="s">
         <v>304</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
+      <c r="E35" s="67"/>
+      <c r="F35" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="66" t="s">
+        <v>306</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="D36" s="67" t="s">
+        <v>307</v>
+      </c>
+      <c r="E36" s="67"/>
+      <c r="F36" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="66" t="s">
+        <v>309</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7181,48 +7317,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -15,7 +15,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F85</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F86</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="311">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -500,6 +500,9 @@
     <t>Heritage Academy Charter - 5-Year Financial Model</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>REVENUE</t>
   </si>
   <si>
@@ -641,7 +644,7 @@
     <t>COVENANT &amp; HEALTH CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Positive Net Income</t>
@@ -764,7 +767,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -902,13 +905,10 @@
     <t>Liquidity</t>
   </si>
   <si>
-    <t>○ Needs attention</t>
-  </si>
-  <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
-  </si>
-  <si>
-    <t>Secure a line of credit or bridge funding before operations begin.</t>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
   </si>
   <si>
     <t>Staffing Burden</t>
@@ -923,7 +923,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 5% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -932,7 +932,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 66.83x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 68.23x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -950,7 +950,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>33.9 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>36.6 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -959,7 +959,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
   </si>
 </sst>
 </file>
@@ -973,7 +973,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1041,6 +1041,12 @@
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1113,12 +1119,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1173,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1209,94 +1215,77 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3163,7 +3152,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -3180,254 +3169,244 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B3" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C3" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D3" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E3" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F3" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B4" s="29">
         <f>Assumptions!B17</f>
         <v>120</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C4" s="29">
         <f>Assumptions!C17</f>
         <v>200</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D4" s="29">
         <f>Assumptions!D17</f>
         <v>300</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E4" s="29">
         <f>Assumptions!E17</f>
         <v>400</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F4" s="29">
         <f>Assumptions!F17</f>
         <v>500</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="21">
-        <v>807500</v>
-      </c>
-      <c r="C6" s="21">
-        <v>1617850</v>
-      </c>
-      <c r="D6" s="21">
-        <v>2466200</v>
-      </c>
-      <c r="E6" s="21">
-        <v>3327850</v>
-      </c>
-      <c r="F6" s="21">
-        <v>4233200</v>
-      </c>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B7" s="21">
-        <v>75000</v>
+        <v>807500</v>
       </c>
       <c r="C7" s="21">
-        <v>153000</v>
+        <v>1617850</v>
       </c>
       <c r="D7" s="21">
-        <v>234000</v>
+        <v>2466200</v>
       </c>
       <c r="E7" s="21">
-        <v>318400</v>
+        <v>3327850</v>
       </c>
       <c r="F7" s="21">
-        <v>406000</v>
+        <v>4233200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="21">
-        <v>110000</v>
+        <v>75000</v>
       </c>
       <c r="C8" s="21">
-        <v>224400</v>
+        <v>153000</v>
       </c>
       <c r="D8" s="21">
-        <v>343200</v>
+        <v>234000</v>
       </c>
       <c r="E8" s="21">
-        <v>466800</v>
+        <v>318400</v>
       </c>
       <c r="F8" s="21">
-        <v>595500</v>
+        <v>406000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="21">
-        <v>125000</v>
+        <v>110000</v>
       </c>
       <c r="C9" s="21">
-        <v>100000</v>
+        <v>224400</v>
       </c>
       <c r="D9" s="21">
-        <v>50000</v>
+        <v>343200</v>
       </c>
       <c r="E9" s="21">
-        <v>0</v>
+        <v>466800</v>
       </c>
       <c r="F9" s="21">
-        <v>0</v>
+        <v>595500</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B10" s="21">
-        <v>20833</v>
+        <v>125000</v>
       </c>
       <c r="C10" s="21">
-        <v>35000</v>
+        <v>100000</v>
       </c>
       <c r="D10" s="21">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="E10" s="21">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="21">
-        <v>65000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="21">
+        <v>20833</v>
+      </c>
+      <c r="C11" s="21">
+        <v>35000</v>
+      </c>
+      <c r="D11" s="21">
+        <v>45000</v>
+      </c>
+      <c r="E11" s="21">
+        <v>55000</v>
+      </c>
+      <c r="F11" s="21">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B12" s="21">
         <v>40000</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C12" s="21">
         <v>82400</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D12" s="21">
         <v>127200</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E12" s="21">
         <v>174800</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F12" s="21">
         <v>225000</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="29">
-        <f>SUM(B6:B11)</f>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="30">
+        <f>SUM(B7:B12)</f>
         <v>1178333</v>
       </c>
-      <c r="C12" s="29">
-        <f>SUM(C6:C11)</f>
+      <c r="C13" s="30">
+        <f>SUM(C7:C12)</f>
         <v>2212650</v>
       </c>
-      <c r="D12" s="29">
-        <f>SUM(D6:D11)</f>
+      <c r="D13" s="30">
+        <f>SUM(D7:D12)</f>
         <v>3265600</v>
       </c>
-      <c r="E12" s="29">
-        <f>SUM(E6:E11)</f>
+      <c r="E13" s="30">
+        <f>SUM(E7:E12)</f>
         <v>4342850</v>
       </c>
-      <c r="F12" s="29">
-        <f>SUM(F6:F11)</f>
+      <c r="F13" s="30">
+        <f>SUM(F7:F12)</f>
         <v>5524700</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="21">
-        <v>116944</v>
-      </c>
-      <c r="C15" s="21">
-        <v>140333</v>
-      </c>
-      <c r="D15" s="21">
-        <v>140333</v>
-      </c>
-      <c r="E15" s="21">
-        <v>140333</v>
-      </c>
-      <c r="F15" s="21">
-        <v>140333</v>
-      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B16" s="21">
-        <v>91328</v>
+        <v>116944</v>
       </c>
       <c r="C16" s="21">
-        <v>109593</v>
+        <v>140333</v>
       </c>
       <c r="D16" s="21">
-        <v>109593</v>
+        <v>140333</v>
       </c>
       <c r="E16" s="21">
-        <v>109593</v>
+        <v>140333</v>
       </c>
       <c r="F16" s="21">
-        <v>109593</v>
+        <v>140333</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,19 +3414,19 @@
         <v>162</v>
       </c>
       <c r="B17" s="21">
-        <v>278438</v>
+        <v>91328</v>
       </c>
       <c r="C17" s="21">
-        <v>334125</v>
+        <v>109593</v>
       </c>
       <c r="D17" s="21">
-        <v>334125</v>
+        <v>109593</v>
       </c>
       <c r="E17" s="21">
-        <v>334125</v>
+        <v>109593</v>
       </c>
       <c r="F17" s="21">
-        <v>334125</v>
+        <v>109593</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,19 +3434,19 @@
         <v>163</v>
       </c>
       <c r="B18" s="21">
-        <v>59029</v>
+        <v>278438</v>
       </c>
       <c r="C18" s="21">
-        <v>70835</v>
+        <v>334125</v>
       </c>
       <c r="D18" s="21">
-        <v>70835</v>
+        <v>334125</v>
       </c>
       <c r="E18" s="21">
-        <v>70835</v>
+        <v>334125</v>
       </c>
       <c r="F18" s="21">
-        <v>70835</v>
+        <v>334125</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,19 +3454,19 @@
         <v>164</v>
       </c>
       <c r="B19" s="21">
-        <v>87955</v>
+        <v>59029</v>
       </c>
       <c r="C19" s="21">
-        <v>105546</v>
+        <v>70835</v>
       </c>
       <c r="D19" s="21">
-        <v>105546</v>
+        <v>70835</v>
       </c>
       <c r="E19" s="21">
-        <v>105546</v>
+        <v>70835</v>
       </c>
       <c r="F19" s="21">
-        <v>105546</v>
+        <v>70835</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3495,19 +3474,19 @@
         <v>165</v>
       </c>
       <c r="B20" s="21">
-        <v>69053</v>
+        <v>87955</v>
       </c>
       <c r="C20" s="21">
-        <v>82863</v>
+        <v>105546</v>
       </c>
       <c r="D20" s="21">
-        <v>82863</v>
+        <v>105546</v>
       </c>
       <c r="E20" s="21">
-        <v>82863</v>
+        <v>105546</v>
       </c>
       <c r="F20" s="21">
-        <v>82863</v>
+        <v>105546</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3515,204 +3494,204 @@
         <v>166</v>
       </c>
       <c r="B21" s="21">
+        <v>69053</v>
+      </c>
+      <c r="C21" s="21">
+        <v>82863</v>
+      </c>
+      <c r="D21" s="21">
+        <v>82863</v>
+      </c>
+      <c r="E21" s="21">
+        <v>82863</v>
+      </c>
+      <c r="F21" s="21">
+        <v>82863</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="21">
         <v>77790</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C22" s="21">
         <v>93348</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D22" s="21">
         <v>93348</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E22" s="21">
         <v>93348</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F22" s="21">
         <v>93348</v>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" s="29">
-        <f>SUM(B15:B21)</f>
+    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="30">
+        <f>SUM(B16:B22)</f>
         <v>780535</v>
       </c>
-      <c r="C22" s="29">
-        <f>SUM(C15:C21)</f>
+      <c r="C23" s="30">
+        <f>SUM(C16:C22)</f>
         <v>936642</v>
       </c>
-      <c r="D22" s="29">
-        <f>SUM(D15:D21)</f>
+      <c r="D23" s="30">
+        <f>SUM(D16:D22)</f>
         <v>936642</v>
       </c>
-      <c r="E22" s="29">
-        <f>SUM(E15:E21)</f>
+      <c r="E23" s="30">
+        <f>SUM(E16:E22)</f>
         <v>936642</v>
       </c>
-      <c r="F22" s="29">
-        <f>SUM(F15:F21)</f>
+      <c r="F23" s="30">
+        <f>SUM(F16:F22)</f>
         <v>936642</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="21">
+        <v>114</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="21">
         <v>65000</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C27" s="21">
         <v>134000</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D27" s="21">
         <v>207000</v>
       </c>
-      <c r="E26" s="21">
+      <c r="E27" s="21">
         <v>284000</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F27" s="21">
         <v>366000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="31">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="32">
         <v>65000</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C28" s="32">
         <v>134000</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D28" s="32">
         <v>207000</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E28" s="32">
         <v>284000</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F28" s="32">
         <v>366000</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B29" s="21">
+        <v>116</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" s="21">
         <v>45000</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C30" s="21">
         <v>92800</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D30" s="21">
         <v>143400</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E30" s="21">
         <v>196800</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F30" s="21">
         <v>253500</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="31">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" s="32">
         <v>45000</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="32">
         <v>92800</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D31" s="32">
         <v>143400</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E31" s="32">
         <v>196800</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F31" s="32">
         <v>253500</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B32" s="21">
-        <v>220000</v>
-      </c>
-      <c r="C32" s="21">
-        <v>271920</v>
-      </c>
-      <c r="D32" s="21">
-        <v>280078</v>
-      </c>
-      <c r="E32" s="21">
-        <v>288480</v>
-      </c>
-      <c r="F32" s="21">
-        <v>297134</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>173</v>
       </c>
       <c r="B33" s="21">
-        <v>30000</v>
+        <v>220000</v>
       </c>
       <c r="C33" s="21">
-        <v>37080</v>
+        <v>271920</v>
       </c>
       <c r="D33" s="21">
-        <v>38196</v>
+        <v>280078</v>
       </c>
       <c r="E33" s="21">
-        <v>39336</v>
+        <v>288480</v>
       </c>
       <c r="F33" s="21">
-        <v>40524</v>
+        <v>297134</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,89 +3699,89 @@
         <v>174</v>
       </c>
       <c r="B34" s="21">
+        <v>30000</v>
+      </c>
+      <c r="C34" s="21">
+        <v>37080</v>
+      </c>
+      <c r="D34" s="21">
+        <v>38196</v>
+      </c>
+      <c r="E34" s="21">
+        <v>39336</v>
+      </c>
+      <c r="F34" s="21">
+        <v>40524</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="21">
         <v>18333</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C35" s="21">
         <v>22660</v>
       </c>
-      <c r="D34" s="21">
+      <c r="D35" s="21">
         <v>23340</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E35" s="21">
         <v>24040</v>
       </c>
-      <c r="F34" s="21">
+      <c r="F35" s="21">
         <v>24761</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="B35" s="31">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="32">
         <v>268333</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="32">
         <v>331660</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D36" s="32">
         <v>341614</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E36" s="32">
         <v>351856</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F36" s="32">
         <v>362419</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B37" s="21">
-        <v>25000</v>
-      </c>
-      <c r="C37" s="21">
-        <v>30900</v>
-      </c>
-      <c r="D37" s="21">
-        <v>31827</v>
-      </c>
-      <c r="E37" s="21">
-        <v>32782</v>
-      </c>
-      <c r="F37" s="21">
-        <v>33765</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>177</v>
       </c>
       <c r="B38" s="21">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="C38" s="21">
-        <v>12360</v>
+        <v>30900</v>
       </c>
       <c r="D38" s="21">
-        <v>12731</v>
+        <v>31827</v>
       </c>
       <c r="E38" s="21">
-        <v>13113</v>
+        <v>32782</v>
       </c>
       <c r="F38" s="21">
-        <v>13506</v>
+        <v>33765</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3810,19 +3789,19 @@
         <v>178</v>
       </c>
       <c r="B39" s="21">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="C39" s="21">
-        <v>18540</v>
+        <v>12360</v>
       </c>
       <c r="D39" s="21">
-        <v>19096</v>
+        <v>12731</v>
       </c>
       <c r="E39" s="21">
-        <v>19669</v>
+        <v>13113</v>
       </c>
       <c r="F39" s="21">
-        <v>20259</v>
+        <v>13506</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3830,199 +3809,194 @@
         <v>179</v>
       </c>
       <c r="B40" s="21">
+        <v>15000</v>
+      </c>
+      <c r="C40" s="21">
+        <v>18540</v>
+      </c>
+      <c r="D40" s="21">
+        <v>19096</v>
+      </c>
+      <c r="E40" s="21">
+        <v>19669</v>
+      </c>
+      <c r="F40" s="21">
+        <v>20259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="21">
         <v>75000</v>
       </c>
-      <c r="C40" s="21">
+      <c r="C41" s="21">
         <v>154600</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D41" s="21">
         <v>238800</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E41" s="21">
         <v>328000</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F41" s="21">
         <v>422500</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="B41" s="31">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="32">
         <v>125000</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C42" s="32">
         <v>216400</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D42" s="32">
         <v>302454</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E42" s="32">
         <v>393564</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F42" s="32">
         <v>490030</v>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B42" s="29">
-        <f>B27+B30+B35+B41</f>
+    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="30">
+        <f>B28+B31+B36+B42</f>
         <v>503333</v>
       </c>
-      <c r="C42" s="29">
-        <f>C27+C30+C35+C41</f>
+      <c r="C43" s="30">
+        <f>C28+C31+C36+C42</f>
         <v>774860</v>
       </c>
-      <c r="D42" s="29">
-        <f>D27+D30+D35+D41</f>
+      <c r="D43" s="30">
+        <f>D28+D31+D36+D42</f>
         <v>994468</v>
       </c>
-      <c r="E42" s="29">
-        <f>E27+E30+E35+E41</f>
+      <c r="E43" s="30">
+        <f>E28+E31+E36+E42</f>
         <v>1226220</v>
       </c>
-      <c r="F42" s="29">
-        <f>F27+F30+F35+F41</f>
+      <c r="F43" s="30">
+        <f>F28+F31+F36+F42</f>
         <v>1471949</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B45" s="21">
-        <v>46629</v>
-      </c>
-      <c r="C45" s="21">
-        <v>46629</v>
-      </c>
-      <c r="D45" s="21">
-        <v>46629</v>
-      </c>
-      <c r="E45" s="21">
-        <v>46629</v>
-      </c>
-      <c r="F45" s="21">
-        <v>46629</v>
-      </c>
+    <row r="45" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="21">
+        <v>46629</v>
+      </c>
+      <c r="C46" s="21">
+        <v>46629</v>
+      </c>
+      <c r="D46" s="21">
+        <v>46629</v>
+      </c>
+      <c r="E46" s="21">
+        <v>46629</v>
+      </c>
+      <c r="F46" s="21">
+        <v>46629</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B47" s="21">
         <v>60000</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C47" s="21">
         <v>20000</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D47" s="21">
         <v>25000</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E47" s="21">
         <v>10000</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F47" s="21">
         <v>10000</v>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B47" s="29">
-        <f>SUM(B45:B46)</f>
+    <row r="48" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="30">
+        <f>SUM(B46:B47)</f>
         <v>106629</v>
       </c>
-      <c r="C47" s="29">
-        <f>SUM(C45:C46)</f>
+      <c r="C48" s="30">
+        <f>SUM(C46:C47)</f>
         <v>66629</v>
       </c>
-      <c r="D47" s="29">
-        <f>SUM(D45:D46)</f>
+      <c r="D48" s="30">
+        <f>SUM(D46:D47)</f>
         <v>71629</v>
       </c>
-      <c r="E47" s="29">
-        <f>SUM(E45:E46)</f>
+      <c r="E48" s="30">
+        <f>SUM(E46:E47)</f>
         <v>56629</v>
       </c>
-      <c r="F47" s="29">
-        <f>SUM(F45:F46)</f>
+      <c r="F48" s="30">
+        <f>SUM(F46:F47)</f>
         <v>56629</v>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="27" t="s">
+    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B50" s="31">
-        <f>B12</f>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="32">
+        <f>B13</f>
         <v>1178333</v>
       </c>
-      <c r="C50" s="31">
-        <f>C12</f>
+      <c r="C51" s="32">
+        <f>C13</f>
         <v>2212650</v>
       </c>
-      <c r="D50" s="31">
-        <f>D12</f>
+      <c r="D51" s="32">
+        <f>D13</f>
         <v>3265600</v>
       </c>
-      <c r="E50" s="31">
-        <f>E12</f>
+      <c r="E51" s="32">
+        <f>E13</f>
         <v>4342850</v>
       </c>
-      <c r="F50" s="31">
-        <f>F12</f>
+      <c r="F51" s="32">
+        <f>F13</f>
         <v>5524700</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B51" s="21">
-        <f>B22</f>
-        <v>780535</v>
-      </c>
-      <c r="C51" s="21">
-        <f>C22</f>
-        <v>936642</v>
-      </c>
-      <c r="D51" s="21">
-        <f>D22</f>
-        <v>936642</v>
-      </c>
-      <c r="E51" s="21">
-        <f>E22</f>
-        <v>936642</v>
-      </c>
-      <c r="F51" s="21">
-        <f>F22</f>
-        <v>936642</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4030,24 +4004,24 @@
         <v>187</v>
       </c>
       <c r="B52" s="21">
-        <f>B42</f>
-        <v>503333</v>
+        <f>B23</f>
+        <v>780535</v>
       </c>
       <c r="C52" s="21">
-        <f>C42</f>
-        <v>774860</v>
+        <f>C23</f>
+        <v>936642</v>
       </c>
       <c r="D52" s="21">
-        <f>D42</f>
-        <v>994468</v>
+        <f>D23</f>
+        <v>936642</v>
       </c>
       <c r="E52" s="21">
-        <f>E42</f>
-        <v>1226220</v>
+        <f>E23</f>
+        <v>936642</v>
       </c>
       <c r="F52" s="21">
-        <f>F42</f>
-        <v>1471949</v>
+        <f>F23</f>
+        <v>936642</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4055,309 +4029,309 @@
         <v>188</v>
       </c>
       <c r="B53" s="21">
-        <f>B47</f>
+        <f>B43</f>
+        <v>503333</v>
+      </c>
+      <c r="C53" s="21">
+        <f>C43</f>
+        <v>774860</v>
+      </c>
+      <c r="D53" s="21">
+        <f>D43</f>
+        <v>994468</v>
+      </c>
+      <c r="E53" s="21">
+        <f>E43</f>
+        <v>1226220</v>
+      </c>
+      <c r="F53" s="21">
+        <f>F43</f>
+        <v>1471949</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="21">
+        <f>B48</f>
         <v>106629</v>
       </c>
-      <c r="C53" s="21">
-        <f>C47</f>
+      <c r="C54" s="21">
+        <f>C48</f>
         <v>66629</v>
       </c>
-      <c r="D53" s="21">
-        <f>D47</f>
+      <c r="D54" s="21">
+        <f>D48</f>
         <v>71629</v>
       </c>
-      <c r="E53" s="21">
-        <f>E47</f>
+      <c r="E54" s="21">
+        <f>E48</f>
         <v>56629</v>
       </c>
-      <c r="F53" s="21">
-        <f>F47</f>
+      <c r="F54" s="21">
+        <f>F48</f>
         <v>56629</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="B54" s="31">
-        <f>B51+B52+B53</f>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="32">
+        <f>B52+B53+B54</f>
         <v>1390497</v>
       </c>
-      <c r="C54" s="31">
-        <f>C51+C52+C53</f>
+      <c r="C55" s="32">
+        <f>C52+C53+C54</f>
         <v>1778131</v>
       </c>
-      <c r="D54" s="31">
-        <f>D51+D52+D53</f>
+      <c r="D55" s="32">
+        <f>D52+D53+D54</f>
         <v>2002739</v>
       </c>
-      <c r="E54" s="31">
-        <f>E51+E52+E53</f>
+      <c r="E55" s="32">
+        <f>E52+E53+E54</f>
         <v>2219491</v>
       </c>
-      <c r="F54" s="31">
-        <f>F51+F52+F53</f>
+      <c r="F55" s="32">
+        <f>F52+F53+F54</f>
         <v>2465220</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="B56" s="33">
-        <f>B50-B54</f>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="34">
+        <f>B51-B55</f>
         <v>-212164</v>
       </c>
-      <c r="C56" s="34">
-        <f>C50-C54</f>
+      <c r="C57" s="35">
+        <f>C51-C55</f>
         <v>434519</v>
       </c>
-      <c r="D56" s="34">
-        <f>D50-D54</f>
+      <c r="D57" s="35">
+        <f>D51-D55</f>
         <v>1262861</v>
       </c>
-      <c r="E56" s="34">
-        <f>E50-E54</f>
+      <c r="E57" s="35">
+        <f>E51-E55</f>
         <v>2123359</v>
       </c>
-      <c r="F56" s="34">
-        <f>F50-F54</f>
+      <c r="F57" s="35">
+        <f>F51-F55</f>
         <v>3059480</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B57" s="35">
-        <f>IF(B50=0,"",B56/B50)</f>
-        <v>-0.18</v>
-      </c>
-      <c r="C57" s="35">
-        <f>IF(C50=0,"",C56/C50)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D57" s="35">
-        <f>IF(D50=0,"",D56/D50)</f>
-        <v>0.39</v>
-      </c>
-      <c r="E57" s="35">
-        <f>IF(E50=0,"",E56/E50)</f>
-        <v>0.49</v>
-      </c>
-      <c r="F57" s="35">
-        <f>IF(F50=0,"",F56/F50)</f>
-        <v>0.55</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B58" s="21">
-        <f>B56</f>
+      <c r="B58" s="36">
+        <f>IF(B51=0,"",B57/B51)</f>
+        <v>-0.18005436</v>
+      </c>
+      <c r="C58" s="36">
+        <f>IF(C51=0,"",C57/C51)</f>
+        <v>0.19637945</v>
+      </c>
+      <c r="D58" s="36">
+        <f>IF(D51=0,"",D57/D51)</f>
+        <v>0.38671638</v>
+      </c>
+      <c r="E58" s="36">
+        <f>IF(E51=0,"",E57/E51)</f>
+        <v>0.48893215</v>
+      </c>
+      <c r="F58" s="36">
+        <f>IF(F51=0,"",F57/F51)</f>
+        <v>0.55378211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="21">
+        <f>B57</f>
         <v>-212164</v>
       </c>
-      <c r="C58" s="21">
-        <f>B58+C56</f>
+      <c r="C59" s="21">
+        <f>B59+C57</f>
         <v>222355</v>
       </c>
-      <c r="D58" s="21">
-        <f>C58+D56</f>
+      <c r="D59" s="21">
+        <f>C59+D57</f>
         <v>1485216</v>
       </c>
-      <c r="E58" s="21">
-        <f>D58+E56</f>
+      <c r="E59" s="21">
+        <f>D59+E57</f>
         <v>3608575</v>
       </c>
-      <c r="F58" s="21">
-        <f>E58+F56</f>
+      <c r="F59" s="21">
+        <f>E59+F57</f>
         <v>6668055</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="B59" s="36" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D59" s="36" t="s">
+      <c r="C60" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="D60" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E59" s="36" t="s">
+      <c r="E60" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F60" s="37" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="27" t="s">
+    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B62" s="31">
-        <f>B50-B51-B52</f>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" s="32">
+        <f>B51-B52-B53</f>
         <v>-105535</v>
       </c>
-      <c r="C62" s="31">
-        <f>C50-C51-C52</f>
+      <c r="C63" s="32">
+        <f>C51-C52-C53</f>
         <v>501148</v>
       </c>
-      <c r="D62" s="31">
-        <f>D50-D51-D52</f>
+      <c r="D63" s="32">
+        <f>D51-D52-D53</f>
         <v>1334490</v>
       </c>
-      <c r="E62" s="31">
-        <f>E50-E51-E52</f>
+      <c r="E63" s="32">
+        <f>E51-E52-E53</f>
         <v>2179988</v>
       </c>
-      <c r="F62" s="31">
-        <f>F50-F51-F52</f>
+      <c r="F63" s="32">
+        <f>F51-F52-F53</f>
         <v>3116109</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="B63" s="21">
-        <f>B53</f>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="21">
+        <f>B54</f>
         <v>106629</v>
       </c>
-      <c r="C63" s="21">
-        <f>C53</f>
+      <c r="C64" s="21">
+        <f>C54</f>
         <v>66629</v>
       </c>
-      <c r="D63" s="21">
-        <f>D53</f>
+      <c r="D64" s="21">
+        <f>D54</f>
         <v>71629</v>
       </c>
-      <c r="E63" s="21">
-        <f>E53</f>
+      <c r="E64" s="21">
+        <f>E54</f>
         <v>56629</v>
       </c>
-      <c r="F63" s="21">
-        <f>F53</f>
+      <c r="F64" s="21">
+        <f>F54</f>
         <v>56629</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="B64" s="38">
-        <f>IF(B63=0,"N/A",B62/B63)</f>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" s="39">
+        <f>IF(B64=0,"N/A",B63/B64)</f>
         <v>-0.99</v>
       </c>
-      <c r="C64" s="38">
-        <f>IF(C63=0,"N/A",C62/C63)</f>
+      <c r="C65" s="39">
+        <f>IF(C64=0,"N/A",C63/C64)</f>
         <v>7.52</v>
       </c>
-      <c r="D64" s="38">
-        <f>IF(D63=0,"N/A",D62/D63)</f>
+      <c r="D65" s="39">
+        <f>IF(D64=0,"N/A",D63/D64)</f>
         <v>18.63</v>
       </c>
-      <c r="E64" s="38">
-        <f>IF(E63=0,"N/A",E62/E63)</f>
+      <c r="E65" s="39">
+        <f>IF(E64=0,"N/A",E63/E64)</f>
         <v>38.5</v>
       </c>
-      <c r="F64" s="38">
-        <f>IF(F63=0,"N/A",F62/F63)</f>
+      <c r="F65" s="39">
+        <f>IF(F64=0,"N/A",F63/F64)</f>
         <v>55.03</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B65" s="21" t="str">
+      <c r="B66" s="21" t="str">
         <f>Assumptions!B63</f>
         <v>0</v>
       </c>
-      <c r="C65" s="21">
-        <f>B66</f>
+      <c r="C66" s="21">
+        <f>B67</f>
         <v>-212164</v>
       </c>
-      <c r="D65" s="21">
-        <f>C66</f>
+      <c r="D66" s="21">
+        <f>C67</f>
         <v>222355</v>
       </c>
-      <c r="E65" s="21">
-        <f>D66</f>
+      <c r="E66" s="21">
+        <f>D67</f>
         <v>1485216</v>
       </c>
-      <c r="F65" s="21">
-        <f>E66</f>
+      <c r="F66" s="21">
+        <f>E67</f>
         <v>3608575</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="31">
-        <f>B65+B56</f>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="32">
+        <f>B66+B57</f>
         <v>-212164</v>
       </c>
-      <c r="C66" s="31">
-        <f>C65+C56</f>
+      <c r="C67" s="32">
+        <f>C66+C57</f>
         <v>222355</v>
       </c>
-      <c r="D66" s="31">
-        <f>D65+D56</f>
+      <c r="D67" s="32">
+        <f>D66+D57</f>
         <v>1485216</v>
       </c>
-      <c r="E66" s="31">
-        <f>E65+E56</f>
+      <c r="E67" s="32">
+        <f>E66+E57</f>
         <v>3608575</v>
       </c>
-      <c r="F66" s="31">
-        <f>F65+F56</f>
+      <c r="F67" s="32">
+        <f>F66+F57</f>
         <v>6668055</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B67" s="39">
-        <f>IF(B54=0,"",B66/B54*365)</f>
-        <v>-56</v>
-      </c>
-      <c r="C67" s="39">
-        <f>IF(C54=0,"",C66/C54*365)</f>
-        <v>46</v>
-      </c>
-      <c r="D67" s="39">
-        <f>IF(D54=0,"",D66/D54*365)</f>
-        <v>271</v>
-      </c>
-      <c r="E67" s="39">
-        <f>IF(E54=0,"",E66/E54*365)</f>
-        <v>593</v>
-      </c>
-      <c r="F67" s="39">
-        <f>IF(F54=0,"",F66/F54*365)</f>
-        <v>987</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4365,108 +4339,108 @@
         <v>201</v>
       </c>
       <c r="B68" s="40">
-        <f>IF(B54=0,"",B66/(B54/12))</f>
-        <v>-1.8</v>
+        <f>IF(B55=0,"",B67/B55*365)</f>
+        <v>-56</v>
       </c>
       <c r="C68" s="40">
-        <f>IF(C54=0,"",C66/(C54/12))</f>
-        <v>1.5</v>
+        <f>IF(C55=0,"",C67/C55*365)</f>
+        <v>46</v>
       </c>
       <c r="D68" s="40">
-        <f>IF(D54=0,"",D66/(D54/12))</f>
-        <v>8.9</v>
+        <f>IF(D55=0,"",D67/D55*365)</f>
+        <v>271</v>
       </c>
       <c r="E68" s="40">
-        <f>IF(E54=0,"",E66/(E54/12))</f>
-        <v>19.5</v>
+        <f>IF(E55=0,"",E67/E55*365)</f>
+        <v>593</v>
       </c>
       <c r="F68" s="40">
-        <f>IF(F54=0,"",F66/(F54/12))</f>
-        <v>32.5</v>
+        <f>IF(F55=0,"",F67/F55*365)</f>
+        <v>987</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B69" s="35">
-        <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
+      <c r="B69" s="41">
+        <f>IF(B55=0,"",B67/(B55/12))</f>
+        <v>-1.8</v>
+      </c>
+      <c r="C69" s="41">
+        <f>IF(C55=0,"",C67/(C55/12))</f>
+        <v>1.5</v>
+      </c>
+      <c r="D69" s="41">
+        <f>IF(D55=0,"",D67/(D55/12))</f>
+        <v>8.9</v>
+      </c>
+      <c r="E69" s="41">
+        <f>IF(E55=0,"",E67/(E55/12))</f>
+        <v>19.5</v>
+      </c>
+      <c r="F69" s="41">
+        <f>IF(F55=0,"",F67/(F55/12))</f>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" s="36">
+        <f>IF(Assumptions!B12=0,"",B4/Assumptions!B12)</f>
         <v>0.2</v>
       </c>
-      <c r="C69" s="35">
-        <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
-        <v>0.33</v>
-      </c>
-      <c r="D69" s="35">
-        <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
+      <c r="C70" s="36">
+        <f>IF(Assumptions!B12=0,"",C4/Assumptions!B12)</f>
+        <v>0.33333333</v>
+      </c>
+      <c r="D70" s="36">
+        <f>IF(Assumptions!B12=0,"",D4/Assumptions!B12)</f>
         <v>0.5</v>
       </c>
-      <c r="E69" s="35">
-        <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
-        <v>0.67</v>
-      </c>
-      <c r="F69" s="35">
-        <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
+      <c r="E70" s="36">
+        <f>IF(Assumptions!B12=0,"",E4/Assumptions!B12)</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="F70" s="36">
+        <f>IF(Assumptions!B12=0,"",F4/Assumptions!B12)</f>
+        <v>0.83333333</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B72" s="13" t="str">
-        <f>IF(B63=0,"N/A",IF(B64&gt;=1.2,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="C72" s="13" t="str">
-        <f>IF(C63=0,"N/A",IF(C64&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D72" s="13" t="str">
-        <f>IF(D63=0,"N/A",IF(D64&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E72" s="13" t="str">
-        <f>IF(E63=0,"N/A",IF(E64&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F72" s="13" t="str">
-        <f>IF(F63=0,"N/A",IF(F64&gt;=1.2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>205</v>
       </c>
       <c r="B73" s="13" t="str">
-        <f>IF(B56&gt;0,"PASS","FAIL")</f>
+        <f>IF(B64=0,"N/A",IF(B65&gt;=1.25,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="C73" s="13" t="str">
-        <f>IF(C56&gt;0,"PASS","FAIL")</f>
+        <f>IF(C64=0,"N/A",IF(C65&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="D73" s="13" t="str">
-        <f>IF(D56&gt;0,"PASS","FAIL")</f>
+        <f>IF(D64=0,"N/A",IF(D65&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="E73" s="13" t="str">
-        <f>IF(E56&gt;0,"PASS","FAIL")</f>
+        <f>IF(E64=0,"N/A",IF(E65&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
       <c r="F73" s="13" t="str">
-        <f>IF(F56&gt;0,"PASS","FAIL")</f>
+        <f>IF(F64=0,"N/A",IF(F65&gt;=1.25,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4475,23 +4449,23 @@
         <v>206</v>
       </c>
       <c r="B74" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(B57&gt;0,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="C74" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
+        <f>IF(C57&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
       <c r="D74" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
+        <f>IF(D57&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
       <c r="E74" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
+        <f>IF(E57&gt;0,"PASS","FAIL")</f>
+        <v>PASS</v>
       </c>
       <c r="F74" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <f>IF(F57&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4500,84 +4474,84 @@
         <v>207</v>
       </c>
       <c r="B75" s="13" t="str">
-        <f>IF(B54=0,"N/A",IF(B66/(B54/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(B4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="C75" s="13" t="str">
-        <f>IF(C54=0,"N/A",IF(C66/(C54/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(C4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>FAIL</v>
       </c>
       <c r="D75" s="13" t="str">
-        <f>IF(D54=0,"N/A",IF(D66/(D54/12)&gt;=2,"PASS","FAIL"))</f>
+        <f>IF(Assumptions!B12=0,"N/A",IF(D4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="E75" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(E4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="F75" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(F4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="E75" s="13" t="str">
-        <f>IF(E54=0,"N/A",IF(E66/(E54/12)&gt;=2,"PASS","FAIL"))</f>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" s="13" t="str">
+        <f>IF(B55=0,"N/A",IF(B67/(B55/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C76" s="13" t="str">
+        <f>IF(C55=0,"N/A",IF(C67/(C55/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="D76" s="13" t="str">
+        <f>IF(D55=0,"N/A",IF(D67/(D55/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-      <c r="F75" s="13" t="str">
-        <f>IF(F54=0,"N/A",IF(F66/(F54/12)&gt;=2,"PASS","FAIL"))</f>
+      <c r="E76" s="13" t="str">
+        <f>IF(E55=0,"N/A",IF(E67/(E55/12)&gt;=2,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="77" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="F76" s="13" t="str">
+        <f>IF(F55=0,"N/A",IF(F67/(F55/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B78" s="21">
-        <f>IF(B3=0,"",B12/B3)</f>
-        <v>9819</v>
-      </c>
-      <c r="C78" s="21">
-        <f>IF(C3=0,"",C12/C3)</f>
-        <v>11063</v>
-      </c>
-      <c r="D78" s="21">
-        <f>IF(D3=0,"",D12/D3)</f>
-        <v>10885</v>
-      </c>
-      <c r="E78" s="21">
-        <f>IF(E3=0,"",E12/E3)</f>
-        <v>10857</v>
-      </c>
-      <c r="F78" s="21">
-        <f>IF(F3=0,"",F12/F3)</f>
-        <v>11049</v>
-      </c>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>210</v>
       </c>
       <c r="B79" s="21">
-        <f>IF(B3=0,"",B54/B3)</f>
-        <v>11587</v>
+        <f>IF(B4=0,"",B13/B4)</f>
+        <v>9819</v>
       </c>
       <c r="C79" s="21">
-        <f>IF(C3=0,"",C54/C3)</f>
-        <v>8891</v>
+        <f>IF(C4=0,"",C13/C4)</f>
+        <v>11063</v>
       </c>
       <c r="D79" s="21">
-        <f>IF(D3=0,"",D54/D3)</f>
-        <v>6676</v>
+        <f>IF(D4=0,"",D13/D4)</f>
+        <v>10885</v>
       </c>
       <c r="E79" s="21">
-        <f>IF(E3=0,"",E54/E3)</f>
-        <v>5549</v>
+        <f>IF(E4=0,"",E13/E4)</f>
+        <v>10857</v>
       </c>
       <c r="F79" s="21">
-        <f>IF(F3=0,"",F54/F3)</f>
-        <v>4930</v>
+        <f>IF(F4=0,"",F13/F4)</f>
+        <v>11049</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4585,24 +4559,24 @@
         <v>211</v>
       </c>
       <c r="B80" s="21">
-        <f>B51+B53</f>
-        <v>887164</v>
+        <f>IF(B4=0,"",B55/B4)</f>
+        <v>11587</v>
       </c>
       <c r="C80" s="21">
-        <f>C51+C53</f>
-        <v>1003271</v>
+        <f>IF(C4=0,"",C55/C4)</f>
+        <v>8891</v>
       </c>
       <c r="D80" s="21">
-        <f>D51+D53</f>
-        <v>1008271</v>
+        <f>IF(D4=0,"",D55/D4)</f>
+        <v>6676</v>
       </c>
       <c r="E80" s="21">
-        <f>E51+E53</f>
-        <v>993271</v>
+        <f>IF(E4=0,"",E55/E4)</f>
+        <v>5549</v>
       </c>
       <c r="F80" s="21">
-        <f>F51+F53</f>
-        <v>993271</v>
+        <f>IF(F4=0,"",F55/F4)</f>
+        <v>4930</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,24 +4584,24 @@
         <v>212</v>
       </c>
       <c r="B81" s="21">
-        <f>IF(B3=0,"",B52/B3)</f>
-        <v>4194</v>
+        <f>B52+B54</f>
+        <v>887164</v>
       </c>
       <c r="C81" s="21">
-        <f>IF(C3=0,"",C52/C3)</f>
-        <v>3874</v>
+        <f>C52+C54</f>
+        <v>1003271</v>
       </c>
       <c r="D81" s="21">
-        <f>IF(D3=0,"",D52/D3)</f>
-        <v>3315</v>
+        <f>D52+D54</f>
+        <v>1008271</v>
       </c>
       <c r="E81" s="21">
-        <f>IF(E3=0,"",E52/E3)</f>
-        <v>3066</v>
+        <f>E52+E54</f>
+        <v>993271</v>
       </c>
       <c r="F81" s="21">
-        <f>IF(F3=0,"",F52/F3)</f>
-        <v>2944</v>
+        <f>F52+F54</f>
+        <v>993271</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4635,65 +4609,91 @@
         <v>213</v>
       </c>
       <c r="B82" s="21">
-        <f>IF(B3=0,"",B78-B81)</f>
+        <f>IF(B4=0,"",B53/B4)</f>
+        <v>4194</v>
+      </c>
+      <c r="C82" s="21">
+        <f>IF(C4=0,"",C53/C4)</f>
+        <v>3874</v>
+      </c>
+      <c r="D82" s="21">
+        <f>IF(D4=0,"",D53/D4)</f>
+        <v>3315</v>
+      </c>
+      <c r="E82" s="21">
+        <f>IF(E4=0,"",E53/E4)</f>
+        <v>3066</v>
+      </c>
+      <c r="F82" s="21">
+        <f>IF(F4=0,"",F53/F4)</f>
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" s="21">
+        <f>IF(B4=0,"",B79-B82)</f>
         <v>5625</v>
       </c>
-      <c r="C82" s="21">
-        <f>IF(C3=0,"",C78-C81)</f>
+      <c r="C83" s="21">
+        <f>IF(C4=0,"",C79-C82)</f>
         <v>7189</v>
       </c>
-      <c r="D82" s="21">
-        <f>IF(D3=0,"",D78-D81)</f>
+      <c r="D83" s="21">
+        <f>IF(D4=0,"",D79-D82)</f>
         <v>7570</v>
       </c>
-      <c r="E82" s="21">
-        <f>IF(E3=0,"",E78-E81)</f>
+      <c r="E83" s="21">
+        <f>IF(E4=0,"",E79-E82)</f>
         <v>7792</v>
       </c>
-      <c r="F82" s="21">
-        <f>IF(F3=0,"",F78-F81)</f>
+      <c r="F83" s="21">
+        <f>IF(F4=0,"",F79-F82)</f>
         <v>8106</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="B83" s="42">
-        <f>IF(B82&lt;=0,"N/A",ROUNDUP(B80/B82,0))</f>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B84" s="43">
+        <f>IF(B83&lt;=0,"N/A",ROUNDUP(B81/B83,0))</f>
         <v>158</v>
       </c>
-      <c r="C83" s="42">
-        <f>IF(C82&lt;=0,"N/A",ROUNDUP(C80/C82,0))</f>
+      <c r="C84" s="43">
+        <f>IF(C83&lt;=0,"N/A",ROUNDUP(C81/C83,0))</f>
         <v>140</v>
       </c>
-      <c r="D83" s="42">
-        <f>IF(D82&lt;=0,"N/A",ROUNDUP(D80/D82,0))</f>
+      <c r="D84" s="43">
+        <f>IF(D83&lt;=0,"N/A",ROUNDUP(D81/D83,0))</f>
         <v>134</v>
       </c>
-      <c r="E83" s="42">
-        <f>IF(E82&lt;=0,"N/A",ROUNDUP(E80/E82,0))</f>
+      <c r="E84" s="43">
+        <f>IF(E83&lt;=0,"N/A",ROUNDUP(E81/E83,0))</f>
         <v>128</v>
       </c>
-      <c r="F83" s="42">
-        <f>IF(F82&lt;=0,"N/A",ROUNDUP(F80/F82,0))</f>
+      <c r="F84" s="43">
+        <f>IF(F83&lt;=0,"N/A",ROUNDUP(F81/F83,0))</f>
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="26" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A86:F86"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -4719,7 +4719,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4743,45 +4743,45 @@
         <v>46</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -5069,57 +5069,57 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="29">
+        <v>159</v>
+      </c>
+      <c r="B10" s="30">
         <f>SUM(B4:B9)</f>
         <v>146500</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>SUM(C4:C9)</f>
         <v>146500</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>SUM(D4:D9)</f>
         <v>146500</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>SUM(E4:E9)</f>
         <v>146500</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>SUM(F4:F9)</f>
         <v>146500</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>SUM(G4:G9)</f>
         <v>146500</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>SUM(H4:H9)</f>
         <v>146500</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>SUM(I4:I9)</f>
         <v>146500</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="30">
         <f>SUM(J4:J9)</f>
         <v>146500</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="30">
         <f>SUM(K4:K9)</f>
         <v>146500</v>
       </c>
-      <c r="L10" s="29" t="str">
+      <c r="L10" s="30" t="str">
         <f>SUM(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="29" t="str">
+      <c r="M10" s="30" t="str">
         <f>SUM(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="29">
+      <c r="N10" s="30">
         <f>SUM(B10:M10)</f>
         <v>1465000</v>
       </c>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -5464,57 +5464,57 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B20" s="29">
+        <v>168</v>
+      </c>
+      <c r="B20" s="30">
         <f>SUM(B13:B19)</f>
         <v>78054</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>SUM(C13:C19)</f>
         <v>78054</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>SUM(D13:D19)</f>
         <v>78054</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>SUM(E13:E19)</f>
         <v>78054</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>SUM(F13:F19)</f>
         <v>78054</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <f>SUM(G13:G19)</f>
         <v>78054</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="30">
         <f>SUM(H13:H19)</f>
         <v>78054</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="30">
         <f>SUM(I13:I19)</f>
         <v>78054</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="30">
         <f>SUM(J13:J19)</f>
         <v>78054</v>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="30">
         <f>SUM(K13:K19)</f>
         <v>78054</v>
       </c>
-      <c r="L20" s="29" t="str">
+      <c r="L20" s="30" t="str">
         <f>SUM(L13:L19)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="29" t="str">
+      <c r="M20" s="30" t="str">
         <f>SUM(M13:M19)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="30">
         <f>SUM(B20:M20)</f>
         <v>780535</v>
       </c>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B24" s="21">
         <v>6500</v>
@@ -5606,46 +5606,46 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="32">
         <v>6500</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>6500</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>6500</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>6500</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>6500</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>6500</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>6500</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>6500</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>6500</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>6500</v>
       </c>
-      <c r="L25" s="31">
-        <v>0</v>
-      </c>
-      <c r="M25" s="31">
-        <v>0</v>
-      </c>
-      <c r="N25" s="31">
+      <c r="L25" s="32">
+        <v>0</v>
+      </c>
+      <c r="M25" s="32">
+        <v>0</v>
+      </c>
+      <c r="N25" s="32">
         <f>SUM(B25:M25)</f>
         <v>65000</v>
       </c>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B27" s="21">
         <v>4500</v>
@@ -5714,46 +5714,46 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="32">
         <v>4500</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>4500</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>4500</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>4500</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>4500</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>4500</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>4500</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>4500</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>4500</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>4500</v>
       </c>
-      <c r="L28" s="31">
-        <v>0</v>
-      </c>
-      <c r="M28" s="31">
-        <v>0</v>
-      </c>
-      <c r="N28" s="31">
+      <c r="L28" s="32">
+        <v>0</v>
+      </c>
+      <c r="M28" s="32">
+        <v>0</v>
+      </c>
+      <c r="N28" s="32">
         <f>SUM(B28:M28)</f>
         <v>45000</v>
       </c>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B30" s="21">
         <v>22000</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B31" s="21">
         <v>3000</v>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B32" s="21">
         <v>1833</v>
@@ -5912,46 +5912,46 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33" s="31">
+      <c r="A33" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="32">
         <v>26833</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="32">
         <v>26833</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="32">
         <v>26833</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="32">
         <v>26833</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="32">
         <v>26833</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="32">
         <v>26833</v>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <v>26833</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="32">
         <v>26833</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="32">
         <v>26833</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="32">
         <v>26833</v>
       </c>
-      <c r="L33" s="31">
-        <v>0</v>
-      </c>
-      <c r="M33" s="31">
-        <v>0</v>
-      </c>
-      <c r="N33" s="31">
+      <c r="L33" s="32">
+        <v>0</v>
+      </c>
+      <c r="M33" s="32">
+        <v>0</v>
+      </c>
+      <c r="N33" s="32">
         <f>SUM(B33:M33)</f>
         <v>268333</v>
       </c>
@@ -5976,7 +5976,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B35" s="21">
         <v>2500</v>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B36" s="21">
         <v>1000</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B37" s="21">
         <v>1500</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B38" s="21">
         <v>7500</v>
@@ -6155,103 +6155,103 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" s="32">
         <v>12500</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>12500</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>12500</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>12500</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>12500</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>12500</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>12500</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>12500</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>12500</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>12500</v>
       </c>
-      <c r="L39" s="31">
-        <v>0</v>
-      </c>
-      <c r="M39" s="31">
-        <v>0</v>
-      </c>
-      <c r="N39" s="31">
+      <c r="L39" s="32">
+        <v>0</v>
+      </c>
+      <c r="M39" s="32">
+        <v>0</v>
+      </c>
+      <c r="N39" s="32">
         <f>SUM(B39:M39)</f>
         <v>125000</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B40" s="29">
+        <v>182</v>
+      </c>
+      <c r="B40" s="30">
         <f>B25+B28+B33+B39</f>
         <v>50333</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <f>C25+C28+C33+C39</f>
         <v>50333</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <f>D25+D28+D33+D39</f>
         <v>50333</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="30">
         <f>E25+E28+E33+E39</f>
         <v>50333</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="30">
         <f>F25+F28+F33+F39</f>
         <v>50333</v>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="30">
         <f>G25+G28+G33+G39</f>
         <v>50333</v>
       </c>
-      <c r="H40" s="29">
+      <c r="H40" s="30">
         <f>H25+H28+H33+H39</f>
         <v>50333</v>
       </c>
-      <c r="I40" s="29">
+      <c r="I40" s="30">
         <f>I25+I28+I33+I39</f>
         <v>50333</v>
       </c>
-      <c r="J40" s="29">
+      <c r="J40" s="30">
         <f>J25+J28+J33+J39</f>
         <v>50333</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="30">
         <f>K25+K28+K33+K39</f>
         <v>50333</v>
       </c>
-      <c r="L40" s="29" t="str">
+      <c r="L40" s="30" t="str">
         <f>L25+L28+L33+L39</f>
         <v>0</v>
       </c>
-      <c r="M40" s="29" t="str">
+      <c r="M40" s="30" t="str">
         <f>M25+M28+M33+M39</f>
         <v>0</v>
       </c>
-      <c r="N40" s="29">
+      <c r="N40" s="30">
         <f>SUM(B40:M40)</f>
         <v>503333</v>
       </c>
@@ -6262,8 +6262,8 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="27" t="s">
-        <v>237</v>
+      <c r="A42" s="28" t="s">
+        <v>238</v>
       </c>
       <c r="B42" s="21">
         <v>8886</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -6330,179 +6330,179 @@
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="32">
         <f>B20+B40+B42</f>
         <v>137273</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <f>C20+C40+C42</f>
         <v>137273</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <f>D20+D40+D42</f>
         <v>137273</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <f>E20+E40+E42</f>
         <v>137273</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <f>F20+F40+F42</f>
         <v>137273</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <f>G20+G40+G42</f>
         <v>137273</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <f>H20+H40+H42</f>
         <v>137273</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <f>I20+I40+I42</f>
         <v>137273</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <f>J20+J40+J42</f>
         <v>137273</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <f>K20+K40+K42</f>
         <v>137273</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <f>L20+L40+L42</f>
         <v>8886</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <f>M20+M40+M42</f>
         <v>8886</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <f>SUM(B45:M45)</f>
         <v>1390502</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46" s="31">
+      <c r="A46" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="32">
         <f>B10-B45</f>
         <v>9227</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <f>C10-C45</f>
         <v>9227</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="32">
         <f>D10-D45</f>
         <v>9227</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="32">
         <f>E10-E45</f>
         <v>9227</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="32">
         <f>F10-F45</f>
         <v>9227</v>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="32">
         <f>G10-G45</f>
         <v>9227</v>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="32">
         <f>H10-H45</f>
         <v>9227</v>
       </c>
-      <c r="I46" s="31">
+      <c r="I46" s="32">
         <f>I10-I45</f>
         <v>9227</v>
       </c>
-      <c r="J46" s="31">
+      <c r="J46" s="32">
         <f>J10-J45</f>
         <v>9227</v>
       </c>
-      <c r="K46" s="31">
+      <c r="K46" s="32">
         <f>K10-K45</f>
         <v>9227</v>
       </c>
-      <c r="L46" s="31">
+      <c r="L46" s="32">
         <f>L10-L45</f>
         <v>-8886</v>
       </c>
-      <c r="M46" s="31">
+      <c r="M46" s="32">
         <f>M10-M45</f>
         <v>-8886</v>
       </c>
-      <c r="N46" s="31">
+      <c r="N46" s="32">
         <f>SUM(B46:M46)</f>
         <v>74498</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B47" s="32">
         <f>0+B46</f>
         <v>9227</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <f>B47+C46</f>
         <v>18454</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <f>C47+D46</f>
         <v>27681</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <f>D47+E46</f>
         <v>36908</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <f>E47+F46</f>
         <v>46135</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <f>F47+G46</f>
         <v>55362</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <f>G47+H46</f>
         <v>64589</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="32">
         <f>H47+I46</f>
         <v>73816</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="32">
         <f>I47+J46</f>
         <v>83043</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="32">
         <f>J47+K46</f>
         <v>92270</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="32">
         <f>K47+L46</f>
         <v>83384</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M47" s="32">
         <f>L47+M46</f>
         <v>74498</v>
       </c>
-      <c r="N47" s="31">
+      <c r="N47" s="32">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -6517,16 +6517,16 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B51" s="31">
+        <v>243</v>
+      </c>
+      <c r="B51" s="32">
         <f>M47</f>
         <v>74498</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B52" s="21">
         <f>MIN(B47:M47)</f>
@@ -6583,7 +6583,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6593,662 +6593,662 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="B3" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="46" t="s">
         <v>248</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="47">
+        <v>257</v>
+      </c>
+      <c r="C7" s="48">
         <v>120</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="48">
         <v>200</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <v>300</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="48">
         <v>400</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="48">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C8" s="48">
+        <v>258</v>
+      </c>
+      <c r="C8" s="49">
         <v>1414000</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="49">
         <v>2212650</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="49">
         <v>3265600</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="49">
         <v>4342850</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="49">
         <v>5524700</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="48">
+        <v>259</v>
+      </c>
+      <c r="C9" s="49">
         <v>780535</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="49">
         <v>936642</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="49">
         <v>936642</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="49">
         <v>936642</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="49">
         <v>936642</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10" s="48">
-        <v>604000</v>
-      </c>
-      <c r="D10" s="48">
-        <v>774860</v>
-      </c>
-      <c r="E10" s="48">
-        <v>994467.6</v>
-      </c>
-      <c r="F10" s="48">
-        <v>1226219.9279999998</v>
-      </c>
-      <c r="G10" s="48">
-        <v>1471949.32584</v>
+        <v>260</v>
+      </c>
+      <c r="C10" s="49">
+        <v>502000</v>
+      </c>
+      <c r="D10" s="49">
+        <v>715120</v>
+      </c>
+      <c r="E10" s="49">
+        <v>932931.6</v>
+      </c>
+      <c r="F10" s="49">
+        <v>1162843.928</v>
+      </c>
+      <c r="G10" s="49">
+        <v>1406664.32584</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="48">
+        <v>198</v>
+      </c>
+      <c r="C11" s="49">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="49">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="49">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="49">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="49">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="49">
-        <v>-17163.6108154935</v>
+      <c r="B12" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="50">
+        <v>84836.3891845065</v>
       </c>
       <c r="D12" s="50">
-        <v>454519.3891845065</v>
+        <v>514259.3891845065</v>
       </c>
       <c r="E12" s="50">
-        <v>1287861.7891845065</v>
+        <v>1349397.7891845065</v>
       </c>
       <c r="F12" s="50">
-        <v>2133359.461184507</v>
+        <v>2196735.4611845063</v>
       </c>
       <c r="G12" s="50">
-        <v>3069480.0633445065</v>
+        <v>3134765.0633445065</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" s="49">
-        <v>-17163.6108154935</v>
+      <c r="B13" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="50">
+        <v>84836.3891845065</v>
       </c>
       <c r="D13" s="50">
-        <v>437355.778369013</v>
+        <v>599095.778369013</v>
       </c>
       <c r="E13" s="50">
-        <v>1725217.5675535195</v>
+        <v>1948493.5675535195</v>
       </c>
       <c r="F13" s="50">
-        <v>3858577.0287380265</v>
+        <v>4145229.0287380256</v>
       </c>
       <c r="G13" s="50">
-        <v>6928057.092082533</v>
+        <v>7279994.092082532</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>260</v>
+      <c r="B14" s="28" t="s">
+        <v>261</v>
       </c>
       <c r="C14" s="51">
-        <v>-0.0121383386248186</v>
-      </c>
-      <c r="D14" s="52">
-        <v>0.20541856560436875</v>
-      </c>
-      <c r="E14" s="52">
-        <v>0.39437217944160535</v>
-      </c>
-      <c r="F14" s="52">
-        <v>0.49123489440908774</v>
-      </c>
-      <c r="G14" s="52">
-        <v>0.555592170315946</v>
+        <v>0.05999744638225353</v>
+      </c>
+      <c r="D14" s="51">
+        <v>0.2324178650868897</v>
+      </c>
+      <c r="E14" s="51">
+        <v>0.4132158835082394</v>
+      </c>
+      <c r="F14" s="51">
+        <v>0.5058280763057684</v>
+      </c>
+      <c r="G14" s="51">
+        <v>0.5674091015520312</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="53">
+      <c r="B15" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="52">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="52">
         <v>11063.25</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="52">
         <v>10885.333333333334</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="52">
         <v>10857.125</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="52">
         <v>11049.4</v>
       </c>
-      <c r="H15" s="54" t="s">
-        <v>262</v>
+      <c r="H15" s="53" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C16" s="55">
-        <v>11926.363423462444</v>
-      </c>
-      <c r="D16" s="55">
-        <v>8790.653054077467</v>
-      </c>
-      <c r="E16" s="55">
-        <v>6592.460702718312</v>
-      </c>
-      <c r="F16" s="55">
-        <v>5523.726347038733</v>
-      </c>
-      <c r="G16" s="55">
-        <v>4910.4398733109865</v>
+      <c r="B16" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="54">
+        <v>11076.363423462444</v>
+      </c>
+      <c r="D16" s="54">
+        <v>8491.953054077467</v>
+      </c>
+      <c r="E16" s="54">
+        <v>6387.340702718312</v>
+      </c>
+      <c r="F16" s="54">
+        <v>5365.286347038735</v>
+      </c>
+      <c r="G16" s="54">
+        <v>4779.869873310987</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="C17" s="48">
+        <v>265</v>
+      </c>
+      <c r="C17" s="49">
         <v>650</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="49">
         <v>670</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="49">
         <v>690</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="49">
         <v>710</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <v>732</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C18" s="56">
-        <v>2683.3333333333335</v>
-      </c>
-      <c r="D18" s="53">
-        <v>1658.3</v>
-      </c>
-      <c r="E18" s="53">
-        <v>1138.712</v>
-      </c>
-      <c r="F18" s="53">
-        <v>879.6398199999999</v>
-      </c>
-      <c r="G18" s="53">
-        <v>724.8386516800001</v>
-      </c>
-      <c r="H18" s="54" t="s">
         <v>266</v>
       </c>
+      <c r="C18" s="52">
+        <v>1833.3333333333333</v>
+      </c>
+      <c r="D18" s="52">
+        <v>1359.6</v>
+      </c>
+      <c r="E18" s="52">
+        <v>933.5919999999999</v>
+      </c>
+      <c r="F18" s="52">
+        <v>721.19982</v>
+      </c>
+      <c r="G18" s="52">
+        <v>594.2686516800002</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C19" s="57">
-        <v>-143.0300901291125</v>
-      </c>
-      <c r="D19" s="58">
-        <v>2272.5969459225325</v>
-      </c>
-      <c r="E19" s="58">
-        <v>4292.872630615022</v>
-      </c>
-      <c r="F19" s="58">
-        <v>5333.398652961267</v>
-      </c>
-      <c r="G19" s="58">
-        <v>6138.960126689013</v>
+      <c r="B19" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="55">
+        <v>706.9699098708875</v>
+      </c>
+      <c r="D19" s="55">
+        <v>2571.2969459225324</v>
+      </c>
+      <c r="E19" s="55">
+        <v>4497.992630615022</v>
+      </c>
+      <c r="F19" s="55">
+        <v>5491.838652961265</v>
+      </c>
+      <c r="G19" s="55">
+        <v>6269.530126689013</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C20" s="59">
+      <c r="B20" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="56">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="51">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="51">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="51">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="51">
         <v>0.16953716943906458</v>
       </c>
-      <c r="H20" s="54" t="s">
-        <v>269</v>
+      <c r="H20" s="53" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="C21" s="51">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D21" s="52">
-        <v>0.1498926626443405</v>
-      </c>
-      <c r="E21" s="52">
-        <v>0.10460975012248896</v>
-      </c>
-      <c r="F21" s="52">
-        <v>0.08101959036116835</v>
-      </c>
-      <c r="G21" s="52">
-        <v>0.06559982005176752</v>
-      </c>
-      <c r="H21" s="54" t="s">
+      <c r="B21" s="28" t="s">
         <v>271</v>
       </c>
+      <c r="C21" s="56">
+        <v>0.15558698727015557</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0.12289336316181954</v>
+      </c>
+      <c r="E21" s="51">
+        <v>0.08576604605585497</v>
+      </c>
+      <c r="F21" s="51">
+        <v>0.06642640846448761</v>
+      </c>
+      <c r="G21" s="51">
+        <v>0.053782888815682314</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C22" s="59">
-        <v>0.020838048090523337</v>
-      </c>
-      <c r="D22" s="52">
-        <v>0.22649221521704743</v>
-      </c>
-      <c r="E22" s="52">
-        <v>0.40865090641842233</v>
-      </c>
-      <c r="F22" s="52">
-        <v>0.5019717632430317</v>
-      </c>
-      <c r="G22" s="52">
-        <v>0.5640321961663076</v>
-      </c>
-      <c r="H22" s="54" t="s">
+      <c r="B22" s="28" t="s">
         <v>273</v>
       </c>
+      <c r="C22" s="56">
+        <v>0.09297383309759548</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0.2534915146995684</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.4274946104850563</v>
+      </c>
+      <c r="F22" s="51">
+        <v>0.5165649451397123</v>
+      </c>
+      <c r="G22" s="51">
+        <v>0.5758491274023929</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="C23" s="60">
+      <c r="B23" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="57">
         <v>3</v>
       </c>
-      <c r="D23" s="60">
+      <c r="D23" s="57">
         <v>3</v>
       </c>
-      <c r="E23" s="60">
+      <c r="E23" s="57">
         <v>3</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F23" s="57">
         <v>3</v>
       </c>
-      <c r="G23" s="60">
+      <c r="G23" s="57">
         <v>3</v>
       </c>
-      <c r="H23" s="54" t="s">
-        <v>275</v>
+      <c r="H23" s="53" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="C24" s="61">
-        <v>0.6319081672107103</v>
-      </c>
-      <c r="D24" s="62">
-        <v>10.747650235238861</v>
-      </c>
-      <c r="E24" s="62">
-        <v>28.61956160951256</v>
-      </c>
-      <c r="F24" s="62">
-        <v>46.752155680255555</v>
-      </c>
-      <c r="G24" s="62">
-        <v>66.82825457722186</v>
-      </c>
-      <c r="H24" s="54" t="s">
+      <c r="B24" s="28" t="s">
         <v>277</v>
       </c>
+      <c r="C24" s="58">
+        <v>2.819406319441915</v>
+      </c>
+      <c r="D24" s="58">
+        <v>12.028837878516235</v>
+      </c>
+      <c r="E24" s="58">
+        <v>29.939266377117455</v>
+      </c>
+      <c r="F24" s="58">
+        <v>48.11132119884187</v>
+      </c>
+      <c r="G24" s="58">
+        <v>68.2283606249514</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="C25" s="63" t="str">
-        <f>IF('5-Year Model'!B58&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="37" t="str">
-        <f>IF(AND('5-Year Model'!C58&gt;=0,'5-Year Model'!B58&lt;0),"✓ Break-even","")</f>
+      <c r="B25" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" s="38" t="str">
+        <f>IF('5-Year Model'!B59&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!D58&gt;=0,'5-Year Model'!C58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!E58&gt;=0,'5-Year Model'!D58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="63" t="str">
-        <f>IF(AND('5-Year Model'!F58&gt;=0,'5-Year Model'!E58&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="54" t="s">
-        <v>250</v>
+      <c r="D25" s="59" t="str">
+        <f>IF(AND('5-Year Model'!C59&gt;=0,'5-Year Model'!B59&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="59" t="str">
+        <f>IF(AND('5-Year Model'!D59&gt;=0,'5-Year Model'!C59&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="59" t="str">
+        <f>IF(AND('5-Year Model'!E59&gt;=0,'5-Year Model'!D59&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="59" t="str">
+        <f>IF(AND('5-Year Model'!F59&gt;=0,'5-Year Model'!E59&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="C26" s="64">
-        <v>0</v>
-      </c>
-      <c r="D26" s="64">
-        <v>3</v>
-      </c>
-      <c r="E26" s="64">
-        <v>10</v>
-      </c>
-      <c r="F26" s="65">
-        <v>21</v>
-      </c>
-      <c r="G26" s="60">
-        <v>34</v>
-      </c>
-      <c r="H26" s="54" t="s">
+      <c r="B26" s="28" t="s">
         <v>280</v>
       </c>
+      <c r="C26" s="60">
+        <v>1</v>
+      </c>
+      <c r="D26" s="60">
+        <v>4</v>
+      </c>
+      <c r="E26" s="61">
+        <v>12</v>
+      </c>
+      <c r="F26" s="61">
+        <v>23</v>
+      </c>
+      <c r="G26" s="57">
+        <v>37</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="64">
-        <v>0</v>
-      </c>
-      <c r="D27" s="60">
-        <v>91</v>
-      </c>
-      <c r="E27" s="60">
-        <v>318</v>
-      </c>
-      <c r="F27" s="60">
-        <v>637</v>
-      </c>
-      <c r="G27" s="60">
-        <v>1030</v>
-      </c>
-      <c r="H27" s="54" t="s">
-        <v>281</v>
+      <c r="B27" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="60">
+        <v>23</v>
+      </c>
+      <c r="D27" s="57">
+        <v>129</v>
+      </c>
+      <c r="E27" s="57">
+        <v>371</v>
+      </c>
+      <c r="F27" s="57">
+        <v>705</v>
+      </c>
+      <c r="G27" s="57">
+        <v>1112</v>
+      </c>
+      <c r="H27" s="53" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" s="37" t="s">
+      <c r="B30" s="62" t="s">
         <v>287</v>
       </c>
-      <c r="D30" s="67" t="s">
+      <c r="C30" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68" t="s">
+      <c r="D30" s="63" t="s">
         <v>289</v>
       </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
+        <v>290</v>
+      </c>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>290</v>
-      </c>
-      <c r="C31" s="69" t="s">
+      <c r="B31" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="C31" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D31" s="63" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
         <v>293</v>
       </c>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="C32" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D32" s="67" t="s">
+      <c r="C32" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" s="63" t="s">
         <v>295</v>
       </c>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68" t="s">
+      <c r="E32" s="63"/>
+      <c r="F32" s="64" t="s">
         <v>296</v>
       </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="62" t="s">
         <v>297</v>
       </c>
-      <c r="C33" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D33" s="67" t="s">
+      <c r="C33" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D33" s="63" t="s">
         <v>298</v>
       </c>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68" t="s">
+      <c r="E33" s="63"/>
+      <c r="F33" s="64" t="s">
         <v>299</v>
       </c>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
+      <c r="B34" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D34" s="67" t="s">
+      <c r="C34" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D34" s="63" t="s">
         <v>301</v>
       </c>
-      <c r="E34" s="67"/>
-      <c r="F34" s="68" t="s">
+      <c r="E34" s="63"/>
+      <c r="F34" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="62" t="s">
         <v>303</v>
       </c>
-      <c r="C35" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="67" t="s">
+      <c r="C35" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D35" s="63" t="s">
         <v>304</v>
       </c>
-      <c r="E35" s="67"/>
-      <c r="F35" s="68" t="s">
+      <c r="E35" s="63"/>
+      <c r="F35" s="64" t="s">
         <v>305</v>
       </c>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="66" t="s">
+      <c r="B36" s="62" t="s">
         <v>306</v>
       </c>
-      <c r="C36" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="67" t="s">
+      <c r="C36" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" s="63" t="s">
         <v>307</v>
       </c>
-      <c r="E36" s="67"/>
-      <c r="F36" s="68" t="s">
+      <c r="E36" s="63"/>
+      <c r="F36" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="66" t="s">
+      <c r="B38" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -7355,10 +7355,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -8,7 +8,8 @@
     <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Decision History" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Financial Health" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
@@ -19,15 +20,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H40</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="314">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -762,6 +765,15 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
   <si>
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
@@ -1179,7 +1191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1236,6 +1248,13 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6571,6 +6590,73 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy Charter&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -6583,7 +6669,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6593,127 +6679,127 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
+      <c r="B3" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>249</v>
+      <c r="B4" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C7" s="48">
+        <v>260</v>
+      </c>
+      <c r="C7" s="51">
         <v>120</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="51">
         <v>200</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="51">
         <v>300</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="51">
         <v>400</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="51">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="49">
+        <v>261</v>
+      </c>
+      <c r="C8" s="52">
         <v>1414000</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="52">
         <v>2212650</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="52">
         <v>3265600</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="52">
         <v>4342850</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="52">
         <v>5524700</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="C9" s="49">
+        <v>262</v>
+      </c>
+      <c r="C9" s="52">
         <v>780535</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="52">
         <v>936642</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="52">
         <v>936642</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="52">
         <v>936642</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="52">
         <v>936642</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="49">
+        <v>263</v>
+      </c>
+      <c r="C10" s="52">
         <v>502000</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="52">
         <v>715120</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="52">
         <v>932931.6</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="52">
         <v>1162843.928</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="52">
         <v>1406664.32584</v>
       </c>
     </row>
@@ -6721,19 +6807,19 @@
       <c r="B11" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="52">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="52">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="52">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="52">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="52">
         <v>46628.6108154935</v>
       </c>
     </row>
@@ -6741,19 +6827,19 @@
       <c r="B12" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="53">
         <v>84836.3891845065</v>
       </c>
-      <c r="D12" s="50">
+      <c r="D12" s="53">
         <v>514259.3891845065</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="53">
         <v>1349397.7891845065</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="53">
         <v>2196735.4611845063</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="53">
         <v>3134765.0633445065</v>
       </c>
     </row>
@@ -6761,494 +6847,494 @@
       <c r="B13" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="53">
         <v>84836.3891845065</v>
       </c>
-      <c r="D13" s="50">
+      <c r="D13" s="53">
         <v>599095.778369013</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="53">
         <v>1948493.5675535195</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="53">
         <v>4145229.0287380256</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="53">
         <v>7279994.092082532</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="C14" s="51">
+        <v>264</v>
+      </c>
+      <c r="C14" s="54">
         <v>0.05999744638225353</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="54">
         <v>0.2324178650868897</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="54">
         <v>0.4132158835082394</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="54">
         <v>0.5058280763057684</v>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="54">
         <v>0.5674091015520312</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="52">
+        <v>265</v>
+      </c>
+      <c r="C15" s="55">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="55">
         <v>11063.25</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="55">
         <v>10885.333333333334</v>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="55">
         <v>10857.125</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="55">
         <v>11049.4</v>
       </c>
-      <c r="H15" s="53" t="s">
-        <v>263</v>
+      <c r="H15" s="56" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="54">
+        <v>267</v>
+      </c>
+      <c r="C16" s="57">
         <v>11076.363423462444</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="57">
         <v>8491.953054077467</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="57">
         <v>6387.340702718312</v>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="57">
         <v>5365.286347038735</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="57">
         <v>4779.869873310987</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C17" s="49">
+        <v>268</v>
+      </c>
+      <c r="C17" s="52">
         <v>650</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="52">
         <v>670</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="52">
         <v>690</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="52">
         <v>710</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="52">
         <v>732</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="52">
+        <v>269</v>
+      </c>
+      <c r="C18" s="55">
         <v>1833.3333333333333</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="55">
         <v>1359.6</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="55">
         <v>933.5919999999999</v>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="55">
         <v>721.19982</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="55">
         <v>594.2686516800002</v>
       </c>
-      <c r="H18" s="53" t="s">
-        <v>267</v>
+      <c r="H18" s="56" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="55">
+        <v>271</v>
+      </c>
+      <c r="C19" s="58">
         <v>706.9699098708875</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="58">
         <v>2571.2969459225324</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="58">
         <v>4497.992630615022</v>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="58">
         <v>5491.838652961265</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="58">
         <v>6269.530126689013</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="56">
+        <v>272</v>
+      </c>
+      <c r="C20" s="59">
         <v>0.5520049504950495</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="54">
         <v>0.4233123178089621</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="54">
         <v>0.2868207986281235</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="54">
         <v>0.21567449946463726</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="54">
         <v>0.16953716943906458</v>
       </c>
-      <c r="H20" s="53" t="s">
-        <v>270</v>
+      <c r="H20" s="56" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="56">
+        <v>274</v>
+      </c>
+      <c r="C21" s="59">
         <v>0.15558698727015557</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="54">
         <v>0.12289336316181954</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="54">
         <v>0.08576604605585497</v>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="54">
         <v>0.06642640846448761</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="54">
         <v>0.053782888815682314</v>
       </c>
-      <c r="H21" s="53" t="s">
-        <v>272</v>
+      <c r="H21" s="56" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="C22" s="56">
+        <v>276</v>
+      </c>
+      <c r="C22" s="59">
         <v>0.09297383309759548</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="54">
         <v>0.2534915146995684</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="54">
         <v>0.4274946104850563</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="54">
         <v>0.5165649451397123</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="54">
         <v>0.5758491274023929</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>274</v>
+      <c r="H22" s="56" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23" s="57">
+        <v>278</v>
+      </c>
+      <c r="C23" s="60">
         <v>3</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="60">
         <v>3</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="60">
         <v>3</v>
       </c>
-      <c r="F23" s="57">
+      <c r="F23" s="60">
         <v>3</v>
       </c>
-      <c r="G23" s="57">
+      <c r="G23" s="60">
         <v>3</v>
       </c>
-      <c r="H23" s="53" t="s">
-        <v>276</v>
+      <c r="H23" s="56" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="58">
+        <v>280</v>
+      </c>
+      <c r="C24" s="61">
         <v>2.819406319441915</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="61">
         <v>12.028837878516235</v>
       </c>
-      <c r="E24" s="58">
+      <c r="E24" s="61">
         <v>29.939266377117455</v>
       </c>
-      <c r="F24" s="58">
+      <c r="F24" s="61">
         <v>48.11132119884187</v>
       </c>
-      <c r="G24" s="58">
+      <c r="G24" s="61">
         <v>68.2283606249514</v>
       </c>
-      <c r="H24" s="53" t="s">
-        <v>278</v>
+      <c r="H24" s="56" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C25" s="38" t="str">
         <f>IF('5-Year Model'!B59&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="59" t="str">
+      <c r="D25" s="62" t="str">
         <f>IF(AND('5-Year Model'!C59&gt;=0,'5-Year Model'!B59&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="59" t="str">
+      <c r="E25" s="62" t="str">
         <f>IF(AND('5-Year Model'!D59&gt;=0,'5-Year Model'!C59&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="59" t="str">
+      <c r="F25" s="62" t="str">
         <f>IF(AND('5-Year Model'!E59&gt;=0,'5-Year Model'!D59&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="59" t="str">
+      <c r="G25" s="62" t="str">
         <f>IF(AND('5-Year Model'!F59&gt;=0,'5-Year Model'!E59&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="53" t="s">
-        <v>251</v>
+      <c r="H25" s="56" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="C26" s="60">
+        <v>283</v>
+      </c>
+      <c r="C26" s="63">
         <v>1</v>
       </c>
-      <c r="D26" s="60">
+      <c r="D26" s="63">
         <v>4</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="64">
         <v>12</v>
       </c>
-      <c r="F26" s="61">
+      <c r="F26" s="64">
         <v>23</v>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="60">
         <v>37</v>
       </c>
-      <c r="H26" s="53" t="s">
-        <v>281</v>
+      <c r="H26" s="56" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="63">
         <v>23</v>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="60">
         <v>129</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="60">
         <v>371</v>
       </c>
-      <c r="F27" s="57">
+      <c r="F27" s="60">
         <v>705</v>
       </c>
-      <c r="G27" s="57">
+      <c r="G27" s="60">
         <v>1112</v>
       </c>
-      <c r="H27" s="53" t="s">
-        <v>282</v>
+      <c r="H27" s="56" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
-        <v>287</v>
+      <c r="B30" s="65" t="s">
+        <v>290</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>289</v>
-      </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
-        <v>290</v>
-      </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D30" s="66" t="s">
+        <v>292</v>
+      </c>
+      <c r="E30" s="66"/>
+      <c r="F30" s="67" t="s">
+        <v>293</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="65" t="s">
+        <v>294</v>
+      </c>
+      <c r="C31" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="C31" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64" t="s">
-        <v>293</v>
-      </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
+      <c r="D31" s="66" t="s">
+        <v>295</v>
+      </c>
+      <c r="E31" s="66"/>
+      <c r="F31" s="67" t="s">
+        <v>296</v>
+      </c>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
-        <v>294</v>
+      <c r="B32" s="65" t="s">
+        <v>297</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D32" s="63" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64" t="s">
-        <v>296</v>
-      </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="E32" s="66"/>
+      <c r="F32" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
-        <v>297</v>
+      <c r="B33" s="65" t="s">
+        <v>300</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="63" t="s">
-        <v>298</v>
-      </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="64" t="s">
-        <v>299</v>
-      </c>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D33" s="66" t="s">
+        <v>301</v>
+      </c>
+      <c r="E33" s="66"/>
+      <c r="F33" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="62" t="s">
-        <v>300</v>
+      <c r="B34" s="65" t="s">
+        <v>303</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D34" s="63" t="s">
-        <v>301</v>
-      </c>
-      <c r="E34" s="63"/>
-      <c r="F34" s="64" t="s">
-        <v>302</v>
-      </c>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D34" s="66" t="s">
+        <v>304</v>
+      </c>
+      <c r="E34" s="66"/>
+      <c r="F34" s="67" t="s">
+        <v>305</v>
+      </c>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>303</v>
+      <c r="B35" s="65" t="s">
+        <v>306</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D35" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="E35" s="63"/>
-      <c r="F35" s="64" t="s">
-        <v>305</v>
-      </c>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D35" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" s="66"/>
+      <c r="F35" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="62" t="s">
-        <v>306</v>
+      <c r="B36" s="65" t="s">
+        <v>309</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D36" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="E36" s="63"/>
-      <c r="F36" s="64" t="s">
-        <v>308</v>
-      </c>
-      <c r="G36" s="64"/>
-      <c r="H36" s="64"/>
+        <v>291</v>
+      </c>
+      <c r="D36" s="66" t="s">
+        <v>310</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="F36" s="67" t="s">
+        <v>311</v>
+      </c>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="62" t="s">
-        <v>309</v>
+      <c r="B38" s="65" t="s">
+        <v>312</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="65" t="s">
+      <c r="B40" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -38,7 +38,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -779,7 +779,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -779,7 +779,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -911,7 +911,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -6657,7 +6657,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6667,7 +6667,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>248</v>
       </c>
@@ -6677,8 +6677,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="47" t="s">
         <v>249</v>
       </c>
@@ -6688,6 +6689,7 @@
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="48" t="s">
@@ -7178,7 +7180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>286</v>
       </c>
@@ -7194,8 +7196,9 @@
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="65" t="s">
         <v>290</v>
       </c>
@@ -7211,8 +7214,9 @@
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="67"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="67"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="65" t="s">
         <v>294</v>
       </c>
@@ -7228,8 +7232,9 @@
       </c>
       <c r="G31" s="67"/>
       <c r="H31" s="67"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="67"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="65" t="s">
         <v>297</v>
       </c>
@@ -7245,8 +7250,9 @@
       </c>
       <c r="G32" s="67"/>
       <c r="H32" s="67"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="67"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="65" t="s">
         <v>300</v>
       </c>
@@ -7262,8 +7268,9 @@
       </c>
       <c r="G33" s="67"/>
       <c r="H33" s="67"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="67"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="65" t="s">
         <v>303</v>
       </c>
@@ -7279,8 +7286,9 @@
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="67"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="67"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="65" t="s">
         <v>306</v>
       </c>
@@ -7296,8 +7304,9 @@
       </c>
       <c r="G35" s="67"/>
       <c r="H35" s="67"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="67"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="65" t="s">
         <v>309</v>
       </c>
@@ -7313,6 +7322,7 @@
       </c>
       <c r="G36" s="67"/>
       <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="65" t="s">
@@ -7325,7 +7335,7 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="68" t="s">
         <v>155</v>
       </c>
@@ -7335,29 +7345,30 @@
       <c r="F40" s="68"/>
       <c r="G40" s="68"/>
       <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Charter_ADA_Grade-Band.xlsx
@@ -38,7 +38,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · nonprofit_501c3</t>
+    <t>Generated May 9, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -779,7 +779,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
